--- a/catamarca_creditos/analisis_cartera_catamarca.xlsx
+++ b/catamarca_creditos/analisis_cartera_catamarca.xlsx
@@ -207,6 +207,223 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Estado de cartera al corte marzo 2026</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Dashboard'!B20</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Dashboard'!$A$21:$A$24</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Dashboard'!$B$21:$B$24</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Estado</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Cantidad de créditos</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Semáforo de cartera</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <pieChart>
+        <varyColors val="1"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Dashboard'!E20</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Dashboard'!$D$21:$D$23</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Dashboard'!$E$21:$E$23</f>
+            </numRef>
+          </val>
+        </ser>
+        <firstSliceAng val="0"/>
+      </pieChart>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5760000" cy="2880000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>19</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4320000" cy="2880000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="2" name="Chart 2"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -553,7 +770,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -739,11 +956,106 @@
         <v>0.3641975308641975</v>
       </c>
     </row>
+    <row r="14"/>
+    <row r="20" hidden="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Categoría</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Semáforo</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" hidden="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Con cobro en marzo</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>8740000</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Verde</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="22" hidden="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Cancelados / finalizados</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>23</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Amarillo</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="23" hidden="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Sin cobro en marzo</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>59</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Rojo</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="24" hidden="1">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Sin registro en marzo</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Mora operativa</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/catamarca_creditos/analisis_cartera_catamarca.xlsx
+++ b/catamarca_creditos/analisis_cartera_catamarca.xlsx
@@ -23,7 +23,7 @@
     <numFmt numFmtId="164" formatCode="$ #,##0.00"/>
     <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -42,6 +42,9 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <color rgb="00000000"/>
     </font>
   </fonts>
   <fills count="7">
@@ -103,7 +106,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -123,6 +126,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -230,14 +235,14 @@
     </title>
     <plotArea>
       <barChart>
-        <barDir val="col"/>
+        <barDir val="bar"/>
         <grouping val="clustered"/>
         <ser>
           <idx val="0"/>
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Dashboard'!B20</f>
+              <f>'Dashboard'!I3</f>
             </strRef>
           </tx>
           <spPr>
@@ -247,12 +252,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Dashboard'!$A$21:$A$24</f>
+              <f>'Dashboard'!$H$4:$H$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Dashboard'!$B$21:$B$24</f>
+              <f>'Dashboard'!$I$4:$I$7</f>
             </numRef>
           </val>
         </ser>
@@ -275,7 +280,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>Estado</a:t>
+                  <a:t>Cantidad</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -302,7 +307,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>Cantidad de créditos</a:t>
+                  <a:t>Estado</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -346,7 +351,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Dashboard'!E20</f>
+              <f>'Dashboard'!I11</f>
             </strRef>
           </tx>
           <spPr>
@@ -356,12 +361,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Dashboard'!$D$21:$D$23</f>
+              <f>'Dashboard'!$H$12:$H$14</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Dashboard'!$E$21:$E$23</f>
+              <f>'Dashboard'!$I$12:$I$14</f>
             </numRef>
           </val>
         </ser>
@@ -381,12 +386,12 @@
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>6</col>
+      <col>10</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5760000" cy="2880000"/>
+    <ext cx="4320000" cy="2520000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -403,12 +408,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>6</col>
+      <col>10</col>
       <colOff>0</colOff>
-      <row>19</row>
+      <row>17</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="4320000" cy="2880000"/>
+    <ext cx="3600000" cy="2520000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -770,7 +775,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -778,6 +783,8 @@
     <col width="4" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -798,6 +805,16 @@
           <t>Cruce entre Excel de depósitos y Excel de cobranzas Cecilia</t>
         </is>
       </c>
+      <c r="H2" s="15" t="inlineStr">
+        <is>
+          <t>Base gráfico estados</t>
+        </is>
+      </c>
+      <c r="I2" s="16" t="n"/>
+      <c r="J2" s="16" t="n"/>
+      <c r="K2" s="16" t="n"/>
+      <c r="L2" s="16" t="n"/>
+      <c r="M2" s="16" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -810,6 +827,20 @@
           <t>Créditos desde 2025-12-01 y lectura de cobranza hasta marzo 2026</t>
         </is>
       </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>Estado</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+      <c r="J3" s="16" t="n"/>
+      <c r="K3" s="16" t="n"/>
+      <c r="L3" s="16" t="n"/>
+      <c r="M3" s="16" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -822,6 +853,32 @@
           <t>VERDE = al día / con cobro o finalizado | AMARILLO = sin exigibilidad clara | ROJO = mora operativa</t>
         </is>
       </c>
+      <c r="H4" s="16" t="inlineStr">
+        <is>
+          <t>Con cobro en marzo</t>
+        </is>
+      </c>
+      <c r="I4" s="16" t="n">
+        <v>59</v>
+      </c>
+      <c r="J4" s="16" t="n"/>
+      <c r="K4" s="16" t="n"/>
+      <c r="L4" s="16" t="n"/>
+      <c r="M4" s="16" t="n"/>
+    </row>
+    <row r="5">
+      <c r="H5" s="16" t="inlineStr">
+        <is>
+          <t>Cancelados / finalizados</t>
+        </is>
+      </c>
+      <c r="I5" s="16" t="n">
+        <v>23</v>
+      </c>
+      <c r="J5" s="16" t="n"/>
+      <c r="K5" s="16" t="n"/>
+      <c r="L5" s="16" t="n"/>
+      <c r="M5" s="16" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -837,6 +894,18 @@
           <t>Resumen de estado</t>
         </is>
       </c>
+      <c r="H6" s="16" t="inlineStr">
+        <is>
+          <t>Sin cobro en marzo</t>
+        </is>
+      </c>
+      <c r="I6" s="16" t="n">
+        <v>59</v>
+      </c>
+      <c r="J6" s="16" t="n"/>
+      <c r="K6" s="16" t="n"/>
+      <c r="L6" s="16" t="n"/>
+      <c r="M6" s="16" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -855,6 +924,18 @@
       <c r="E7" s="4" t="n">
         <v>78</v>
       </c>
+      <c r="H7" s="16" t="inlineStr">
+        <is>
+          <t>Sin registro en marzo</t>
+        </is>
+      </c>
+      <c r="I7" s="16" t="n">
+        <v>25</v>
+      </c>
+      <c r="J7" s="16" t="n"/>
+      <c r="K7" s="16" t="n"/>
+      <c r="L7" s="16" t="n"/>
+      <c r="M7" s="16" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -873,6 +954,12 @@
       <c r="E8" s="4" t="n">
         <v>25</v>
       </c>
+      <c r="H8" s="16" t="n"/>
+      <c r="I8" s="16" t="n"/>
+      <c r="J8" s="16" t="n"/>
+      <c r="K8" s="16" t="n"/>
+      <c r="L8" s="16" t="n"/>
+      <c r="M8" s="16" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -891,6 +978,12 @@
       <c r="E9" s="4" t="n">
         <v>59</v>
       </c>
+      <c r="H9" s="16" t="n"/>
+      <c r="I9" s="16" t="n"/>
+      <c r="J9" s="16" t="n"/>
+      <c r="K9" s="16" t="n"/>
+      <c r="L9" s="16" t="n"/>
+      <c r="M9" s="16" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -909,6 +1002,16 @@
       <c r="E10" s="4" t="n">
         <v>23</v>
       </c>
+      <c r="H10" s="15" t="inlineStr">
+        <is>
+          <t>Base gráfico semáforo</t>
+        </is>
+      </c>
+      <c r="I10" s="16" t="n"/>
+      <c r="J10" s="16" t="n"/>
+      <c r="K10" s="16" t="n"/>
+      <c r="L10" s="16" t="n"/>
+      <c r="M10" s="16" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -927,6 +1030,20 @@
       <c r="E11" s="4" t="n">
         <v>59</v>
       </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>Semáforo</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+      <c r="J11" s="16" t="n"/>
+      <c r="K11" s="16" t="n"/>
+      <c r="L11" s="16" t="n"/>
+      <c r="M11" s="16" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -945,6 +1062,18 @@
       <c r="E12" s="4" t="n">
         <v>25</v>
       </c>
+      <c r="H12" s="16" t="inlineStr">
+        <is>
+          <t>Verde</t>
+        </is>
+      </c>
+      <c r="I12" s="16" t="n">
+        <v>78</v>
+      </c>
+      <c r="J12" s="16" t="n"/>
+      <c r="K12" s="16" t="n"/>
+      <c r="L12" s="16" t="n"/>
+      <c r="M12" s="16" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -955,8 +1084,73 @@
       <c r="B13" s="10" t="n">
         <v>0.3641975308641975</v>
       </c>
-    </row>
-    <row r="14"/>
+      <c r="H13" s="16" t="inlineStr">
+        <is>
+          <t>Amarillo</t>
+        </is>
+      </c>
+      <c r="I13" s="16" t="n">
+        <v>25</v>
+      </c>
+      <c r="J13" s="16" t="n"/>
+      <c r="K13" s="16" t="n"/>
+      <c r="L13" s="16" t="n"/>
+      <c r="M13" s="16" t="n"/>
+    </row>
+    <row r="14">
+      <c r="H14" s="16" t="inlineStr">
+        <is>
+          <t>Rojo</t>
+        </is>
+      </c>
+      <c r="I14" s="16" t="n">
+        <v>59</v>
+      </c>
+      <c r="J14" s="16" t="n"/>
+      <c r="K14" s="16" t="n"/>
+      <c r="L14" s="16" t="n"/>
+      <c r="M14" s="16" t="n"/>
+    </row>
+    <row r="15">
+      <c r="H15" s="16" t="n"/>
+      <c r="I15" s="16" t="n"/>
+      <c r="J15" s="16" t="n"/>
+      <c r="K15" s="16" t="n"/>
+      <c r="L15" s="16" t="n"/>
+      <c r="M15" s="16" t="n"/>
+    </row>
+    <row r="16">
+      <c r="H16" s="16" t="n"/>
+      <c r="I16" s="16" t="n"/>
+      <c r="J16" s="16" t="n"/>
+      <c r="K16" s="16" t="n"/>
+      <c r="L16" s="16" t="n"/>
+      <c r="M16" s="16" t="n"/>
+    </row>
+    <row r="17">
+      <c r="H17" s="16" t="n"/>
+      <c r="I17" s="16" t="n"/>
+      <c r="J17" s="16" t="n"/>
+      <c r="K17" s="16" t="n"/>
+      <c r="L17" s="16" t="n"/>
+      <c r="M17" s="16" t="n"/>
+    </row>
+    <row r="18">
+      <c r="H18" s="16" t="n"/>
+      <c r="I18" s="16" t="n"/>
+      <c r="J18" s="16" t="n"/>
+      <c r="K18" s="16" t="n"/>
+      <c r="L18" s="16" t="n"/>
+      <c r="M18" s="16" t="n"/>
+    </row>
+    <row r="19">
+      <c r="H19" s="16" t="n"/>
+      <c r="I19" s="16" t="n"/>
+      <c r="J19" s="16" t="n"/>
+      <c r="K19" s="16" t="n"/>
+      <c r="L19" s="16" t="n"/>
+      <c r="M19" s="16" t="n"/>
+    </row>
     <row r="20" hidden="1">
       <c r="A20" t="inlineStr">
         <is>
@@ -978,6 +1172,12 @@
           <t>Cantidad</t>
         </is>
       </c>
+      <c r="H20" s="16" t="n"/>
+      <c r="I20" s="16" t="n"/>
+      <c r="J20" s="16" t="n"/>
+      <c r="K20" s="16" t="n"/>
+      <c r="L20" s="16" t="n"/>
+      <c r="M20" s="16" t="n"/>
     </row>
     <row r="21" hidden="1">
       <c r="A21" t="inlineStr">

--- a/catamarca_creditos/analisis_cartera_catamarca.xlsx
+++ b/catamarca_creditos/analisis_cartera_catamarca.xlsx
@@ -214,218 +214,56 @@
 </styleSheet>
 </file>
 
-<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="10"/>
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>Estado de cartera al corte marzo 2026</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <barChart>
-        <barDir val="bar"/>
-        <grouping val="clustered"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'Dashboard'!I3</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Dashboard'!$H$4:$H$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Dashboard'!$I$4:$I$7</f>
-            </numRef>
-          </val>
-        </ser>
-        <gapWidth val="150"/>
-        <axId val="10"/>
-        <axId val="100"/>
-      </barChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Cantidad</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Estado</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="10"/>
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>Semáforo de cartera</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <pieChart>
-        <varyColors val="1"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'Dashboard'!I11</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Dashboard'!$H$12:$H$14</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Dashboard'!$I$12:$I$14</f>
-            </numRef>
-          </val>
-        </ser>
-        <firstSliceAng val="0"/>
-      </pieChart>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>10</col>
+      <col>6</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="4320000" cy="2520000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="1" name="Chart 1"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
+    <ext cx="6858000" cy="3238500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
     <clientData/>
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>10</col>
+      <col>7</col>
       <colOff>0</colOff>
-      <row>17</row>
+      <row>21</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="3600000" cy="2520000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="2" name="Chart 2"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
+    <ext cx="4381500" cy="3048000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
     <clientData/>
   </oneCellAnchor>
 </wsDr>

--- a/catamarca_creditos/analisis_cartera_catamarca.xlsx
+++ b/catamarca_creditos/analisis_cartera_catamarca.xlsx
@@ -106,7 +106,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -128,6 +128,7 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -212,61 +213,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>6</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="6858000" cy="3238500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>7</col>
-      <colOff>0</colOff>
-      <row>21</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="4381500" cy="3048000"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -613,7 +559,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M25"/>
+  <dimension ref="A1:O40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -621,7 +567,8 @@
     <col width="4" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
@@ -643,16 +590,19 @@
           <t>Cruce entre Excel de depósitos y Excel de cobranzas Cecilia</t>
         </is>
       </c>
-      <c r="H2" s="15" t="inlineStr">
-        <is>
-          <t>Base gráfico estados</t>
-        </is>
-      </c>
-      <c r="I2" s="16" t="n"/>
-      <c r="J2" s="16" t="n"/>
-      <c r="K2" s="16" t="n"/>
-      <c r="L2" s="16" t="n"/>
-      <c r="M2" s="16" t="n"/>
+      <c r="G2" s="17" t="inlineStr">
+        <is>
+          <t>Resumen ejecutivo</t>
+        </is>
+      </c>
+      <c r="H2" s="17" t="n"/>
+      <c r="I2" s="17" t="n"/>
+      <c r="J2" s="17" t="n"/>
+      <c r="K2" s="17" t="n"/>
+      <c r="L2" s="17" t="n"/>
+      <c r="M2" s="17" t="n"/>
+      <c r="N2" s="17" t="n"/>
+      <c r="O2" s="17" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -665,20 +615,21 @@
           <t>Créditos desde 2025-12-01 y lectura de cobranza hasta marzo 2026</t>
         </is>
       </c>
-      <c r="H3" s="5" t="inlineStr">
-        <is>
-          <t>Estado</t>
-        </is>
-      </c>
-      <c r="I3" s="5" t="inlineStr">
-        <is>
-          <t>Cantidad</t>
-        </is>
-      </c>
-      <c r="J3" s="16" t="n"/>
-      <c r="K3" s="16" t="n"/>
-      <c r="L3" s="16" t="n"/>
-      <c r="M3" s="16" t="n"/>
+      <c r="G3" s="17" t="inlineStr">
+        <is>
+          <t>Créditos analizados</t>
+        </is>
+      </c>
+      <c r="H3" s="17" t="n">
+        <v>162</v>
+      </c>
+      <c r="I3" s="17" t="n"/>
+      <c r="J3" s="17" t="n"/>
+      <c r="K3" s="17" t="n"/>
+      <c r="L3" s="17" t="n"/>
+      <c r="M3" s="17" t="n"/>
+      <c r="N3" s="17" t="n"/>
+      <c r="O3" s="17" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -691,32 +642,38 @@
           <t>VERDE = al día / con cobro o finalizado | AMARILLO = sin exigibilidad clara | ROJO = mora operativa</t>
         </is>
       </c>
-      <c r="H4" s="16" t="inlineStr">
-        <is>
-          <t>Con cobro en marzo</t>
-        </is>
-      </c>
-      <c r="I4" s="16" t="n">
-        <v>59</v>
-      </c>
-      <c r="J4" s="16" t="n"/>
-      <c r="K4" s="16" t="n"/>
-      <c r="L4" s="16" t="n"/>
-      <c r="M4" s="16" t="n"/>
+      <c r="G4" s="17" t="inlineStr">
+        <is>
+          <t>Monto depositado total</t>
+        </is>
+      </c>
+      <c r="H4" s="17" t="n">
+        <v>70588070</v>
+      </c>
+      <c r="I4" s="17" t="n"/>
+      <c r="J4" s="17" t="n"/>
+      <c r="K4" s="17" t="n"/>
+      <c r="L4" s="17" t="n"/>
+      <c r="M4" s="17" t="n"/>
+      <c r="N4" s="17" t="n"/>
+      <c r="O4" s="17" t="n"/>
     </row>
     <row r="5">
-      <c r="H5" s="16" t="inlineStr">
-        <is>
-          <t>Cancelados / finalizados</t>
-        </is>
-      </c>
-      <c r="I5" s="16" t="n">
-        <v>23</v>
-      </c>
-      <c r="J5" s="16" t="n"/>
-      <c r="K5" s="16" t="n"/>
-      <c r="L5" s="16" t="n"/>
-      <c r="M5" s="16" t="n"/>
+      <c r="G5" s="17" t="inlineStr">
+        <is>
+          <t>Monto total a cobrar</t>
+        </is>
+      </c>
+      <c r="H5" s="17" t="n">
+        <v>293652000</v>
+      </c>
+      <c r="I5" s="17" t="n"/>
+      <c r="J5" s="17" t="n"/>
+      <c r="K5" s="17" t="n"/>
+      <c r="L5" s="17" t="n"/>
+      <c r="M5" s="17" t="n"/>
+      <c r="N5" s="17" t="n"/>
+      <c r="O5" s="17" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -732,18 +689,21 @@
           <t>Resumen de estado</t>
         </is>
       </c>
-      <c r="H6" s="16" t="inlineStr">
-        <is>
-          <t>Sin cobro en marzo</t>
-        </is>
-      </c>
-      <c r="I6" s="16" t="n">
-        <v>59</v>
-      </c>
-      <c r="J6" s="16" t="n"/>
-      <c r="K6" s="16" t="n"/>
-      <c r="L6" s="16" t="n"/>
-      <c r="M6" s="16" t="n"/>
+      <c r="G6" s="17" t="inlineStr">
+        <is>
+          <t>Monto cobrado en marzo</t>
+        </is>
+      </c>
+      <c r="H6" s="17" t="n">
+        <v>8740000</v>
+      </c>
+      <c r="I6" s="17" t="n"/>
+      <c r="J6" s="17" t="n"/>
+      <c r="K6" s="17" t="n"/>
+      <c r="L6" s="17" t="n"/>
+      <c r="M6" s="17" t="n"/>
+      <c r="N6" s="17" t="n"/>
+      <c r="O6" s="17" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -762,18 +722,19 @@
       <c r="E7" s="4" t="n">
         <v>78</v>
       </c>
-      <c r="H7" s="16" t="inlineStr">
-        <is>
-          <t>Sin registro en marzo</t>
-        </is>
-      </c>
-      <c r="I7" s="16" t="n">
-        <v>25</v>
-      </c>
-      <c r="J7" s="16" t="n"/>
-      <c r="K7" s="16" t="n"/>
-      <c r="L7" s="16" t="n"/>
-      <c r="M7" s="16" t="n"/>
+      <c r="G7" s="17" t="inlineStr">
+        <is>
+          <t>Mora operativa</t>
+        </is>
+      </c>
+      <c r="H7" s="17" t="n"/>
+      <c r="I7" s="17" t="n"/>
+      <c r="J7" s="17" t="n"/>
+      <c r="K7" s="17" t="n"/>
+      <c r="L7" s="17" t="n"/>
+      <c r="M7" s="17" t="n"/>
+      <c r="N7" s="17" t="n"/>
+      <c r="O7" s="17" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -792,12 +753,19 @@
       <c r="E8" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="H8" s="16" t="n"/>
-      <c r="I8" s="16" t="n"/>
-      <c r="J8" s="16" t="n"/>
-      <c r="K8" s="16" t="n"/>
-      <c r="L8" s="16" t="n"/>
-      <c r="M8" s="16" t="n"/>
+      <c r="G8" s="17" t="inlineStr">
+        <is>
+          <t>% mora operativa</t>
+        </is>
+      </c>
+      <c r="H8" s="17" t="n"/>
+      <c r="I8" s="17" t="n"/>
+      <c r="J8" s="17" t="n"/>
+      <c r="K8" s="17" t="n"/>
+      <c r="L8" s="17" t="n"/>
+      <c r="M8" s="17" t="n"/>
+      <c r="N8" s="17" t="n"/>
+      <c r="O8" s="17" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -816,12 +784,15 @@
       <c r="E9" s="4" t="n">
         <v>59</v>
       </c>
-      <c r="H9" s="16" t="n"/>
-      <c r="I9" s="16" t="n"/>
-      <c r="J9" s="16" t="n"/>
-      <c r="K9" s="16" t="n"/>
-      <c r="L9" s="16" t="n"/>
-      <c r="M9" s="16" t="n"/>
+      <c r="G9" s="17" t="n"/>
+      <c r="H9" s="17" t="n"/>
+      <c r="I9" s="17" t="n"/>
+      <c r="J9" s="17" t="n"/>
+      <c r="K9" s="17" t="n"/>
+      <c r="L9" s="17" t="n"/>
+      <c r="M9" s="17" t="n"/>
+      <c r="N9" s="17" t="n"/>
+      <c r="O9" s="17" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -840,16 +811,15 @@
       <c r="E10" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="H10" s="15" t="inlineStr">
-        <is>
-          <t>Base gráfico semáforo</t>
-        </is>
-      </c>
-      <c r="I10" s="16" t="n"/>
-      <c r="J10" s="16" t="n"/>
-      <c r="K10" s="16" t="n"/>
-      <c r="L10" s="16" t="n"/>
-      <c r="M10" s="16" t="n"/>
+      <c r="G10" s="17" t="n"/>
+      <c r="H10" s="17" t="n"/>
+      <c r="I10" s="17" t="n"/>
+      <c r="J10" s="17" t="n"/>
+      <c r="K10" s="17" t="n"/>
+      <c r="L10" s="17" t="n"/>
+      <c r="M10" s="17" t="n"/>
+      <c r="N10" s="17" t="n"/>
+      <c r="O10" s="17" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -868,20 +838,15 @@
       <c r="E11" s="4" t="n">
         <v>59</v>
       </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>Semáforo</t>
-        </is>
-      </c>
-      <c r="I11" s="5" t="inlineStr">
-        <is>
-          <t>Cantidad</t>
-        </is>
-      </c>
-      <c r="J11" s="16" t="n"/>
-      <c r="K11" s="16" t="n"/>
-      <c r="L11" s="16" t="n"/>
-      <c r="M11" s="16" t="n"/>
+      <c r="G11" s="17" t="n"/>
+      <c r="H11" s="17" t="n"/>
+      <c r="I11" s="17" t="n"/>
+      <c r="J11" s="17" t="n"/>
+      <c r="K11" s="17" t="n"/>
+      <c r="L11" s="17" t="n"/>
+      <c r="M11" s="17" t="n"/>
+      <c r="N11" s="17" t="n"/>
+      <c r="O11" s="17" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -900,18 +865,15 @@
       <c r="E12" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="H12" s="16" t="inlineStr">
-        <is>
-          <t>Verde</t>
-        </is>
-      </c>
-      <c r="I12" s="16" t="n">
-        <v>78</v>
-      </c>
-      <c r="J12" s="16" t="n"/>
-      <c r="K12" s="16" t="n"/>
-      <c r="L12" s="16" t="n"/>
-      <c r="M12" s="16" t="n"/>
+      <c r="G12" s="17" t="n"/>
+      <c r="H12" s="17" t="n"/>
+      <c r="I12" s="17" t="n"/>
+      <c r="J12" s="17" t="n"/>
+      <c r="K12" s="17" t="n"/>
+      <c r="L12" s="17" t="n"/>
+      <c r="M12" s="17" t="n"/>
+      <c r="N12" s="17" t="n"/>
+      <c r="O12" s="17" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -922,75 +884,84 @@
       <c r="B13" s="10" t="n">
         <v>0.3641975308641975</v>
       </c>
-      <c r="H13" s="16" t="inlineStr">
-        <is>
-          <t>Amarillo</t>
-        </is>
-      </c>
-      <c r="I13" s="16" t="n">
-        <v>25</v>
-      </c>
-      <c r="J13" s="16" t="n"/>
-      <c r="K13" s="16" t="n"/>
-      <c r="L13" s="16" t="n"/>
-      <c r="M13" s="16" t="n"/>
+      <c r="G13" s="17" t="n"/>
+      <c r="H13" s="17" t="n"/>
+      <c r="I13" s="17" t="n"/>
+      <c r="J13" s="17" t="n"/>
+      <c r="K13" s="17" t="n"/>
+      <c r="L13" s="17" t="n"/>
+      <c r="M13" s="17" t="n"/>
+      <c r="N13" s="17" t="n"/>
+      <c r="O13" s="17" t="n"/>
     </row>
     <row r="14">
-      <c r="H14" s="16" t="inlineStr">
-        <is>
-          <t>Rojo</t>
-        </is>
-      </c>
-      <c r="I14" s="16" t="n">
-        <v>59</v>
-      </c>
-      <c r="J14" s="16" t="n"/>
-      <c r="K14" s="16" t="n"/>
-      <c r="L14" s="16" t="n"/>
-      <c r="M14" s="16" t="n"/>
+      <c r="G14" s="17" t="n"/>
+      <c r="H14" s="17" t="n"/>
+      <c r="I14" s="17" t="n"/>
+      <c r="J14" s="17" t="n"/>
+      <c r="K14" s="17" t="n"/>
+      <c r="L14" s="17" t="n"/>
+      <c r="M14" s="17" t="n"/>
+      <c r="N14" s="17" t="n"/>
+      <c r="O14" s="17" t="n"/>
     </row>
     <row r="15">
-      <c r="H15" s="16" t="n"/>
-      <c r="I15" s="16" t="n"/>
-      <c r="J15" s="16" t="n"/>
-      <c r="K15" s="16" t="n"/>
-      <c r="L15" s="16" t="n"/>
-      <c r="M15" s="16" t="n"/>
+      <c r="G15" s="17" t="n"/>
+      <c r="H15" s="17" t="n"/>
+      <c r="I15" s="17" t="n"/>
+      <c r="J15" s="17" t="n"/>
+      <c r="K15" s="17" t="n"/>
+      <c r="L15" s="17" t="n"/>
+      <c r="M15" s="17" t="n"/>
+      <c r="N15" s="17" t="n"/>
+      <c r="O15" s="17" t="n"/>
     </row>
     <row r="16">
-      <c r="H16" s="16" t="n"/>
-      <c r="I16" s="16" t="n"/>
-      <c r="J16" s="16" t="n"/>
-      <c r="K16" s="16" t="n"/>
-      <c r="L16" s="16" t="n"/>
-      <c r="M16" s="16" t="n"/>
+      <c r="G16" s="17" t="n"/>
+      <c r="H16" s="17" t="n"/>
+      <c r="I16" s="17" t="n"/>
+      <c r="J16" s="17" t="n"/>
+      <c r="K16" s="17" t="n"/>
+      <c r="L16" s="17" t="n"/>
+      <c r="M16" s="17" t="n"/>
+      <c r="N16" s="17" t="n"/>
+      <c r="O16" s="17" t="n"/>
     </row>
     <row r="17">
-      <c r="H17" s="16" t="n"/>
-      <c r="I17" s="16" t="n"/>
-      <c r="J17" s="16" t="n"/>
-      <c r="K17" s="16" t="n"/>
-      <c r="L17" s="16" t="n"/>
-      <c r="M17" s="16" t="n"/>
+      <c r="G17" s="17" t="n"/>
+      <c r="H17" s="17" t="n"/>
+      <c r="I17" s="17" t="n"/>
+      <c r="J17" s="17" t="n"/>
+      <c r="K17" s="17" t="n"/>
+      <c r="L17" s="17" t="n"/>
+      <c r="M17" s="17" t="n"/>
+      <c r="N17" s="17" t="n"/>
+      <c r="O17" s="17" t="n"/>
     </row>
     <row r="18">
-      <c r="H18" s="16" t="n"/>
-      <c r="I18" s="16" t="n"/>
-      <c r="J18" s="16" t="n"/>
-      <c r="K18" s="16" t="n"/>
-      <c r="L18" s="16" t="n"/>
-      <c r="M18" s="16" t="n"/>
+      <c r="G18" s="17" t="n"/>
+      <c r="H18" s="17" t="n"/>
+      <c r="I18" s="17" t="n"/>
+      <c r="J18" s="17" t="n"/>
+      <c r="K18" s="17" t="n"/>
+      <c r="L18" s="17" t="n"/>
+      <c r="M18" s="17" t="n"/>
+      <c r="N18" s="17" t="n"/>
+      <c r="O18" s="17" t="n"/>
     </row>
     <row r="19">
-      <c r="H19" s="16" t="n"/>
-      <c r="I19" s="16" t="n"/>
-      <c r="J19" s="16" t="n"/>
-      <c r="K19" s="16" t="n"/>
-      <c r="L19" s="16" t="n"/>
-      <c r="M19" s="16" t="n"/>
+      <c r="G19" s="17" t="n"/>
+      <c r="H19" s="17" t="n"/>
+      <c r="I19" s="17" t="n"/>
+      <c r="J19" s="17" t="n"/>
+      <c r="K19" s="17" t="n"/>
+      <c r="L19" s="17" t="n"/>
+      <c r="M19" s="17" t="n"/>
+      <c r="N19" s="17" t="n"/>
+      <c r="O19" s="17" t="n"/>
     </row>
     <row r="20" hidden="1">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="17" t="inlineStr">
         <is>
           <t>Categoría</t>
         </is>
@@ -1010,12 +981,15 @@
           <t>Cantidad</t>
         </is>
       </c>
-      <c r="H20" s="16" t="n"/>
-      <c r="I20" s="16" t="n"/>
-      <c r="J20" s="16" t="n"/>
-      <c r="K20" s="16" t="n"/>
-      <c r="L20" s="16" t="n"/>
-      <c r="M20" s="16" t="n"/>
+      <c r="G20" s="17" t="n"/>
+      <c r="H20" s="17" t="n"/>
+      <c r="I20" s="17" t="n"/>
+      <c r="J20" s="17" t="n"/>
+      <c r="K20" s="17" t="n"/>
+      <c r="L20" s="17" t="n"/>
+      <c r="M20" s="17" t="n"/>
+      <c r="N20" s="17" t="n"/>
+      <c r="O20" s="17" t="n"/>
     </row>
     <row r="21" hidden="1">
       <c r="A21" t="inlineStr">
@@ -1034,6 +1008,15 @@
       <c r="E21" t="n">
         <v>78</v>
       </c>
+      <c r="G21" s="17" t="n"/>
+      <c r="H21" s="17" t="n"/>
+      <c r="I21" s="17" t="n"/>
+      <c r="J21" s="17" t="n"/>
+      <c r="K21" s="17" t="n"/>
+      <c r="L21" s="17" t="n"/>
+      <c r="M21" s="17" t="n"/>
+      <c r="N21" s="17" t="n"/>
+      <c r="O21" s="17" t="n"/>
     </row>
     <row r="22" hidden="1">
       <c r="A22" t="inlineStr">
@@ -1052,6 +1035,15 @@
       <c r="E22" t="n">
         <v>25</v>
       </c>
+      <c r="G22" s="17" t="n"/>
+      <c r="H22" s="17" t="n"/>
+      <c r="I22" s="17" t="n"/>
+      <c r="J22" s="17" t="n"/>
+      <c r="K22" s="17" t="n"/>
+      <c r="L22" s="17" t="n"/>
+      <c r="M22" s="17" t="n"/>
+      <c r="N22" s="17" t="n"/>
+      <c r="O22" s="17" t="n"/>
     </row>
     <row r="23" hidden="1">
       <c r="A23" t="inlineStr">
@@ -1070,6 +1062,15 @@
       <c r="E23" t="n">
         <v>59</v>
       </c>
+      <c r="G23" s="17" t="n"/>
+      <c r="H23" s="17" t="n"/>
+      <c r="I23" s="17" t="n"/>
+      <c r="J23" s="17" t="n"/>
+      <c r="K23" s="17" t="n"/>
+      <c r="L23" s="17" t="n"/>
+      <c r="M23" s="17" t="n"/>
+      <c r="N23" s="17" t="n"/>
+      <c r="O23" s="17" t="n"/>
     </row>
     <row r="24" hidden="1">
       <c r="A24" t="inlineStr">
@@ -1080,6 +1081,15 @@
       <c r="B24" t="n">
         <v>25</v>
       </c>
+      <c r="G24" s="17" t="n"/>
+      <c r="H24" s="17" t="n"/>
+      <c r="I24" s="17" t="n"/>
+      <c r="J24" s="17" t="n"/>
+      <c r="K24" s="17" t="n"/>
+      <c r="L24" s="17" t="n"/>
+      <c r="M24" s="17" t="n"/>
+      <c r="N24" s="17" t="n"/>
+      <c r="O24" s="17" t="n"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1087,13 +1097,186 @@
           <t>Mora operativa</t>
         </is>
       </c>
+      <c r="G25" s="17" t="n"/>
+      <c r="H25" s="17" t="n"/>
+      <c r="I25" s="17" t="n"/>
+      <c r="J25" s="17" t="n"/>
+      <c r="K25" s="17" t="n"/>
+      <c r="L25" s="17" t="n"/>
+      <c r="M25" s="17" t="n"/>
+      <c r="N25" s="17" t="n"/>
+      <c r="O25" s="17" t="n"/>
+    </row>
+    <row r="26">
+      <c r="G26" s="17" t="n"/>
+      <c r="H26" s="17" t="n"/>
+      <c r="I26" s="17" t="n"/>
+      <c r="J26" s="17" t="n"/>
+      <c r="K26" s="17" t="n"/>
+      <c r="L26" s="17" t="n"/>
+      <c r="M26" s="17" t="n"/>
+      <c r="N26" s="17" t="n"/>
+      <c r="O26" s="17" t="n"/>
+    </row>
+    <row r="27">
+      <c r="G27" s="17" t="n"/>
+      <c r="H27" s="17" t="n"/>
+      <c r="I27" s="17" t="n"/>
+      <c r="J27" s="17" t="n"/>
+      <c r="K27" s="17" t="n"/>
+      <c r="L27" s="17" t="n"/>
+      <c r="M27" s="17" t="n"/>
+      <c r="N27" s="17" t="n"/>
+      <c r="O27" s="17" t="n"/>
+    </row>
+    <row r="28">
+      <c r="G28" s="17" t="n"/>
+      <c r="H28" s="17" t="n"/>
+      <c r="I28" s="17" t="n"/>
+      <c r="J28" s="17" t="n"/>
+      <c r="K28" s="17" t="n"/>
+      <c r="L28" s="17" t="n"/>
+      <c r="M28" s="17" t="n"/>
+      <c r="N28" s="17" t="n"/>
+      <c r="O28" s="17" t="n"/>
+    </row>
+    <row r="29">
+      <c r="G29" s="17" t="n"/>
+      <c r="H29" s="17" t="n"/>
+      <c r="I29" s="17" t="n"/>
+      <c r="J29" s="17" t="n"/>
+      <c r="K29" s="17" t="n"/>
+      <c r="L29" s="17" t="n"/>
+      <c r="M29" s="17" t="n"/>
+      <c r="N29" s="17" t="n"/>
+      <c r="O29" s="17" t="n"/>
+    </row>
+    <row r="30">
+      <c r="G30" s="17" t="n"/>
+      <c r="H30" s="17" t="n"/>
+      <c r="I30" s="17" t="n"/>
+      <c r="J30" s="17" t="n"/>
+      <c r="K30" s="17" t="n"/>
+      <c r="L30" s="17" t="n"/>
+      <c r="M30" s="17" t="n"/>
+      <c r="N30" s="17" t="n"/>
+      <c r="O30" s="17" t="n"/>
+    </row>
+    <row r="31">
+      <c r="G31" s="17" t="n"/>
+      <c r="H31" s="17" t="n"/>
+      <c r="I31" s="17" t="n"/>
+      <c r="J31" s="17" t="n"/>
+      <c r="K31" s="17" t="n"/>
+      <c r="L31" s="17" t="n"/>
+      <c r="M31" s="17" t="n"/>
+      <c r="N31" s="17" t="n"/>
+      <c r="O31" s="17" t="n"/>
+    </row>
+    <row r="32">
+      <c r="G32" s="17" t="n"/>
+      <c r="H32" s="17" t="n"/>
+      <c r="I32" s="17" t="n"/>
+      <c r="J32" s="17" t="n"/>
+      <c r="K32" s="17" t="n"/>
+      <c r="L32" s="17" t="n"/>
+      <c r="M32" s="17" t="n"/>
+      <c r="N32" s="17" t="n"/>
+      <c r="O32" s="17" t="n"/>
+    </row>
+    <row r="33">
+      <c r="G33" s="17" t="n"/>
+      <c r="H33" s="17" t="n"/>
+      <c r="I33" s="17" t="n"/>
+      <c r="J33" s="17" t="n"/>
+      <c r="K33" s="17" t="n"/>
+      <c r="L33" s="17" t="n"/>
+      <c r="M33" s="17" t="n"/>
+      <c r="N33" s="17" t="n"/>
+      <c r="O33" s="17" t="n"/>
+    </row>
+    <row r="34">
+      <c r="G34" s="17" t="n"/>
+      <c r="H34" s="17" t="n"/>
+      <c r="I34" s="17" t="n"/>
+      <c r="J34" s="17" t="n"/>
+      <c r="K34" s="17" t="n"/>
+      <c r="L34" s="17" t="n"/>
+      <c r="M34" s="17" t="n"/>
+      <c r="N34" s="17" t="n"/>
+      <c r="O34" s="17" t="n"/>
+    </row>
+    <row r="35">
+      <c r="G35" s="17" t="n"/>
+      <c r="H35" s="17" t="n"/>
+      <c r="I35" s="17" t="n"/>
+      <c r="J35" s="17" t="n"/>
+      <c r="K35" s="17" t="n"/>
+      <c r="L35" s="17" t="n"/>
+      <c r="M35" s="17" t="n"/>
+      <c r="N35" s="17" t="n"/>
+      <c r="O35" s="17" t="n"/>
+    </row>
+    <row r="36">
+      <c r="G36" s="17" t="n"/>
+      <c r="H36" s="17" t="n"/>
+      <c r="I36" s="17" t="n"/>
+      <c r="J36" s="17" t="n"/>
+      <c r="K36" s="17" t="n"/>
+      <c r="L36" s="17" t="n"/>
+      <c r="M36" s="17" t="n"/>
+      <c r="N36" s="17" t="n"/>
+      <c r="O36" s="17" t="n"/>
+    </row>
+    <row r="37">
+      <c r="G37" s="17" t="n"/>
+      <c r="H37" s="17" t="n"/>
+      <c r="I37" s="17" t="n"/>
+      <c r="J37" s="17" t="n"/>
+      <c r="K37" s="17" t="n"/>
+      <c r="L37" s="17" t="n"/>
+      <c r="M37" s="17" t="n"/>
+      <c r="N37" s="17" t="n"/>
+      <c r="O37" s="17" t="n"/>
+    </row>
+    <row r="38">
+      <c r="G38" s="17" t="n"/>
+      <c r="H38" s="17" t="n"/>
+      <c r="I38" s="17" t="n"/>
+      <c r="J38" s="17" t="n"/>
+      <c r="K38" s="17" t="n"/>
+      <c r="L38" s="17" t="n"/>
+      <c r="M38" s="17" t="n"/>
+      <c r="N38" s="17" t="n"/>
+      <c r="O38" s="17" t="n"/>
+    </row>
+    <row r="39">
+      <c r="G39" s="17" t="n"/>
+      <c r="H39" s="17" t="n"/>
+      <c r="I39" s="17" t="n"/>
+      <c r="J39" s="17" t="n"/>
+      <c r="K39" s="17" t="n"/>
+      <c r="L39" s="17" t="n"/>
+      <c r="M39" s="17" t="n"/>
+      <c r="N39" s="17" t="n"/>
+      <c r="O39" s="17" t="n"/>
+    </row>
+    <row r="40">
+      <c r="G40" s="17" t="n"/>
+      <c r="H40" s="17" t="n"/>
+      <c r="I40" s="17" t="n"/>
+      <c r="J40" s="17" t="n"/>
+      <c r="K40" s="17" t="n"/>
+      <c r="L40" s="17" t="n"/>
+      <c r="M40" s="17" t="n"/>
+      <c r="N40" s="17" t="n"/>
+      <c r="O40" s="17" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/catamarca_creditos/analisis_cartera_catamarca.xlsx
+++ b/catamarca_creditos/analisis_cartera_catamarca.xlsx
@@ -23,7 +23,7 @@
     <numFmt numFmtId="164" formatCode="$ #,##0.00"/>
     <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -42,9 +42,6 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-    </font>
-    <font>
-      <color rgb="00000000"/>
     </font>
   </fonts>
   <fills count="7">
@@ -106,15 +103,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -126,9 +122,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -216,7 +209,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TKPIs" displayName="TKPIs" ref="A1:B14" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T_KPIs" displayName="T_KPIs" ref="A1:B14" headerRowCount="1">
   <autoFilter ref="A1:B14"/>
   <tableColumns count="2">
     <tableColumn id="1" name="KPI"/>
@@ -227,7 +220,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="TMora" displayName="TMora" ref="A1:J60" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="T_Mora" displayName="T_Mora" ref="A1:J60" headerRowCount="1">
   <autoFilter ref="A1:J60"/>
   <tableColumns count="10">
     <tableColumn id="1" name="Semáforo"/>
@@ -246,7 +239,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="TConsolidado" displayName="TConsolidado" ref="A1:P163" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="T_Consolidado" displayName="T_Consolidado" ref="A1:P163" headerRowCount="1">
   <autoFilter ref="A1:P163"/>
   <tableColumns count="16">
     <tableColumn id="1" name="Semáforo"/>
@@ -559,17 +552,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O40"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="4" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="28" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -590,19 +580,6 @@
           <t>Cruce entre Excel de depósitos y Excel de cobranzas Cecilia</t>
         </is>
       </c>
-      <c r="G2" s="17" t="inlineStr">
-        <is>
-          <t>Resumen ejecutivo</t>
-        </is>
-      </c>
-      <c r="H2" s="17" t="n"/>
-      <c r="I2" s="17" t="n"/>
-      <c r="J2" s="17" t="n"/>
-      <c r="K2" s="17" t="n"/>
-      <c r="L2" s="17" t="n"/>
-      <c r="M2" s="17" t="n"/>
-      <c r="N2" s="17" t="n"/>
-      <c r="O2" s="17" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -615,21 +592,6 @@
           <t>Créditos desde 2025-12-01 y lectura de cobranza hasta marzo 2026</t>
         </is>
       </c>
-      <c r="G3" s="17" t="inlineStr">
-        <is>
-          <t>Créditos analizados</t>
-        </is>
-      </c>
-      <c r="H3" s="17" t="n">
-        <v>162</v>
-      </c>
-      <c r="I3" s="17" t="n"/>
-      <c r="J3" s="17" t="n"/>
-      <c r="K3" s="17" t="n"/>
-      <c r="L3" s="17" t="n"/>
-      <c r="M3" s="17" t="n"/>
-      <c r="N3" s="17" t="n"/>
-      <c r="O3" s="17" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -642,79 +604,39 @@
           <t>VERDE = al día / con cobro o finalizado | AMARILLO = sin exigibilidad clara | ROJO = mora operativa</t>
         </is>
       </c>
-      <c r="G4" s="17" t="inlineStr">
-        <is>
-          <t>Monto depositado total</t>
-        </is>
-      </c>
-      <c r="H4" s="17" t="n">
-        <v>70588070</v>
-      </c>
-      <c r="I4" s="17" t="n"/>
-      <c r="J4" s="17" t="n"/>
-      <c r="K4" s="17" t="n"/>
-      <c r="L4" s="17" t="n"/>
-      <c r="M4" s="17" t="n"/>
-      <c r="N4" s="17" t="n"/>
-      <c r="O4" s="17" t="n"/>
-    </row>
-    <row r="5">
-      <c r="G5" s="17" t="inlineStr">
-        <is>
-          <t>Monto total a cobrar</t>
-        </is>
-      </c>
-      <c r="H5" s="17" t="n">
-        <v>293652000</v>
-      </c>
-      <c r="I5" s="17" t="n"/>
-      <c r="J5" s="17" t="n"/>
-      <c r="K5" s="17" t="n"/>
-      <c r="L5" s="17" t="n"/>
-      <c r="M5" s="17" t="n"/>
-      <c r="N5" s="17" t="n"/>
-      <c r="O5" s="17" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
+          <t>KPIs principales</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Resumen de estado</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
           <t>Créditos analizados</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n">
+      <c r="B7" s="4" t="n">
         <v>162</v>
       </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>Resumen de estado</t>
-        </is>
-      </c>
-      <c r="G6" s="17" t="inlineStr">
-        <is>
-          <t>Monto cobrado en marzo</t>
-        </is>
-      </c>
-      <c r="H6" s="17" t="n">
-        <v>8740000</v>
-      </c>
-      <c r="I6" s="17" t="n"/>
-      <c r="J6" s="17" t="n"/>
-      <c r="K6" s="17" t="n"/>
-      <c r="L6" s="17" t="n"/>
-      <c r="M6" s="17" t="n"/>
-      <c r="N6" s="17" t="n"/>
-      <c r="O6" s="17" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Monto depositado total</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="n">
-        <v>70588070</v>
-      </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>VERDE</t>
         </is>
@@ -722,30 +644,17 @@
       <c r="E7" s="4" t="n">
         <v>78</v>
       </c>
-      <c r="G7" s="17" t="inlineStr">
-        <is>
-          <t>Mora operativa</t>
-        </is>
-      </c>
-      <c r="H7" s="17" t="n"/>
-      <c r="I7" s="17" t="n"/>
-      <c r="J7" s="17" t="n"/>
-      <c r="K7" s="17" t="n"/>
-      <c r="L7" s="17" t="n"/>
-      <c r="M7" s="17" t="n"/>
-      <c r="N7" s="17" t="n"/>
-      <c r="O7" s="17" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Monto total a cobrar</t>
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Monto depositado total</t>
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>293652000</v>
-      </c>
-      <c r="D8" s="8" t="inlineStr">
+        <v>70588070</v>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>AMARILLO</t>
         </is>
@@ -753,30 +662,17 @@
       <c r="E8" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="G8" s="17" t="inlineStr">
-        <is>
-          <t>% mora operativa</t>
-        </is>
-      </c>
-      <c r="H8" s="17" t="n"/>
-      <c r="I8" s="17" t="n"/>
-      <c r="J8" s="17" t="n"/>
-      <c r="K8" s="17" t="n"/>
-      <c r="L8" s="17" t="n"/>
-      <c r="M8" s="17" t="n"/>
-      <c r="N8" s="17" t="n"/>
-      <c r="O8" s="17" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>Monto cobrado en marzo</t>
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Monto total a cobrar</t>
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>8740000</v>
-      </c>
-      <c r="D9" s="9" t="inlineStr">
+        <v>293652000</v>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
         <is>
           <t>ROJO</t>
         </is>
@@ -784,24 +680,15 @@
       <c r="E9" s="4" t="n">
         <v>59</v>
       </c>
-      <c r="G9" s="17" t="n"/>
-      <c r="H9" s="17" t="n"/>
-      <c r="I9" s="17" t="n"/>
-      <c r="J9" s="17" t="n"/>
-      <c r="K9" s="17" t="n"/>
-      <c r="L9" s="17" t="n"/>
-      <c r="M9" s="17" t="n"/>
-      <c r="N9" s="17" t="n"/>
-      <c r="O9" s="17" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>Clientes con cobro en marzo</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="n">
-        <v>59</v>
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Monto cobrado en marzo</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>8740000</v>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
@@ -811,20 +698,11 @@
       <c r="E10" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="G10" s="17" t="n"/>
-      <c r="H10" s="17" t="n"/>
-      <c r="I10" s="17" t="n"/>
-      <c r="J10" s="17" t="n"/>
-      <c r="K10" s="17" t="n"/>
-      <c r="L10" s="17" t="n"/>
-      <c r="M10" s="17" t="n"/>
-      <c r="N10" s="17" t="n"/>
-      <c r="O10" s="17" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>Mora operativa</t>
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Clientes con cobro en marzo</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
@@ -838,24 +716,15 @@
       <c r="E11" s="4" t="n">
         <v>59</v>
       </c>
-      <c r="G11" s="17" t="n"/>
-      <c r="H11" s="17" t="n"/>
-      <c r="I11" s="17" t="n"/>
-      <c r="J11" s="17" t="n"/>
-      <c r="K11" s="17" t="n"/>
-      <c r="L11" s="17" t="n"/>
-      <c r="M11" s="17" t="n"/>
-      <c r="N11" s="17" t="n"/>
-      <c r="O11" s="17" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>Monto cartera en mora</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="n">
-        <v>106806000</v>
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Mora operativa</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="n">
+        <v>59</v>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
@@ -865,416 +734,65 @@
       <c r="E12" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="G12" s="17" t="n"/>
-      <c r="H12" s="17" t="n"/>
-      <c r="I12" s="17" t="n"/>
-      <c r="J12" s="17" t="n"/>
-      <c r="K12" s="17" t="n"/>
-      <c r="L12" s="17" t="n"/>
-      <c r="M12" s="17" t="n"/>
-      <c r="N12" s="17" t="n"/>
-      <c r="O12" s="17" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Monto cartera en mora</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n">
+        <v>106806000</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>% mora operativa</t>
         </is>
       </c>
-      <c r="B13" s="10" t="n">
+      <c r="B14" s="9" t="n">
         <v>0.3641975308641975</v>
       </c>
-      <c r="G13" s="17" t="n"/>
-      <c r="H13" s="17" t="n"/>
-      <c r="I13" s="17" t="n"/>
-      <c r="J13" s="17" t="n"/>
-      <c r="K13" s="17" t="n"/>
-      <c r="L13" s="17" t="n"/>
-      <c r="M13" s="17" t="n"/>
-      <c r="N13" s="17" t="n"/>
-      <c r="O13" s="17" t="n"/>
-    </row>
-    <row r="14">
-      <c r="G14" s="17" t="n"/>
-      <c r="H14" s="17" t="n"/>
-      <c r="I14" s="17" t="n"/>
-      <c r="J14" s="17" t="n"/>
-      <c r="K14" s="17" t="n"/>
-      <c r="L14" s="17" t="n"/>
-      <c r="M14" s="17" t="n"/>
-      <c r="N14" s="17" t="n"/>
-      <c r="O14" s="17" t="n"/>
     </row>
     <row r="15">
-      <c r="G15" s="17" t="n"/>
-      <c r="H15" s="17" t="n"/>
-      <c r="I15" s="17" t="n"/>
-      <c r="J15" s="17" t="n"/>
-      <c r="K15" s="17" t="n"/>
-      <c r="L15" s="17" t="n"/>
-      <c r="M15" s="17" t="n"/>
-      <c r="N15" s="17" t="n"/>
-      <c r="O15" s="17" t="n"/>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Resumen ejecutivo</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="G16" s="17" t="n"/>
-      <c r="H16" s="17" t="n"/>
-      <c r="I16" s="17" t="n"/>
-      <c r="J16" s="17" t="n"/>
-      <c r="K16" s="17" t="n"/>
-      <c r="L16" s="17" t="n"/>
-      <c r="M16" s="17" t="n"/>
-      <c r="N16" s="17" t="n"/>
-      <c r="O16" s="17" t="n"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Créditos analizados: 162</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="G17" s="17" t="n"/>
-      <c r="H17" s="17" t="n"/>
-      <c r="I17" s="17" t="n"/>
-      <c r="J17" s="17" t="n"/>
-      <c r="K17" s="17" t="n"/>
-      <c r="L17" s="17" t="n"/>
-      <c r="M17" s="17" t="n"/>
-      <c r="N17" s="17" t="n"/>
-      <c r="O17" s="17" t="n"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Clientes con cobro en marzo: 59</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="G18" s="17" t="n"/>
-      <c r="H18" s="17" t="n"/>
-      <c r="I18" s="17" t="n"/>
-      <c r="J18" s="17" t="n"/>
-      <c r="K18" s="17" t="n"/>
-      <c r="L18" s="17" t="n"/>
-      <c r="M18" s="17" t="n"/>
-      <c r="N18" s="17" t="n"/>
-      <c r="O18" s="17" t="n"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Mora operativa: 59</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="G19" s="17" t="n"/>
-      <c r="H19" s="17" t="n"/>
-      <c r="I19" s="17" t="n"/>
-      <c r="J19" s="17" t="n"/>
-      <c r="K19" s="17" t="n"/>
-      <c r="L19" s="17" t="n"/>
-      <c r="M19" s="17" t="n"/>
-      <c r="N19" s="17" t="n"/>
-      <c r="O19" s="17" t="n"/>
-    </row>
-    <row r="20" hidden="1">
-      <c r="A20" s="17" t="inlineStr">
-        <is>
-          <t>Categoría</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Cantidad</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Semáforo</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Cantidad</t>
-        </is>
-      </c>
-      <c r="G20" s="17" t="n"/>
-      <c r="H20" s="17" t="n"/>
-      <c r="I20" s="17" t="n"/>
-      <c r="J20" s="17" t="n"/>
-      <c r="K20" s="17" t="n"/>
-      <c r="L20" s="17" t="n"/>
-      <c r="M20" s="17" t="n"/>
-      <c r="N20" s="17" t="n"/>
-      <c r="O20" s="17" t="n"/>
-    </row>
-    <row r="21" hidden="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Con cobro en marzo</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>8740000</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Verde</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>78</v>
-      </c>
-      <c r="G21" s="17" t="n"/>
-      <c r="H21" s="17" t="n"/>
-      <c r="I21" s="17" t="n"/>
-      <c r="J21" s="17" t="n"/>
-      <c r="K21" s="17" t="n"/>
-      <c r="L21" s="17" t="n"/>
-      <c r="M21" s="17" t="n"/>
-      <c r="N21" s="17" t="n"/>
-      <c r="O21" s="17" t="n"/>
-    </row>
-    <row r="22" hidden="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Cancelados / finalizados</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>23</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Amarillo</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>25</v>
-      </c>
-      <c r="G22" s="17" t="n"/>
-      <c r="H22" s="17" t="n"/>
-      <c r="I22" s="17" t="n"/>
-      <c r="J22" s="17" t="n"/>
-      <c r="K22" s="17" t="n"/>
-      <c r="L22" s="17" t="n"/>
-      <c r="M22" s="17" t="n"/>
-      <c r="N22" s="17" t="n"/>
-      <c r="O22" s="17" t="n"/>
-    </row>
-    <row r="23" hidden="1">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Sin cobro en marzo</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>59</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Rojo</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>59</v>
-      </c>
-      <c r="G23" s="17" t="n"/>
-      <c r="H23" s="17" t="n"/>
-      <c r="I23" s="17" t="n"/>
-      <c r="J23" s="17" t="n"/>
-      <c r="K23" s="17" t="n"/>
-      <c r="L23" s="17" t="n"/>
-      <c r="M23" s="17" t="n"/>
-      <c r="N23" s="17" t="n"/>
-      <c r="O23" s="17" t="n"/>
-    </row>
-    <row r="24" hidden="1">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Sin registro en marzo</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>25</v>
-      </c>
-      <c r="G24" s="17" t="n"/>
-      <c r="H24" s="17" t="n"/>
-      <c r="I24" s="17" t="n"/>
-      <c r="J24" s="17" t="n"/>
-      <c r="K24" s="17" t="n"/>
-      <c r="L24" s="17" t="n"/>
-      <c r="M24" s="17" t="n"/>
-      <c r="N24" s="17" t="n"/>
-      <c r="O24" s="17" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Mora operativa</t>
-        </is>
-      </c>
-      <c r="G25" s="17" t="n"/>
-      <c r="H25" s="17" t="n"/>
-      <c r="I25" s="17" t="n"/>
-      <c r="J25" s="17" t="n"/>
-      <c r="K25" s="17" t="n"/>
-      <c r="L25" s="17" t="n"/>
-      <c r="M25" s="17" t="n"/>
-      <c r="N25" s="17" t="n"/>
-      <c r="O25" s="17" t="n"/>
-    </row>
-    <row r="26">
-      <c r="G26" s="17" t="n"/>
-      <c r="H26" s="17" t="n"/>
-      <c r="I26" s="17" t="n"/>
-      <c r="J26" s="17" t="n"/>
-      <c r="K26" s="17" t="n"/>
-      <c r="L26" s="17" t="n"/>
-      <c r="M26" s="17" t="n"/>
-      <c r="N26" s="17" t="n"/>
-      <c r="O26" s="17" t="n"/>
-    </row>
-    <row r="27">
-      <c r="G27" s="17" t="n"/>
-      <c r="H27" s="17" t="n"/>
-      <c r="I27" s="17" t="n"/>
-      <c r="J27" s="17" t="n"/>
-      <c r="K27" s="17" t="n"/>
-      <c r="L27" s="17" t="n"/>
-      <c r="M27" s="17" t="n"/>
-      <c r="N27" s="17" t="n"/>
-      <c r="O27" s="17" t="n"/>
-    </row>
-    <row r="28">
-      <c r="G28" s="17" t="n"/>
-      <c r="H28" s="17" t="n"/>
-      <c r="I28" s="17" t="n"/>
-      <c r="J28" s="17" t="n"/>
-      <c r="K28" s="17" t="n"/>
-      <c r="L28" s="17" t="n"/>
-      <c r="M28" s="17" t="n"/>
-      <c r="N28" s="17" t="n"/>
-      <c r="O28" s="17" t="n"/>
-    </row>
-    <row r="29">
-      <c r="G29" s="17" t="n"/>
-      <c r="H29" s="17" t="n"/>
-      <c r="I29" s="17" t="n"/>
-      <c r="J29" s="17" t="n"/>
-      <c r="K29" s="17" t="n"/>
-      <c r="L29" s="17" t="n"/>
-      <c r="M29" s="17" t="n"/>
-      <c r="N29" s="17" t="n"/>
-      <c r="O29" s="17" t="n"/>
-    </row>
-    <row r="30">
-      <c r="G30" s="17" t="n"/>
-      <c r="H30" s="17" t="n"/>
-      <c r="I30" s="17" t="n"/>
-      <c r="J30" s="17" t="n"/>
-      <c r="K30" s="17" t="n"/>
-      <c r="L30" s="17" t="n"/>
-      <c r="M30" s="17" t="n"/>
-      <c r="N30" s="17" t="n"/>
-      <c r="O30" s="17" t="n"/>
-    </row>
-    <row r="31">
-      <c r="G31" s="17" t="n"/>
-      <c r="H31" s="17" t="n"/>
-      <c r="I31" s="17" t="n"/>
-      <c r="J31" s="17" t="n"/>
-      <c r="K31" s="17" t="n"/>
-      <c r="L31" s="17" t="n"/>
-      <c r="M31" s="17" t="n"/>
-      <c r="N31" s="17" t="n"/>
-      <c r="O31" s="17" t="n"/>
-    </row>
-    <row r="32">
-      <c r="G32" s="17" t="n"/>
-      <c r="H32" s="17" t="n"/>
-      <c r="I32" s="17" t="n"/>
-      <c r="J32" s="17" t="n"/>
-      <c r="K32" s="17" t="n"/>
-      <c r="L32" s="17" t="n"/>
-      <c r="M32" s="17" t="n"/>
-      <c r="N32" s="17" t="n"/>
-      <c r="O32" s="17" t="n"/>
-    </row>
-    <row r="33">
-      <c r="G33" s="17" t="n"/>
-      <c r="H33" s="17" t="n"/>
-      <c r="I33" s="17" t="n"/>
-      <c r="J33" s="17" t="n"/>
-      <c r="K33" s="17" t="n"/>
-      <c r="L33" s="17" t="n"/>
-      <c r="M33" s="17" t="n"/>
-      <c r="N33" s="17" t="n"/>
-      <c r="O33" s="17" t="n"/>
-    </row>
-    <row r="34">
-      <c r="G34" s="17" t="n"/>
-      <c r="H34" s="17" t="n"/>
-      <c r="I34" s="17" t="n"/>
-      <c r="J34" s="17" t="n"/>
-      <c r="K34" s="17" t="n"/>
-      <c r="L34" s="17" t="n"/>
-      <c r="M34" s="17" t="n"/>
-      <c r="N34" s="17" t="n"/>
-      <c r="O34" s="17" t="n"/>
-    </row>
-    <row r="35">
-      <c r="G35" s="17" t="n"/>
-      <c r="H35" s="17" t="n"/>
-      <c r="I35" s="17" t="n"/>
-      <c r="J35" s="17" t="n"/>
-      <c r="K35" s="17" t="n"/>
-      <c r="L35" s="17" t="n"/>
-      <c r="M35" s="17" t="n"/>
-      <c r="N35" s="17" t="n"/>
-      <c r="O35" s="17" t="n"/>
-    </row>
-    <row r="36">
-      <c r="G36" s="17" t="n"/>
-      <c r="H36" s="17" t="n"/>
-      <c r="I36" s="17" t="n"/>
-      <c r="J36" s="17" t="n"/>
-      <c r="K36" s="17" t="n"/>
-      <c r="L36" s="17" t="n"/>
-      <c r="M36" s="17" t="n"/>
-      <c r="N36" s="17" t="n"/>
-      <c r="O36" s="17" t="n"/>
-    </row>
-    <row r="37">
-      <c r="G37" s="17" t="n"/>
-      <c r="H37" s="17" t="n"/>
-      <c r="I37" s="17" t="n"/>
-      <c r="J37" s="17" t="n"/>
-      <c r="K37" s="17" t="n"/>
-      <c r="L37" s="17" t="n"/>
-      <c r="M37" s="17" t="n"/>
-      <c r="N37" s="17" t="n"/>
-      <c r="O37" s="17" t="n"/>
-    </row>
-    <row r="38">
-      <c r="G38" s="17" t="n"/>
-      <c r="H38" s="17" t="n"/>
-      <c r="I38" s="17" t="n"/>
-      <c r="J38" s="17" t="n"/>
-      <c r="K38" s="17" t="n"/>
-      <c r="L38" s="17" t="n"/>
-      <c r="M38" s="17" t="n"/>
-      <c r="N38" s="17" t="n"/>
-      <c r="O38" s="17" t="n"/>
-    </row>
-    <row r="39">
-      <c r="G39" s="17" t="n"/>
-      <c r="H39" s="17" t="n"/>
-      <c r="I39" s="17" t="n"/>
-      <c r="J39" s="17" t="n"/>
-      <c r="K39" s="17" t="n"/>
-      <c r="L39" s="17" t="n"/>
-      <c r="M39" s="17" t="n"/>
-      <c r="N39" s="17" t="n"/>
-      <c r="O39" s="17" t="n"/>
-    </row>
-    <row r="40">
-      <c r="G40" s="17" t="n"/>
-      <c r="H40" s="17" t="n"/>
-      <c r="I40" s="17" t="n"/>
-      <c r="J40" s="17" t="n"/>
-      <c r="K40" s="17" t="n"/>
-      <c r="L40" s="17" t="n"/>
-      <c r="M40" s="17" t="n"/>
-      <c r="N40" s="17" t="n"/>
-      <c r="O40" s="17" t="n"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Cancelados / finalizados: 23</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:E1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1294,12 +812,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>KPI</t>
         </is>
       </c>
-      <c r="B1" s="11" t="inlineStr">
+      <c r="B1" s="10" t="inlineStr">
         <is>
           <t>Valor</t>
         </is>
@@ -1421,7 +939,7 @@
           <t>% con cobro en marzo</t>
         </is>
       </c>
-      <c r="B13" s="10" t="n">
+      <c r="B13" s="9" t="n">
         <v>0.3641975308641975</v>
       </c>
     </row>
@@ -1431,7 +949,7 @@
           <t>% mora operativa</t>
         </is>
       </c>
-      <c r="B14" s="10" t="n">
+      <c r="B14" s="9" t="n">
         <v>0.3641975308641975</v>
       </c>
     </row>
@@ -1465,59 +983,59 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>Semáforo</t>
         </is>
       </c>
-      <c r="B1" s="12" t="inlineStr">
+      <c r="B1" s="11" t="inlineStr">
         <is>
           <t>Nombre</t>
         </is>
       </c>
-      <c r="C1" s="12" t="inlineStr">
+      <c r="C1" s="11" t="inlineStr">
         <is>
           <t>CUIL</t>
         </is>
       </c>
-      <c r="D1" s="12" t="inlineStr">
+      <c r="D1" s="11" t="inlineStr">
         <is>
           <t>Fecha otorgamiento</t>
         </is>
       </c>
-      <c r="E1" s="12" t="inlineStr">
+      <c r="E1" s="11" t="inlineStr">
         <is>
           <t>Monto depositado</t>
         </is>
       </c>
-      <c r="F1" s="12" t="inlineStr">
+      <c r="F1" s="11" t="inlineStr">
         <is>
           <t>Monto total a cobrar</t>
         </is>
       </c>
-      <c r="G1" s="12" t="inlineStr">
+      <c r="G1" s="11" t="inlineStr">
         <is>
           <t>Cuotas esperables a marzo</t>
         </is>
       </c>
-      <c r="H1" s="12" t="inlineStr">
+      <c r="H1" s="11" t="inlineStr">
         <is>
           <t>Cuotas cobradas en marzo</t>
         </is>
       </c>
-      <c r="I1" s="12" t="inlineStr">
+      <c r="I1" s="11" t="inlineStr">
         <is>
           <t>Estado marzo</t>
         </is>
       </c>
-      <c r="J1" s="12" t="inlineStr">
+      <c r="J1" s="11" t="inlineStr">
         <is>
           <t>Observación marzo</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>ROJO</t>
         </is>
@@ -1532,7 +1050,7 @@
           <t>27185124962</t>
         </is>
       </c>
-      <c r="D2" s="13" t="n">
+      <c r="D2" s="12" t="n">
         <v>45994</v>
       </c>
       <c r="E2" s="6" t="n">
@@ -1559,7 +1077,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>ROJO</t>
         </is>
@@ -1574,7 +1092,7 @@
           <t>27213260249</t>
         </is>
       </c>
-      <c r="D3" s="13" t="n">
+      <c r="D3" s="12" t="n">
         <v>45996</v>
       </c>
       <c r="E3" s="6" t="n">
@@ -1601,7 +1119,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>ROJO</t>
         </is>
@@ -1616,7 +1134,7 @@
           <t>27253267300</t>
         </is>
       </c>
-      <c r="D4" s="13" t="n">
+      <c r="D4" s="12" t="n">
         <v>46000</v>
       </c>
       <c r="E4" s="6" t="n">
@@ -1643,7 +1161,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>ROJO</t>
         </is>
@@ -1658,7 +1176,7 @@
           <t>20281727797</t>
         </is>
       </c>
-      <c r="D5" s="13" t="n">
+      <c r="D5" s="12" t="n">
         <v>46010</v>
       </c>
       <c r="E5" s="6" t="n">
@@ -1685,7 +1203,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>ROJO</t>
         </is>
@@ -1700,7 +1218,7 @@
           <t>27217315528</t>
         </is>
       </c>
-      <c r="D6" s="13" t="n">
+      <c r="D6" s="12" t="n">
         <v>46014</v>
       </c>
       <c r="E6" s="6" t="n">
@@ -1727,7 +1245,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>ROJO</t>
         </is>
@@ -1742,7 +1260,7 @@
           <t>20322822104</t>
         </is>
       </c>
-      <c r="D7" s="13" t="n">
+      <c r="D7" s="12" t="n">
         <v>46021</v>
       </c>
       <c r="E7" s="6" t="n">
@@ -1769,7 +1287,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>ROJO</t>
         </is>
@@ -1784,7 +1302,7 @@
           <t>27386275446</t>
         </is>
       </c>
-      <c r="D8" s="13" t="n">
+      <c r="D8" s="12" t="n">
         <v>46030</v>
       </c>
       <c r="E8" s="6" t="n">
@@ -1811,7 +1329,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>ROJO</t>
         </is>
@@ -1826,7 +1344,7 @@
           <t>27267685431</t>
         </is>
       </c>
-      <c r="D9" s="13" t="n">
+      <c r="D9" s="12" t="n">
         <v>46031</v>
       </c>
       <c r="E9" s="6" t="n">
@@ -1853,7 +1371,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>ROJO</t>
         </is>
@@ -1868,7 +1386,7 @@
           <t>27221876968</t>
         </is>
       </c>
-      <c r="D10" s="13" t="n">
+      <c r="D10" s="12" t="n">
         <v>46035</v>
       </c>
       <c r="E10" s="6" t="n">
@@ -1895,7 +1413,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>ROJO</t>
         </is>
@@ -1910,7 +1428,7 @@
           <t>27243608509</t>
         </is>
       </c>
-      <c r="D11" s="13" t="n">
+      <c r="D11" s="12" t="n">
         <v>46036</v>
       </c>
       <c r="E11" s="6" t="n">
@@ -1937,7 +1455,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="inlineStr">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>ROJO</t>
         </is>
@@ -1952,7 +1470,7 @@
           <t>27239200252</t>
         </is>
       </c>
-      <c r="D12" s="13" t="n">
+      <c r="D12" s="12" t="n">
         <v>46037</v>
       </c>
       <c r="E12" s="6" t="n">
@@ -1979,7 +1497,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>ROJO</t>
         </is>
@@ -1994,7 +1512,7 @@
           <t>20254831825</t>
         </is>
       </c>
-      <c r="D13" s="13" t="n">
+      <c r="D13" s="12" t="n">
         <v>46056</v>
       </c>
       <c r="E13" s="6" t="n">
@@ -2021,7 +1539,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>ROJO</t>
         </is>
@@ -2036,7 +1554,7 @@
           <t>27299721448</t>
         </is>
       </c>
-      <c r="D14" s="13" t="n">
+      <c r="D14" s="12" t="n">
         <v>46057</v>
       </c>
       <c r="E14" s="6" t="n">
@@ -2063,7 +1581,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>ROJO</t>
         </is>
@@ -2078,7 +1596,7 @@
           <t>20102420269</t>
         </is>
       </c>
-      <c r="D15" s="13" t="n">
+      <c r="D15" s="12" t="n">
         <v>46057</v>
       </c>
       <c r="E15" s="6" t="n">
@@ -2105,7 +1623,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
+      <c r="A16" s="8" t="inlineStr">
         <is>
           <t>ROJO</t>
         </is>
@@ -2120,7 +1638,7 @@
           <t>20341295913</t>
         </is>
       </c>
-      <c r="D16" s="13" t="n">
+      <c r="D16" s="12" t="n">
         <v>46073</v>
       </c>
       <c r="E16" s="6" t="n">
@@ -2147,7 +1665,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>ROJO</t>
         </is>
@@ -2162,7 +1680,7 @@
           <t>27266852482</t>
         </is>
       </c>
-      <c r="D17" s="13" t="n">
+      <c r="D17" s="12" t="n">
         <v>46073</v>
       </c>
       <c r="E17" s="6" t="n">
@@ -2189,7 +1707,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="inlineStr">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>ROJO</t>
         </is>
@@ -2204,7 +1722,7 @@
           <t>27279171638</t>
         </is>
       </c>
-      <c r="D18" s="13" t="n">
+      <c r="D18" s="12" t="n">
         <v>46077</v>
       </c>
       <c r="E18" s="6" t="n">
@@ -2231,7 +1749,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="9" t="inlineStr">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>ROJO</t>
         </is>
@@ -2246,7 +1764,7 @@
           <t>27240652604</t>
         </is>
       </c>
-      <c r="D19" s="13" t="n">
+      <c r="D19" s="12" t="n">
         <v>46078</v>
       </c>
       <c r="E19" s="6" t="n">
@@ -2273,7 +1791,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="inlineStr">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>ROJO</t>
         </is>
@@ -2288,7 +1806,7 @@
           <t>27213254044</t>
         </is>
       </c>
-      <c r="D20" s="13" t="n">
+      <c r="D20" s="12" t="n">
         <v>46079</v>
       </c>
       <c r="E20" s="6" t="n">
@@ -2315,7 +1833,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="inlineStr">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>ROJO</t>
         </is>
@@ -2330,7 +1848,7 @@
           <t>27142962042</t>
         </is>
       </c>
-      <c r="D21" s="13" t="n">
+      <c r="D21" s="12" t="n">
         <v>46083</v>
       </c>
       <c r="E21" s="6" t="n">
@@ -2357,7 +1875,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="inlineStr">
+      <c r="A22" s="8" t="inlineStr">
         <is>
           <t>ROJO</t>
         </is>
@@ -2372,7 +1890,7 @@
           <t>27295270166</t>
         </is>
       </c>
-      <c r="D22" s="13" t="n">
+      <c r="D22" s="12" t="n">
         <v>46084</v>
       </c>
       <c r="E22" s="6" t="n">
@@ -2399,7 +1917,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="9" t="inlineStr">
+      <c r="A23" s="8" t="inlineStr">
         <is>
           <t>ROJO</t>
         </is>
@@ -2414,7 +1932,7 @@
           <t>27376373482</t>
         </is>
       </c>
-      <c r="D23" s="13" t="n">
+      <c r="D23" s="12" t="n">
         <v>46084</v>
       </c>
       <c r="E23" s="6" t="n">
@@ -2441,7 +1959,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="9" t="inlineStr">
+      <c r="A24" s="8" t="inlineStr">
         <is>
           <t>ROJO</t>
         </is>
@@ -2456,7 +1974,7 @@
           <t>27200711527</t>
         </is>
       </c>
-      <c r="D24" s="13" t="n">
+      <c r="D24" s="12" t="n">
         <v>46084</v>
       </c>
       <c r="E24" s="6" t="n">
@@ -2483,7 +2001,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="9" t="inlineStr">
+      <c r="A25" s="8" t="inlineStr">
         <is>
           <t>ROJO</t>
         </is>
@@ -2498,7 +2016,7 @@
           <t>27056023971</t>
         </is>
       </c>
-      <c r="D25" s="13" t="n">
+      <c r="D25" s="12" t="n">
         <v>46084</v>
       </c>
       <c r="E25" s="6" t="n">
@@ -2525,7 +2043,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="9" t="inlineStr">
+      <c r="A26" s="8" t="inlineStr">
         <is>
           <t>ROJO</t>
         </is>
@@ -2540,7 +2058,7 @@
           <t>20166671699</t>
         </is>
       </c>
-      <c r="D26" s="13" t="n">
+      <c r="D26" s="12" t="n">
         <v>46084</v>
       </c>
       <c r="E26" s="6" t="n">
@@ -2567,7 +2085,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="9" t="inlineStr">
+      <c r="A27" s="8" t="inlineStr">
         <is>
           <t>ROJO</t>
         </is>
@@ -2582,7 +2100,7 @@
           <t>20179161088</t>
         </is>
       </c>
-      <c r="D27" s="13" t="n">
+      <c r="D27" s="12" t="n">
         <v>46084</v>
       </c>
       <c r="E27" s="6" t="n">
@@ -2609,7 +2127,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="9" t="inlineStr">
+      <c r="A28" s="8" t="inlineStr">
         <is>
           <t>ROJO</t>
         </is>
@@ -2624,7 +2142,7 @@
           <t>27166677578</t>
         </is>
       </c>
-      <c r="D28" s="13" t="n">
+      <c r="D28" s="12" t="n">
         <v>46084</v>
       </c>
       <c r="E28" s="6" t="n">
@@ -2651,7 +2169,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="9" t="inlineStr">
+      <c r="A29" s="8" t="inlineStr">
         <is>
           <t>ROJO</t>
         </is>
@@ -2666,7 +2184,7 @@
           <t>20136885953</t>
         </is>
       </c>
-      <c r="D29" s="13" t="n">
+      <c r="D29" s="12" t="n">
         <v>46085</v>
       </c>
       <c r="E29" s="6" t="n">
@@ -2693,7 +2211,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="9" t="inlineStr">
+      <c r="A30" s="8" t="inlineStr">
         <is>
           <t>ROJO</t>
         </is>
@@ -2708,7 +2226,7 @@
           <t>20121902134</t>
         </is>
       </c>
-      <c r="D30" s="13" t="n">
+      <c r="D30" s="12" t="n">
         <v>46085</v>
       </c>
       <c r="E30" s="6" t="n">
@@ -2735,7 +2253,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="9" t="inlineStr">
+      <c r="A31" s="8" t="inlineStr">
         <is>
           <t>ROJO</t>
         </is>
@@ -2750,7 +2268,7 @@
           <t>20143241263</t>
         </is>
       </c>
-      <c r="D31" s="13" t="n">
+      <c r="D31" s="12" t="n">
         <v>46086</v>
       </c>
       <c r="E31" s="6" t="n">
@@ -2777,7 +2295,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="9" t="inlineStr">
+      <c r="A32" s="8" t="inlineStr">
         <is>
           <t>ROJO</t>
         </is>
@@ -2792,7 +2310,7 @@
           <t>20395410661</t>
         </is>
       </c>
-      <c r="D32" s="13" t="n">
+      <c r="D32" s="12" t="n">
         <v>46087</v>
       </c>
       <c r="E32" s="6" t="n">
@@ -2819,7 +2337,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="9" t="inlineStr">
+      <c r="A33" s="8" t="inlineStr">
         <is>
           <t>ROJO</t>
         </is>
@@ -2834,7 +2352,7 @@
           <t>27322863832</t>
         </is>
       </c>
-      <c r="D33" s="13" t="n">
+      <c r="D33" s="12" t="n">
         <v>46087</v>
       </c>
       <c r="E33" s="6" t="n">
@@ -2861,7 +2379,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="9" t="inlineStr">
+      <c r="A34" s="8" t="inlineStr">
         <is>
           <t>ROJO</t>
         </is>
@@ -2876,7 +2394,7 @@
           <t>27230245113</t>
         </is>
       </c>
-      <c r="D34" s="13" t="n">
+      <c r="D34" s="12" t="n">
         <v>46087</v>
       </c>
       <c r="E34" s="6" t="n">
@@ -2903,7 +2421,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="9" t="inlineStr">
+      <c r="A35" s="8" t="inlineStr">
         <is>
           <t>ROJO</t>
         </is>
@@ -2918,7 +2436,7 @@
           <t>20314508050</t>
         </is>
       </c>
-      <c r="D35" s="13" t="n">
+      <c r="D35" s="12" t="n">
         <v>46090</v>
       </c>
       <c r="E35" s="6" t="n">
@@ -2945,7 +2463,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="9" t="inlineStr">
+      <c r="A36" s="8" t="inlineStr">
         <is>
           <t>ROJO</t>
         </is>
@@ -2960,7 +2478,7 @@
           <t>27135863373</t>
         </is>
       </c>
-      <c r="D36" s="13" t="n">
+      <c r="D36" s="12" t="n">
         <v>46090</v>
       </c>
       <c r="E36" s="6" t="n">
@@ -2987,7 +2505,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="9" t="inlineStr">
+      <c r="A37" s="8" t="inlineStr">
         <is>
           <t>ROJO</t>
         </is>
@@ -3002,7 +2520,7 @@
           <t>27376418540</t>
         </is>
       </c>
-      <c r="D37" s="13" t="n">
+      <c r="D37" s="12" t="n">
         <v>46090</v>
       </c>
       <c r="E37" s="6" t="n">
@@ -3029,7 +2547,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="9" t="inlineStr">
+      <c r="A38" s="8" t="inlineStr">
         <is>
           <t>ROJO</t>
         </is>
@@ -3044,7 +2562,7 @@
           <t>20307195357</t>
         </is>
       </c>
-      <c r="D38" s="13" t="n">
+      <c r="D38" s="12" t="n">
         <v>46091</v>
       </c>
       <c r="E38" s="6" t="n">
@@ -3071,7 +2589,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="9" t="inlineStr">
+      <c r="A39" s="8" t="inlineStr">
         <is>
           <t>ROJO</t>
         </is>
@@ -3086,7 +2604,7 @@
           <t>27269135773</t>
         </is>
       </c>
-      <c r="D39" s="13" t="n">
+      <c r="D39" s="12" t="n">
         <v>46092</v>
       </c>
       <c r="E39" s="6" t="n">
@@ -3113,7 +2631,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="9" t="inlineStr">
+      <c r="A40" s="8" t="inlineStr">
         <is>
           <t>ROJO</t>
         </is>
@@ -3128,7 +2646,7 @@
           <t>27330499287</t>
         </is>
       </c>
-      <c r="D40" s="13" t="n">
+      <c r="D40" s="12" t="n">
         <v>46092</v>
       </c>
       <c r="E40" s="6" t="n">
@@ -3155,7 +2673,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="9" t="inlineStr">
+      <c r="A41" s="8" t="inlineStr">
         <is>
           <t>ROJO</t>
         </is>
@@ -3170,7 +2688,7 @@
           <t>20320834172</t>
         </is>
       </c>
-      <c r="D41" s="13" t="n">
+      <c r="D41" s="12" t="n">
         <v>46092</v>
       </c>
       <c r="E41" s="6" t="n">
@@ -3197,7 +2715,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="9" t="inlineStr">
+      <c r="A42" s="8" t="inlineStr">
         <is>
           <t>ROJO</t>
         </is>
@@ -3212,7 +2730,7 @@
           <t>27209244700</t>
         </is>
       </c>
-      <c r="D42" s="13" t="n">
+      <c r="D42" s="12" t="n">
         <v>46092</v>
       </c>
       <c r="E42" s="6" t="n">
@@ -3239,7 +2757,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="9" t="inlineStr">
+      <c r="A43" s="8" t="inlineStr">
         <is>
           <t>ROJO</t>
         </is>
@@ -3254,7 +2772,7 @@
           <t>20169866717</t>
         </is>
       </c>
-      <c r="D43" s="13" t="n">
+      <c r="D43" s="12" t="n">
         <v>46092</v>
       </c>
       <c r="E43" s="6" t="n">
@@ -3281,7 +2799,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="9" t="inlineStr">
+      <c r="A44" s="8" t="inlineStr">
         <is>
           <t>ROJO</t>
         </is>
@@ -3296,7 +2814,7 @@
           <t>27229501130</t>
         </is>
       </c>
-      <c r="D44" s="13" t="n">
+      <c r="D44" s="12" t="n">
         <v>46092</v>
       </c>
       <c r="E44" s="6" t="n">
@@ -3323,7 +2841,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="9" t="inlineStr">
+      <c r="A45" s="8" t="inlineStr">
         <is>
           <t>ROJO</t>
         </is>
@@ -3338,7 +2856,7 @@
           <t>27275685718</t>
         </is>
       </c>
-      <c r="D45" s="13" t="n">
+      <c r="D45" s="12" t="n">
         <v>46094</v>
       </c>
       <c r="E45" s="6" t="n">
@@ -3365,7 +2883,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="9" t="inlineStr">
+      <c r="A46" s="8" t="inlineStr">
         <is>
           <t>ROJO</t>
         </is>
@@ -3380,7 +2898,7 @@
           <t>20142962226</t>
         </is>
       </c>
-      <c r="D46" s="13" t="n">
+      <c r="D46" s="12" t="n">
         <v>46094</v>
       </c>
       <c r="E46" s="6" t="n">
@@ -3407,7 +2925,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="9" t="inlineStr">
+      <c r="A47" s="8" t="inlineStr">
         <is>
           <t>ROJO</t>
         </is>
@@ -3422,7 +2940,7 @@
           <t>20162763653</t>
         </is>
       </c>
-      <c r="D47" s="13" t="n">
+      <c r="D47" s="12" t="n">
         <v>46094</v>
       </c>
       <c r="E47" s="6" t="n">
@@ -3449,7 +2967,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="9" t="inlineStr">
+      <c r="A48" s="8" t="inlineStr">
         <is>
           <t>ROJO</t>
         </is>
@@ -3464,7 +2982,7 @@
           <t>20289286730</t>
         </is>
       </c>
-      <c r="D48" s="13" t="n">
+      <c r="D48" s="12" t="n">
         <v>46094</v>
       </c>
       <c r="E48" s="6" t="n">
@@ -3491,7 +3009,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="9" t="inlineStr">
+      <c r="A49" s="8" t="inlineStr">
         <is>
           <t>ROJO</t>
         </is>
@@ -3506,7 +3024,7 @@
           <t>27128960320</t>
         </is>
       </c>
-      <c r="D49" s="13" t="n">
+      <c r="D49" s="12" t="n">
         <v>46100</v>
       </c>
       <c r="E49" s="6" t="n">
@@ -3533,7 +3051,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="9" t="inlineStr">
+      <c r="A50" s="8" t="inlineStr">
         <is>
           <t>ROJO</t>
         </is>
@@ -3548,7 +3066,7 @@
           <t>20270530495</t>
         </is>
       </c>
-      <c r="D50" s="13" t="n">
+      <c r="D50" s="12" t="n">
         <v>46100</v>
       </c>
       <c r="E50" s="6" t="n">
@@ -3575,7 +3093,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="9" t="inlineStr">
+      <c r="A51" s="8" t="inlineStr">
         <is>
           <t>ROJO</t>
         </is>
@@ -3590,7 +3108,7 @@
           <t>27405989048</t>
         </is>
       </c>
-      <c r="D51" s="13" t="n">
+      <c r="D51" s="12" t="n">
         <v>46101</v>
       </c>
       <c r="E51" s="6" t="n">
@@ -3617,7 +3135,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="9" t="inlineStr">
+      <c r="A52" s="8" t="inlineStr">
         <is>
           <t>ROJO</t>
         </is>
@@ -3632,7 +3150,7 @@
           <t>27227519121</t>
         </is>
       </c>
-      <c r="D52" s="13" t="n">
+      <c r="D52" s="12" t="n">
         <v>46101</v>
       </c>
       <c r="E52" s="6" t="n">
@@ -3659,7 +3177,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="9" t="inlineStr">
+      <c r="A53" s="8" t="inlineStr">
         <is>
           <t>ROJO</t>
         </is>
@@ -3674,7 +3192,7 @@
           <t>27119820907</t>
         </is>
       </c>
-      <c r="D53" s="13" t="n">
+      <c r="D53" s="12" t="n">
         <v>46101</v>
       </c>
       <c r="E53" s="6" t="n">
@@ -3701,7 +3219,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="9" t="inlineStr">
+      <c r="A54" s="8" t="inlineStr">
         <is>
           <t>ROJO</t>
         </is>
@@ -3716,7 +3234,7 @@
           <t>20326249751</t>
         </is>
       </c>
-      <c r="D54" s="13" t="n">
+      <c r="D54" s="12" t="n">
         <v>46106</v>
       </c>
       <c r="E54" s="6" t="n">
@@ -3743,7 +3261,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="9" t="inlineStr">
+      <c r="A55" s="8" t="inlineStr">
         <is>
           <t>ROJO</t>
         </is>
@@ -3758,7 +3276,7 @@
           <t>27162762767</t>
         </is>
       </c>
-      <c r="D55" s="13" t="n">
+      <c r="D55" s="12" t="n">
         <v>46106</v>
       </c>
       <c r="E55" s="6" t="n">
@@ -3785,7 +3303,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="9" t="inlineStr">
+      <c r="A56" s="8" t="inlineStr">
         <is>
           <t>ROJO</t>
         </is>
@@ -3800,7 +3318,7 @@
           <t>27174282825</t>
         </is>
       </c>
-      <c r="D56" s="13" t="n">
+      <c r="D56" s="12" t="n">
         <v>46106</v>
       </c>
       <c r="E56" s="6" t="n">
@@ -3827,7 +3345,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="9" t="inlineStr">
+      <c r="A57" s="8" t="inlineStr">
         <is>
           <t>ROJO</t>
         </is>
@@ -3842,7 +3360,7 @@
           <t>20292599995</t>
         </is>
       </c>
-      <c r="D57" s="13" t="n">
+      <c r="D57" s="12" t="n">
         <v>46108</v>
       </c>
       <c r="E57" s="6" t="n">
@@ -3869,7 +3387,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="9" t="inlineStr">
+      <c r="A58" s="8" t="inlineStr">
         <is>
           <t>ROJO</t>
         </is>
@@ -3884,7 +3402,7 @@
           <t>23131418639</t>
         </is>
       </c>
-      <c r="D58" s="13" t="n">
+      <c r="D58" s="12" t="n">
         <v>46108</v>
       </c>
       <c r="E58" s="6" t="n">
@@ -3911,7 +3429,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="9" t="inlineStr">
+      <c r="A59" s="8" t="inlineStr">
         <is>
           <t>ROJO</t>
         </is>
@@ -3926,7 +3444,7 @@
           <t>27238542168</t>
         </is>
       </c>
-      <c r="D59" s="13" t="n">
+      <c r="D59" s="12" t="n">
         <v>46112</v>
       </c>
       <c r="E59" s="6" t="n">
@@ -3953,7 +3471,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="9" t="inlineStr">
+      <c r="A60" s="8" t="inlineStr">
         <is>
           <t>ROJO</t>
         </is>
@@ -3968,7 +3486,7 @@
           <t>20140458393</t>
         </is>
       </c>
-      <c r="D60" s="13" t="n">
+      <c r="D60" s="12" t="n">
         <v>46112</v>
       </c>
       <c r="E60" s="6" t="n">
@@ -4030,89 +3548,89 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>Semáforo</t>
         </is>
       </c>
-      <c r="B1" s="12" t="inlineStr">
+      <c r="B1" s="11" t="inlineStr">
         <is>
           <t>Estado marzo</t>
         </is>
       </c>
-      <c r="C1" s="12" t="inlineStr">
+      <c r="C1" s="11" t="inlineStr">
         <is>
           <t>Mora operativa</t>
         </is>
       </c>
-      <c r="D1" s="12" t="inlineStr">
+      <c r="D1" s="11" t="inlineStr">
         <is>
           <t>Fecha otorgamiento</t>
         </is>
       </c>
-      <c r="E1" s="12" t="inlineStr">
+      <c r="E1" s="11" t="inlineStr">
         <is>
           <t>Nombre</t>
         </is>
       </c>
-      <c r="F1" s="12" t="inlineStr">
+      <c r="F1" s="11" t="inlineStr">
         <is>
           <t>CUIL</t>
         </is>
       </c>
-      <c r="G1" s="12" t="inlineStr">
+      <c r="G1" s="11" t="inlineStr">
         <is>
           <t>CBU</t>
         </is>
       </c>
-      <c r="H1" s="12" t="inlineStr">
+      <c r="H1" s="11" t="inlineStr">
         <is>
           <t>Monto depositado</t>
         </is>
       </c>
-      <c r="I1" s="12" t="inlineStr">
+      <c r="I1" s="11" t="inlineStr">
         <is>
           <t>Cantidad cuotas</t>
         </is>
       </c>
-      <c r="J1" s="12" t="inlineStr">
+      <c r="J1" s="11" t="inlineStr">
         <is>
           <t>Monto cuota</t>
         </is>
       </c>
-      <c r="K1" s="12" t="inlineStr">
+      <c r="K1" s="11" t="inlineStr">
         <is>
           <t>Monto total a cobrar</t>
         </is>
       </c>
-      <c r="L1" s="12" t="inlineStr">
+      <c r="L1" s="11" t="inlineStr">
         <is>
           <t>Cuotas esperables a marzo</t>
         </is>
       </c>
-      <c r="M1" s="12" t="inlineStr">
+      <c r="M1" s="11" t="inlineStr">
         <is>
           <t>Cuotas cobradas en marzo</t>
         </is>
       </c>
-      <c r="N1" s="12" t="inlineStr">
+      <c r="N1" s="11" t="inlineStr">
         <is>
           <t>Monto cobrado en marzo</t>
         </is>
       </c>
-      <c r="O1" s="12" t="inlineStr">
+      <c r="O1" s="11" t="inlineStr">
         <is>
           <t>Observación marzo</t>
         </is>
       </c>
-      <c r="P1" s="12" t="inlineStr">
+      <c r="P1" s="11" t="inlineStr">
         <is>
           <t>Historial resumen</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>VERDE</t>
         </is>
@@ -4127,7 +3645,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="D2" s="13" t="n">
+      <c r="D2" s="12" t="n">
         <v>45993</v>
       </c>
       <c r="E2" s="4" t="inlineStr">
@@ -4171,14 +3689,14 @@
           <t>cancelado</t>
         </is>
       </c>
-      <c r="P2" s="14" t="inlineStr">
+      <c r="P2" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: cuotas=1, monto=76000, obs=9na cuota | enero2026: cuotas=1, monto=76000, obs=10ma cuota | febrero2026: cuotas=1, monto=76000, obs=11va cuota | marzo2026: cuotas=1, monto=76000, obs=cancelado</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>ROJO</t>
         </is>
@@ -4193,7 +3711,7 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="D3" s="13" t="n">
+      <c r="D3" s="12" t="n">
         <v>45994</v>
       </c>
       <c r="E3" s="4" t="inlineStr">
@@ -4237,14 +3755,14 @@
           <t>va 4 cuotas reversa</t>
         </is>
       </c>
-      <c r="P3" s="14" t="inlineStr">
+      <c r="P3" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: cuotas=1, monto=76000, obs=3ra cuota | enero2026: cuotas=1, monto=76000, obs=4ta cuota | febrero2026: cuotas=1, monto=76000, obs=5ta cuota | marzo2026: cuotas=0, monto=0, obs=va 4 cuotas reversa</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>VERDE</t>
         </is>
@@ -4259,7 +3777,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="D4" s="13" t="n">
+      <c r="D4" s="12" t="n">
         <v>45995</v>
       </c>
       <c r="E4" s="4" t="inlineStr">
@@ -4303,14 +3821,14 @@
           <t>3ra cuota</t>
         </is>
       </c>
-      <c r="P4" s="14" t="inlineStr">
+      <c r="P4" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: cuotas=0, monto=0, obs=0 cuotas/ descuento febrero | enero2026: cuotas=1, monto=114000, obs=1ra cuota | febrero2026: cuotas=1, monto=114000, obs=2da cuota | marzo2026: cuotas=1, monto=114000, obs=3ra cuota</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>VERDE</t>
         </is>
@@ -4325,7 +3843,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="D5" s="13" t="n">
+      <c r="D5" s="12" t="n">
         <v>45996</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -4369,14 +3887,14 @@
           <t>3ra cuota</t>
         </is>
       </c>
-      <c r="P5" s="14" t="inlineStr">
+      <c r="P5" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: cuotas=0, monto=0, obs=0 cuotas/ descuento febrero | enero2026: cuotas=1, monto=38000, obs=1ra cuota | febrero2026: cuotas=1, monto=38000, obs=2da cuota | marzo2026: cuotas=1, monto=38000, obs=3ra cuota</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>VERDE</t>
         </is>
@@ -4391,7 +3909,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="D6" s="13" t="n">
+      <c r="D6" s="12" t="n">
         <v>45996</v>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -4435,14 +3953,14 @@
           <t>10ma cuota</t>
         </is>
       </c>
-      <c r="P6" s="14" t="inlineStr">
+      <c r="P6" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: cuotas=1, monto=76000, obs=7ma cuota | enero2026: cuotas=1, monto=76000, obs=8va cuota | febrero2026: cuotas=1, monto=76000, obs=9na cuota | marzo2026: cuotas=1, monto=76000, obs=10ma cuota</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>ROJO</t>
         </is>
@@ -4457,7 +3975,7 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="D7" s="13" t="n">
+      <c r="D7" s="12" t="n">
         <v>45996</v>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -4501,14 +4019,14 @@
           <t>fondos insuficientes</t>
         </is>
       </c>
-      <c r="P7" s="14" t="inlineStr">
+      <c r="P7" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: cuotas=0, monto=0, obs=0 cuotas/ descuento febrero | enero2026: cuotas=0, monto=0, obs=fondos insuficientes | febrero2026: cuotas=0, monto=0, obs=fondos insuficientes | marzo2026: cuotas=0, monto=0, obs=fondos insuficientes</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>VERDE</t>
         </is>
@@ -4523,7 +4041,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="D8" s="13" t="n">
+      <c r="D8" s="12" t="n">
         <v>46000</v>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -4567,14 +4085,14 @@
           <t>cancelado</t>
         </is>
       </c>
-      <c r="P8" s="14" t="inlineStr">
+      <c r="P8" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: cuotas=1, monto=450000, obs=10ma cuota | enero2026: cuotas=1, monto=450000, obs=11va cuota | febrero2026: cuotas=1, monto=450000, obs=cancelado | marzo2026: cuotas=0, monto=0, obs=cancelado</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>ROJO</t>
         </is>
@@ -4589,7 +4107,7 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="D9" s="13" t="n">
+      <c r="D9" s="12" t="n">
         <v>46000</v>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -4633,14 +4151,14 @@
           <t>va 2 cuotas fondos insuficientes</t>
         </is>
       </c>
-      <c r="P9" s="14" t="inlineStr">
+      <c r="P9" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: cuotas=0, monto=0, obs=0 cuotas/ descuento febrero | enero2026: cuotas=1, monto=114000, obs=1ra cuota | febrero2026: cuotas=1, monto=114000, obs=2da cuota | marzo2026: cuotas=0, monto=0, obs=va 2 cuotas fondos insuficientes</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>VERDE</t>
         </is>
@@ -4655,7 +4173,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="D10" s="13" t="n">
+      <c r="D10" s="12" t="n">
         <v>46001</v>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -4699,14 +4217,14 @@
           <t>3ra cuota</t>
         </is>
       </c>
-      <c r="P10" s="14" t="inlineStr">
+      <c r="P10" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: cuotas=0, monto=0, obs=0 cuotas/ descuento febrero | enero2026: cuotas=1, monto=190000, obs=1ra cuota | febrero2026: cuotas=1, monto=190000, obs=2da cuota | marzo2026: cuotas=1, monto=190000, obs=3ra cuota</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>VERDE</t>
         </is>
@@ -4721,7 +4239,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="D11" s="13" t="n">
+      <c r="D11" s="12" t="n">
         <v>46001</v>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -4765,14 +4283,14 @@
           <t>3ra cuota</t>
         </is>
       </c>
-      <c r="P11" s="14" t="inlineStr">
+      <c r="P11" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: cuotas=0, monto=0, obs=0 cuotas/ descuento febrero | enero2026: cuotas=1, monto=380000, obs=1ra cuota | febrero2026: cuotas=1, monto=380000, obs=2da cuota | marzo2026: cuotas=1, monto=380000, obs=3ra cuota</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>VERDE</t>
         </is>
@@ -4787,7 +4305,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="D12" s="13" t="n">
+      <c r="D12" s="12" t="n">
         <v>46003</v>
       </c>
       <c r="E12" s="4" t="inlineStr">
@@ -4831,14 +4349,14 @@
           <t>3ra cuota</t>
         </is>
       </c>
-      <c r="P12" s="14" t="inlineStr">
+      <c r="P12" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: cuotas=0, monto=0, obs=0 cuotas/ descuento febrero | enero2026: cuotas=1, monto=76000, obs=1ra cuota | febrero2026: cuotas=1, monto=76000, obs=2da cuota | marzo2026: cuotas=1, monto=76000, obs=3ra cuota</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>VERDE</t>
         </is>
@@ -4853,7 +4371,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="D13" s="13" t="n">
+      <c r="D13" s="12" t="n">
         <v>46003</v>
       </c>
       <c r="E13" s="4" t="inlineStr">
@@ -4897,14 +4415,14 @@
           <t>3ra cuota</t>
         </is>
       </c>
-      <c r="P13" s="14" t="inlineStr">
+      <c r="P13" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: cuotas=0, monto=0, obs=0 cuotas/ descuento febrero | enero2026: cuotas=1, monto=190000, obs=1ra cuota | febrero2026: cuotas=1, monto=190000, obs=2da cuota | marzo2026: cuotas=1, monto=190000, obs=3ra cuota</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>VERDE</t>
         </is>
@@ -4919,7 +4437,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="D14" s="13" t="n">
+      <c r="D14" s="12" t="n">
         <v>46007</v>
       </c>
       <c r="E14" s="4" t="inlineStr">
@@ -4963,14 +4481,14 @@
           <t>9na cuota</t>
         </is>
       </c>
-      <c r="P14" s="14" t="inlineStr">
+      <c r="P14" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: cuotas=1, monto=76000, obs=7ma cuota | enero2026: cuotas=1, monto=76000, obs=8va cuota | febrero2026: cuotas=0, monto=0, obs=va 8 cuotas fondos insuficientes | marzo2026: cuotas=1, monto=76000, obs=9na cuota</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>VERDE</t>
         </is>
@@ -4985,7 +4503,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="D15" s="13" t="n">
+      <c r="D15" s="12" t="n">
         <v>46008</v>
       </c>
       <c r="E15" s="4" t="inlineStr">
@@ -5029,14 +4547,14 @@
           <t>3ra cuota</t>
         </is>
       </c>
-      <c r="P15" s="14" t="inlineStr">
+      <c r="P15" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: cuotas=0, monto=0, obs=0 cuotas/ descuento febrero | enero2026: cuotas=1, monto=114000, obs=1ra cuota | febrero2026: cuotas=1, monto=114000, obs=2da cuota | marzo2026: cuotas=1, monto=114000, obs=3ra cuota</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="inlineStr">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>VERDE</t>
         </is>
@@ -5051,7 +4569,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="D16" s="13" t="n">
+      <c r="D16" s="12" t="n">
         <v>46009</v>
       </c>
       <c r="E16" s="4" t="inlineStr">
@@ -5095,14 +4613,14 @@
           <t>3ra cuota</t>
         </is>
       </c>
-      <c r="P16" s="14" t="inlineStr">
+      <c r="P16" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: cuotas=0, monto=0, obs=0 cuotas/ descuento febrero | enero2026: cuotas=1, monto=38000, obs=1ra cuota | febrero2026: cuotas=1, monto=38000, obs=2da cuota | marzo2026: cuotas=1, monto=38000, obs=3ra cuota</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>ROJO</t>
         </is>
@@ -5117,7 +4635,7 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="D17" s="13" t="n">
+      <c r="D17" s="12" t="n">
         <v>46010</v>
       </c>
       <c r="E17" s="4" t="inlineStr">
@@ -5161,14 +4679,14 @@
           <t>0 cuotas fondos insuficientes</t>
         </is>
       </c>
-      <c r="P17" s="14" t="inlineStr">
+      <c r="P17" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: cuotas=0, monto=0, obs=0 cuotas/ descuento febrero | enero2026: cuotas=0, monto=0, obs=0 cuotas fondos insuficientes | febrero2026: cuotas=0, monto=0, obs=0 cuotas fondos insuficientes | marzo2026: cuotas=0, monto=0, obs=0 cuotas fondos insuficientes</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="inlineStr">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>VERDE</t>
         </is>
@@ -5183,7 +4701,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="D18" s="13" t="n">
+      <c r="D18" s="12" t="n">
         <v>46013</v>
       </c>
       <c r="E18" s="4" t="inlineStr">
@@ -5227,14 +4745,14 @@
           <t>9na cuota</t>
         </is>
       </c>
-      <c r="P18" s="14" t="inlineStr">
+      <c r="P18" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: cuotas=0, monto=0, obs=va 2 cuotas fondos insuficientes | enero2026: cuotas=2, monto=380000, obs=3ra y 4ta cuota | febrero2026: cuotas=4, monto=720000, obs=5ta,6ta,7ma y 8va cuota | marzo2026: cuotas=1, monto=190000, obs=9na cuota</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="7" t="inlineStr">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>VERDE</t>
         </is>
@@ -5249,7 +4767,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="D19" s="13" t="n">
+      <c r="D19" s="12" t="n">
         <v>46013</v>
       </c>
       <c r="E19" s="4" t="inlineStr">
@@ -5293,14 +4811,14 @@
           <t>8va cuota</t>
         </is>
       </c>
-      <c r="P19" s="14" t="inlineStr">
+      <c r="P19" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: cuotas=1, monto=114000, obs=4ta cuota | enero2026: cuotas=1, monto=114000, obs=5ta cuota | febrero2026: cuotas=2, monto=228000, obs=6ta y 7ma cuota | marzo2026: cuotas=1, monto=114000, obs=8va cuota</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="inlineStr">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>ROJO</t>
         </is>
@@ -5315,7 +4833,7 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="D20" s="13" t="n">
+      <c r="D20" s="12" t="n">
         <v>46014</v>
       </c>
       <c r="E20" s="4" t="inlineStr">
@@ -5359,14 +4877,14 @@
           <t>0 cuotas fondos insuficientes</t>
         </is>
       </c>
-      <c r="P20" s="14" t="inlineStr">
+      <c r="P20" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: cuotas=0, monto=0, obs=0 cuotas/ descuento febrero | enero2026: cuotas=0, monto=0, obs=0 cuotas fondos insuficientes | febrero2026: cuotas=0, monto=0, obs=0 cuotas fondos insuficientes | marzo2026: cuotas=0, monto=0, obs=0 cuotas fondos insuficientes</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="7" t="inlineStr">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>VERDE</t>
         </is>
@@ -5381,7 +4899,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="D21" s="13" t="n">
+      <c r="D21" s="12" t="n">
         <v>46014</v>
       </c>
       <c r="E21" s="4" t="inlineStr">
@@ -5425,14 +4943,14 @@
           <t>10ma cuota</t>
         </is>
       </c>
-      <c r="P21" s="14" t="inlineStr">
+      <c r="P21" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: cuotas=1, monto=38000, obs=7ma cuota | enero2026: cuotas=1, monto=38000, obs=8va cuota | febrero2026: cuotas=1, monto=38000, obs=9na cuota | marzo2026: cuotas=1, monto=38000, obs=10ma cuota</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="7" t="inlineStr">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>VERDE</t>
         </is>
@@ -5447,7 +4965,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="D22" s="13" t="n">
+      <c r="D22" s="12" t="n">
         <v>46017</v>
       </c>
       <c r="E22" s="4" t="inlineStr">
@@ -5491,14 +5009,14 @@
           <t>2da cuota</t>
         </is>
       </c>
-      <c r="P22" s="14" t="inlineStr">
+      <c r="P22" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: cuotas=0, monto=0, obs=0 cuotas/ descuento febrero | enero2026: cuotas=0, monto=0, obs=0 cuotas fondos insuficientes | febrero2026: cuotas=1, monto=38000, obs=1ra cuota | marzo2026: cuotas=1, monto=38000, obs=2da cuota</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="7" t="inlineStr">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>VERDE</t>
         </is>
@@ -5513,7 +5031,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="D23" s="13" t="n">
+      <c r="D23" s="12" t="n">
         <v>46020</v>
       </c>
       <c r="E23" s="4" t="inlineStr">
@@ -5557,14 +5075,14 @@
           <t>cancelado</t>
         </is>
       </c>
-      <c r="P23" s="14" t="inlineStr">
+      <c r="P23" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: cuotas=1, monto=225000, obs=10ma cuota y renovacion, se cancelo 450000, se deposito el resto | enero2026: cuotas=1, monto=225000, obs=10ma cuota y renovacion, se cancelo 450000, se deposito el resto | febrero2026: cuotas=0, monto=0, obs=cancelado | marzo2026: cuotas=0, monto=0, obs=cancelado</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="7" t="inlineStr">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>VERDE</t>
         </is>
@@ -5579,7 +5097,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="D24" s="13" t="n">
+      <c r="D24" s="12" t="n">
         <v>46020</v>
       </c>
       <c r="E24" s="4" t="inlineStr">
@@ -5623,14 +5141,14 @@
           <t>2da cuota</t>
         </is>
       </c>
-      <c r="P24" s="14" t="inlineStr">
+      <c r="P24" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: cuotas=0, monto=0, obs=0 cuotas/ descuento febrero | enero2026: cuotas=0, monto=0, obs=va 0 cuotas fondos insuficientes | febrero2026: cuotas=1, monto=190000, obs=1ra cuota | marzo2026: cuotas=1, monto=190000, obs=2da cuota</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="9" t="inlineStr">
+      <c r="A25" s="8" t="inlineStr">
         <is>
           <t>ROJO</t>
         </is>
@@ -5645,7 +5163,7 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="D25" s="13" t="n">
+      <c r="D25" s="12" t="n">
         <v>46021</v>
       </c>
       <c r="E25" s="4" t="inlineStr">
@@ -5689,14 +5207,14 @@
           <t>va 8 cuotas fondos insuficientes</t>
         </is>
       </c>
-      <c r="P25" s="14" t="inlineStr">
+      <c r="P25" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: cuotas=1, monto=76000, obs=6ta cuota | enero2026: cuotas=1, monto=76000, obs=7ma cuota | febrero2026: cuotas=1, monto=76000, obs=8va cuota | marzo2026: cuotas=0, monto=0, obs=va 8 cuotas fondos insuficientes</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="7" t="inlineStr">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>VERDE</t>
         </is>
@@ -5711,7 +5229,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="D26" s="13" t="n">
+      <c r="D26" s="12" t="n">
         <v>46027</v>
       </c>
       <c r="E26" s="4" t="inlineStr">
@@ -5755,14 +5273,14 @@
           <t>7ma cuota</t>
         </is>
       </c>
-      <c r="P26" s="14" t="inlineStr">
+      <c r="P26" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: cuotas=1, monto=114000, obs=4ta cuota | enero2026: cuotas=1, monto=114000, obs=5ta cuota | febrero2026: cuotas=1, monto=114000, obs=6ta cuota | marzo2026: cuotas=1, monto=114000, obs=7ma cuota</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="7" t="inlineStr">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t>VERDE</t>
         </is>
@@ -5777,7 +5295,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="D27" s="13" t="n">
+      <c r="D27" s="12" t="n">
         <v>46027</v>
       </c>
       <c r="E27" s="4" t="inlineStr">
@@ -5821,14 +5339,14 @@
           <t>9na cuota</t>
         </is>
       </c>
-      <c r="P27" s="14" t="inlineStr">
+      <c r="P27" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: cuotas=0, monto=0, obs=va 6 cuotas fondos insuficientes | enero2026: cuotas=1, monto=380000, obs=7ma cuota | febrero2026: cuotas=1, monto=380000, obs=8va cuota | marzo2026: cuotas=1, monto=380000, obs=9na cuota</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="7" t="inlineStr">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t>VERDE</t>
         </is>
@@ -5843,7 +5361,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="D28" s="13" t="n">
+      <c r="D28" s="12" t="n">
         <v>46029</v>
       </c>
       <c r="E28" s="4" t="inlineStr">
@@ -5887,14 +5405,14 @@
           <t>2da cuota</t>
         </is>
       </c>
-      <c r="P28" s="14" t="inlineStr">
+      <c r="P28" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: sin registro | enero2026: cuotas=0, monto=0, obs= | febrero2026: cuotas=1, monto=114000, obs=1ra cuota | marzo2026: cuotas=1, monto=114000, obs=2da cuota</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="9" t="inlineStr">
+      <c r="A29" s="8" t="inlineStr">
         <is>
           <t>ROJO</t>
         </is>
@@ -5909,7 +5427,7 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="D29" s="13" t="n">
+      <c r="D29" s="12" t="n">
         <v>46030</v>
       </c>
       <c r="E29" s="4" t="inlineStr">
@@ -5953,14 +5471,14 @@
           <t>va 1 cuota fondos insuficientes</t>
         </is>
       </c>
-      <c r="P29" s="14" t="inlineStr">
+      <c r="P29" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: sin registro | enero2026: cuotas=0, monto=0, obs= | febrero2026: cuotas=1, monto=38000, obs=1ra cuota | marzo2026: cuotas=0, monto=0, obs=va 1 cuota fondos insuficientes</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="7" t="inlineStr">
+      <c r="A30" s="5" t="inlineStr">
         <is>
           <t>VERDE</t>
         </is>
@@ -5975,7 +5493,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="D30" s="13" t="n">
+      <c r="D30" s="12" t="n">
         <v>46030</v>
       </c>
       <c r="E30" s="4" t="inlineStr">
@@ -6019,14 +5537,14 @@
           <t>2da cuota</t>
         </is>
       </c>
-      <c r="P30" s="14" t="inlineStr">
+      <c r="P30" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: sin registro | enero2026: cuotas=0, monto=0, obs= | febrero2026: cuotas=1, monto=76000, obs=1ra cuota | marzo2026: cuotas=1, monto=76000, obs=2da cuota</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="7" t="inlineStr">
+      <c r="A31" s="5" t="inlineStr">
         <is>
           <t>VERDE</t>
         </is>
@@ -6041,7 +5559,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="D31" s="13" t="n">
+      <c r="D31" s="12" t="n">
         <v>46031</v>
       </c>
       <c r="E31" s="4" t="inlineStr">
@@ -6085,14 +5603,14 @@
           <t>2da cuota</t>
         </is>
       </c>
-      <c r="P31" s="14" t="inlineStr">
+      <c r="P31" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: sin registro | enero2026: cuotas=0, monto=0, obs= | febrero2026: cuotas=1, monto=380000, obs=1ra cuota | marzo2026: cuotas=1, monto=380000, obs=2da cuota</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="9" t="inlineStr">
+      <c r="A32" s="8" t="inlineStr">
         <is>
           <t>ROJO</t>
         </is>
@@ -6107,7 +5625,7 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="D32" s="13" t="n">
+      <c r="D32" s="12" t="n">
         <v>46031</v>
       </c>
       <c r="E32" s="4" t="inlineStr">
@@ -6151,14 +5669,14 @@
           <t>0 cuotas fondos insuficientes</t>
         </is>
       </c>
-      <c r="P32" s="14" t="inlineStr">
+      <c r="P32" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: sin registro | enero2026: cuotas=0, monto=0, obs= | febrero2026: cuotas=0, monto=0, obs=0 cuotas fondos insuficientes | marzo2026: cuotas=0, monto=0, obs=0 cuotas fondos insuficientes</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="7" t="inlineStr">
+      <c r="A33" s="5" t="inlineStr">
         <is>
           <t>VERDE</t>
         </is>
@@ -6173,7 +5691,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="D33" s="13" t="n">
+      <c r="D33" s="12" t="n">
         <v>46035</v>
       </c>
       <c r="E33" s="4" t="inlineStr">
@@ -6217,14 +5735,14 @@
           <t>2da cuota</t>
         </is>
       </c>
-      <c r="P33" s="14" t="inlineStr">
+      <c r="P33" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: sin registro | enero2026: cuotas=0, monto=0, obs= | febrero2026: cuotas=1, monto=190000, obs=1ra cuota | marzo2026: cuotas=1, monto=190000, obs=2da cuota</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="7" t="inlineStr">
+      <c r="A34" s="5" t="inlineStr">
         <is>
           <t>VERDE</t>
         </is>
@@ -6239,7 +5757,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="D34" s="13" t="n">
+      <c r="D34" s="12" t="n">
         <v>46035</v>
       </c>
       <c r="E34" s="4" t="inlineStr">
@@ -6283,14 +5801,14 @@
           <t>2da cuota</t>
         </is>
       </c>
-      <c r="P34" s="14" t="inlineStr">
+      <c r="P34" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: sin registro | enero2026: cuotas=0, monto=0, obs= | febrero2026: cuotas=1, monto=76000, obs=1ra cuota | marzo2026: cuotas=1, monto=76000, obs=2da cuota</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="9" t="inlineStr">
+      <c r="A35" s="8" t="inlineStr">
         <is>
           <t>ROJO</t>
         </is>
@@ -6305,7 +5823,7 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="D35" s="13" t="n">
+      <c r="D35" s="12" t="n">
         <v>46035</v>
       </c>
       <c r="E35" s="4" t="inlineStr">
@@ -6349,14 +5867,14 @@
           <t>va 1 cuota fondos insuficientes</t>
         </is>
       </c>
-      <c r="P35" s="14" t="inlineStr">
+      <c r="P35" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: sin registro | enero2026: cuotas=0, monto=0, obs= | febrero2026: cuotas=1, monto=190000, obs=1ra cuota | marzo2026: cuotas=0, monto=0, obs=va 1 cuota fondos insuficientes</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="7" t="inlineStr">
+      <c r="A36" s="5" t="inlineStr">
         <is>
           <t>VERDE</t>
         </is>
@@ -6371,7 +5889,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="D36" s="13" t="n">
+      <c r="D36" s="12" t="n">
         <v>46035</v>
       </c>
       <c r="E36" s="4" t="inlineStr">
@@ -6415,14 +5933,14 @@
           <t>cancelado</t>
         </is>
       </c>
-      <c r="P36" s="14" t="inlineStr">
+      <c r="P36" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: cuotas=1, monto=450000, obs=10ma cuota | enero2026: cuotas=1, monto=450000, obs=11va cuota | febrero2026: cuotas=1, monto=450000, obs=cancelado | marzo2026: cuotas=0, monto=0, obs=cancelado</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="9" t="inlineStr">
+      <c r="A37" s="8" t="inlineStr">
         <is>
           <t>ROJO</t>
         </is>
@@ -6437,7 +5955,7 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="D37" s="13" t="n">
+      <c r="D37" s="12" t="n">
         <v>46036</v>
       </c>
       <c r="E37" s="4" t="inlineStr">
@@ -6481,14 +5999,14 @@
           <t>0 cuotas fondos insuficientes</t>
         </is>
       </c>
-      <c r="P37" s="14" t="inlineStr">
+      <c r="P37" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: sin registro | enero2026: cuotas=0, monto=0, obs= | febrero2026: cuotas=0, monto=0, obs=0 cuotas fondos insuficientes | marzo2026: cuotas=0, monto=0, obs=0 cuotas fondos insuficientes</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="7" t="inlineStr">
+      <c r="A38" s="5" t="inlineStr">
         <is>
           <t>VERDE</t>
         </is>
@@ -6503,7 +6021,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="D38" s="13" t="n">
+      <c r="D38" s="12" t="n">
         <v>46037</v>
       </c>
       <c r="E38" s="4" t="inlineStr">
@@ -6547,14 +6065,14 @@
           <t>cancelado renovacion</t>
         </is>
       </c>
-      <c r="P38" s="14" t="inlineStr">
+      <c r="P38" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: cuotas=1, monto=342000, obs=5ta, 6ta y 7ma cuota | enero2026: cuotas=1, monto=114000, obs=8va cuota | febrero2026: cuotas=2, monto=228000, obs=9na y 10ma cuota | marzo2026: cuotas=0, monto=0, obs=cancelado renovacion</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="7" t="inlineStr">
+      <c r="A39" s="5" t="inlineStr">
         <is>
           <t>VERDE</t>
         </is>
@@ -6569,7 +6087,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="D39" s="13" t="n">
+      <c r="D39" s="12" t="n">
         <v>46037</v>
       </c>
       <c r="E39" s="4" t="inlineStr">
@@ -6613,14 +6131,14 @@
           <t>8va cuota</t>
         </is>
       </c>
-      <c r="P39" s="14" t="inlineStr">
+      <c r="P39" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: cuotas=1, monto=76000, obs=2da cuota | enero2026: cuotas=1, monto=76000, obs=3ra cuota | febrero2026: cuotas=4, monto=304000, obs=4ta,5ta,6ta y 7ma cuota | marzo2026: cuotas=1, monto=76000, obs=8va cuota</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="9" t="inlineStr">
+      <c r="A40" s="8" t="inlineStr">
         <is>
           <t>ROJO</t>
         </is>
@@ -6635,7 +6153,7 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="D40" s="13" t="n">
+      <c r="D40" s="12" t="n">
         <v>46037</v>
       </c>
       <c r="E40" s="4" t="inlineStr">
@@ -6679,14 +6197,14 @@
           <t>va 1 cuota fondos insuficientes</t>
         </is>
       </c>
-      <c r="P40" s="14" t="inlineStr">
+      <c r="P40" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: sin registro | enero2026: cuotas=0, monto=0, obs= | febrero2026: cuotas=1, monto=76000, obs=1ra cuota | marzo2026: cuotas=0, monto=0, obs=va 1 cuota fondos insuficientes</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="7" t="inlineStr">
+      <c r="A41" s="5" t="inlineStr">
         <is>
           <t>VERDE</t>
         </is>
@@ -6701,7 +6219,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="D41" s="13" t="n">
+      <c r="D41" s="12" t="n">
         <v>46038</v>
       </c>
       <c r="E41" s="4" t="inlineStr">
@@ -6745,14 +6263,14 @@
           <t>2da cuota</t>
         </is>
       </c>
-      <c r="P41" s="14" t="inlineStr">
+      <c r="P41" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: sin registro | enero2026: cuotas=0, monto=0, obs= | febrero2026: cuotas=1, monto=266000, obs=1ra cuota | marzo2026: cuotas=1, monto=266000, obs=2da cuota</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="7" t="inlineStr">
+      <c r="A42" s="5" t="inlineStr">
         <is>
           <t>VERDE</t>
         </is>
@@ -6767,7 +6285,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="D42" s="13" t="n">
+      <c r="D42" s="12" t="n">
         <v>46038</v>
       </c>
       <c r="E42" s="4" t="inlineStr">
@@ -6811,14 +6329,14 @@
           <t>2da cuota</t>
         </is>
       </c>
-      <c r="P42" s="14" t="inlineStr">
+      <c r="P42" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: sin registro | enero2026: cuotas=0, monto=0, obs= | febrero2026: cuotas=1, monto=266000, obs=1ra cuota | marzo2026: cuotas=1, monto=266000, obs=2da cuota</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="7" t="inlineStr">
+      <c r="A43" s="5" t="inlineStr">
         <is>
           <t>VERDE</t>
         </is>
@@ -6833,7 +6351,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="D43" s="13" t="n">
+      <c r="D43" s="12" t="n">
         <v>46041</v>
       </c>
       <c r="E43" s="4" t="inlineStr">
@@ -6877,14 +6395,14 @@
           <t>cancelado</t>
         </is>
       </c>
-      <c r="P43" s="14" t="inlineStr">
+      <c r="P43" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: cuotas=1, monto=380000, obs=9na cuota | enero2026: cuotas=0, monto=0, obs=va 10 cuotas, fondos insuficientes | febrero2026: cuotas=1, monto=380000, obs=11va cuota | marzo2026: cuotas=1, monto=380000, obs=cancelado</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="7" t="inlineStr">
+      <c r="A44" s="5" t="inlineStr">
         <is>
           <t>VERDE</t>
         </is>
@@ -6899,7 +6417,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="D44" s="13" t="n">
+      <c r="D44" s="12" t="n">
         <v>46043</v>
       </c>
       <c r="E44" s="4" t="inlineStr">
@@ -6943,14 +6461,14 @@
           <t>cancelado</t>
         </is>
       </c>
-      <c r="P44" s="14" t="inlineStr">
+      <c r="P44" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: cuotas=1, monto=90000, obs=12va cuota finalizado | enero2026: cuotas=1, monto=90000, obs=12va cuota finalizado | febrero2026: cuotas=0, monto=0, obs=cancelado | marzo2026: cuotas=0, monto=0, obs=cancelado</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="7" t="inlineStr">
+      <c r="A45" s="5" t="inlineStr">
         <is>
           <t>VERDE</t>
         </is>
@@ -6965,7 +6483,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="D45" s="13" t="n">
+      <c r="D45" s="12" t="n">
         <v>46044</v>
       </c>
       <c r="E45" s="4" t="inlineStr">
@@ -7009,14 +6527,14 @@
           <t>1ra cuota</t>
         </is>
       </c>
-      <c r="P45" s="14" t="inlineStr">
+      <c r="P45" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: sin registro | enero2026: cuotas=0, monto=0, obs= | febrero2026: cuotas=0, monto=0, obs=MARZO | marzo2026: cuotas=1, monto=190000, obs=1ra cuota</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="7" t="inlineStr">
+      <c r="A46" s="5" t="inlineStr">
         <is>
           <t>VERDE</t>
         </is>
@@ -7031,7 +6549,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="D46" s="13" t="n">
+      <c r="D46" s="12" t="n">
         <v>46044</v>
       </c>
       <c r="E46" s="4" t="inlineStr">
@@ -7075,14 +6593,14 @@
           <t>7ma cuota</t>
         </is>
       </c>
-      <c r="P46" s="14" t="inlineStr">
+      <c r="P46" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: cuotas=1, monto=38000, obs=4ta cuota | enero2026: cuotas=1, monto=38000, obs=5ta cuota | febrero2026: cuotas=1, monto=38000, obs=6ta cuota | marzo2026: cuotas=1, monto=38000, obs=7ma cuota</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="7" t="inlineStr">
+      <c r="A47" s="5" t="inlineStr">
         <is>
           <t>VERDE</t>
         </is>
@@ -7097,7 +6615,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="D47" s="13" t="n">
+      <c r="D47" s="12" t="n">
         <v>46049</v>
       </c>
       <c r="E47" s="4" t="inlineStr">
@@ -7141,14 +6659,14 @@
           <t>1ra cuota</t>
         </is>
       </c>
-      <c r="P47" s="14" t="inlineStr">
+      <c r="P47" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: sin registro | enero2026: cuotas=0, monto=0, obs= | febrero2026: cuotas=0, monto=0, obs=MARZO | marzo2026: cuotas=1, monto=114000, obs=1ra cuota</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="7" t="inlineStr">
+      <c r="A48" s="5" t="inlineStr">
         <is>
           <t>VERDE</t>
         </is>
@@ -7163,7 +6681,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="D48" s="13" t="n">
+      <c r="D48" s="12" t="n">
         <v>46049</v>
       </c>
       <c r="E48" s="4" t="inlineStr">
@@ -7207,14 +6725,14 @@
           <t>1ra cuota</t>
         </is>
       </c>
-      <c r="P48" s="14" t="inlineStr">
+      <c r="P48" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: sin registro | enero2026: cuotas=0, monto=0, obs= | febrero2026: cuotas=0, monto=0, obs=MARZO | marzo2026: cuotas=1, monto=380000, obs=1ra cuota</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="7" t="inlineStr">
+      <c r="A49" s="5" t="inlineStr">
         <is>
           <t>VERDE</t>
         </is>
@@ -7229,7 +6747,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="D49" s="13" t="n">
+      <c r="D49" s="12" t="n">
         <v>46051</v>
       </c>
       <c r="E49" s="4" t="inlineStr">
@@ -7273,14 +6791,14 @@
           <t>1ra cuota</t>
         </is>
       </c>
-      <c r="P49" s="14" t="inlineStr">
+      <c r="P49" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: sin registro | enero2026: cuotas=0, monto=0, obs= | febrero2026: cuotas=0, monto=0, obs=MARZO | marzo2026: cuotas=1, monto=114000, obs=1ra cuota</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="7" t="inlineStr">
+      <c r="A50" s="5" t="inlineStr">
         <is>
           <t>VERDE</t>
         </is>
@@ -7295,7 +6813,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="D50" s="13" t="n">
+      <c r="D50" s="12" t="n">
         <v>46051</v>
       </c>
       <c r="E50" s="4" t="inlineStr">
@@ -7339,14 +6857,14 @@
           <t>1ra cuota</t>
         </is>
       </c>
-      <c r="P50" s="14" t="inlineStr">
+      <c r="P50" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: sin registro | enero2026: cuotas=0, monto=0, obs= | febrero2026: cuotas=0, monto=0, obs=MARZO | marzo2026: cuotas=1, monto=76000, obs=1ra cuota</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="7" t="inlineStr">
+      <c r="A51" s="5" t="inlineStr">
         <is>
           <t>VERDE</t>
         </is>
@@ -7361,7 +6879,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="D51" s="13" t="n">
+      <c r="D51" s="12" t="n">
         <v>46051</v>
       </c>
       <c r="E51" s="4" t="inlineStr">
@@ -7405,14 +6923,14 @@
           <t>1ra cuota</t>
         </is>
       </c>
-      <c r="P51" s="14" t="inlineStr">
+      <c r="P51" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: sin registro | enero2026: cuotas=0, monto=0, obs= | febrero2026: cuotas=0, monto=0, obs=MARZO | marzo2026: cuotas=1, monto=38000, obs=1ra cuota</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="7" t="inlineStr">
+      <c r="A52" s="5" t="inlineStr">
         <is>
           <t>VERDE</t>
         </is>
@@ -7427,7 +6945,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="D52" s="13" t="n">
+      <c r="D52" s="12" t="n">
         <v>46052</v>
       </c>
       <c r="E52" s="4" t="inlineStr">
@@ -7471,14 +6989,14 @@
           <t>1ra cuota</t>
         </is>
       </c>
-      <c r="P52" s="14" t="inlineStr">
+      <c r="P52" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: sin registro | enero2026: cuotas=0, monto=0, obs= | febrero2026: cuotas=0, monto=0, obs=MARZO | marzo2026: cuotas=1, monto=380000, obs=1ra cuota</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="7" t="inlineStr">
+      <c r="A53" s="5" t="inlineStr">
         <is>
           <t>VERDE</t>
         </is>
@@ -7493,7 +7011,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="D53" s="13" t="n">
+      <c r="D53" s="12" t="n">
         <v>46052</v>
       </c>
       <c r="E53" s="4" t="inlineStr">
@@ -7537,14 +7055,14 @@
           <t>1ra cuota</t>
         </is>
       </c>
-      <c r="P53" s="14" t="inlineStr">
+      <c r="P53" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: sin registro | enero2026: cuotas=0, monto=0, obs= | febrero2026: cuotas=0, monto=0, obs=MARZO | marzo2026: cuotas=1, monto=190000, obs=1ra cuota</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="9" t="inlineStr">
+      <c r="A54" s="8" t="inlineStr">
         <is>
           <t>ROJO</t>
         </is>
@@ -7559,7 +7077,7 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="D54" s="13" t="n">
+      <c r="D54" s="12" t="n">
         <v>46056</v>
       </c>
       <c r="E54" s="4" t="inlineStr">
@@ -7603,14 +7121,14 @@
           <t>va 5 cuotas reversa</t>
         </is>
       </c>
-      <c r="P54" s="14" t="inlineStr">
+      <c r="P54" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: cuotas=1, monto=76000, obs=4ta cuota | enero2026: cuotas=1, monto=76000, obs=5ta cuota | febrero2026: cuotas=1, monto=76000, obs=6ta cuota | marzo2026: cuotas=0, monto=0, obs=va 5 cuotas reversa</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="9" t="inlineStr">
+      <c r="A55" s="8" t="inlineStr">
         <is>
           <t>ROJO</t>
         </is>
@@ -7625,7 +7143,7 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="D55" s="13" t="n">
+      <c r="D55" s="12" t="n">
         <v>46057</v>
       </c>
       <c r="E55" s="4" t="inlineStr">
@@ -7669,14 +7187,14 @@
           <t>va 0 cuotas fondos insuficientes</t>
         </is>
       </c>
-      <c r="P55" s="14" t="inlineStr">
+      <c r="P55" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: sin registro | enero2026: sin registro | febrero2026: cuotas=0, monto=0, obs=MARZO | marzo2026: cuotas=0, monto=0, obs=va 0 cuotas fondos insuficientes</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="9" t="inlineStr">
+      <c r="A56" s="8" t="inlineStr">
         <is>
           <t>ROJO</t>
         </is>
@@ -7691,7 +7209,7 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="D56" s="13" t="n">
+      <c r="D56" s="12" t="n">
         <v>46057</v>
       </c>
       <c r="E56" s="4" t="inlineStr">
@@ -7735,14 +7253,14 @@
           <t>0 cuotas fondos insuficientes</t>
         </is>
       </c>
-      <c r="P56" s="14" t="inlineStr">
+      <c r="P56" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: sin registro | enero2026: sin registro | febrero2026: cuotas=0, monto=0, obs=MARZO | marzo2026: cuotas=0, monto=0, obs=0 cuotas fondos insuficientes</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="7" t="inlineStr">
+      <c r="A57" s="5" t="inlineStr">
         <is>
           <t>VERDE</t>
         </is>
@@ -7757,7 +7275,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="D57" s="13" t="n">
+      <c r="D57" s="12" t="n">
         <v>46063</v>
       </c>
       <c r="E57" s="4" t="inlineStr">
@@ -7801,14 +7319,14 @@
           <t>cancelado renovacion</t>
         </is>
       </c>
-      <c r="P57" s="14" t="inlineStr">
+      <c r="P57" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: cuotas=3, monto=342000, obs=5ta.6ta y 7ma cuota | enero2026: cuotas=1, monto=114000, obs=8va cuota | febrero2026: cuotas=1, monto=114000, obs=9na cuota | marzo2026: cuotas=0, monto=0, obs=cancelado renovacion</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="7" t="inlineStr">
+      <c r="A58" s="5" t="inlineStr">
         <is>
           <t>VERDE</t>
         </is>
@@ -7823,7 +7341,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="D58" s="13" t="n">
+      <c r="D58" s="12" t="n">
         <v>46064</v>
       </c>
       <c r="E58" s="4" t="inlineStr">
@@ -7867,14 +7385,14 @@
           <t>cancelado</t>
         </is>
       </c>
-      <c r="P58" s="14" t="inlineStr">
+      <c r="P58" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: cuotas=0, monto=0, obs=12va cuota finalizado | enero2026: cuotas=0, monto=0, obs=12va cuota finalizado | febrero2026: cuotas=0, monto=0, obs=cancelado | marzo2026: cuotas=0, monto=0, obs=cancelado</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="7" t="inlineStr">
+      <c r="A59" s="5" t="inlineStr">
         <is>
           <t>VERDE</t>
         </is>
@@ -7889,7 +7407,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="D59" s="13" t="n">
+      <c r="D59" s="12" t="n">
         <v>46065</v>
       </c>
       <c r="E59" s="4" t="inlineStr">
@@ -7933,14 +7451,14 @@
           <t>1ra cuota</t>
         </is>
       </c>
-      <c r="P59" s="14" t="inlineStr">
+      <c r="P59" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: sin registro | enero2026: sin registro | febrero2026: cuotas=0, monto=0, obs=MARZO | marzo2026: cuotas=1, monto=114000, obs=1ra cuota</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="7" t="inlineStr">
+      <c r="A60" s="5" t="inlineStr">
         <is>
           <t>VERDE</t>
         </is>
@@ -7955,7 +7473,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="D60" s="13" t="n">
+      <c r="D60" s="12" t="n">
         <v>46066</v>
       </c>
       <c r="E60" s="4" t="inlineStr">
@@ -7999,14 +7517,14 @@
           <t>1ra cuota</t>
         </is>
       </c>
-      <c r="P60" s="14" t="inlineStr">
+      <c r="P60" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: sin registro | enero2026: sin registro | febrero2026: cuotas=0, monto=0, obs=MARZO | marzo2026: cuotas=1, monto=380000, obs=1ra cuota</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="7" t="inlineStr">
+      <c r="A61" s="5" t="inlineStr">
         <is>
           <t>VERDE</t>
         </is>
@@ -8021,7 +7539,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="D61" s="13" t="n">
+      <c r="D61" s="12" t="n">
         <v>46071</v>
       </c>
       <c r="E61" s="4" t="inlineStr">
@@ -8065,14 +7583,14 @@
           <t>1ra cuota</t>
         </is>
       </c>
-      <c r="P61" s="14" t="inlineStr">
+      <c r="P61" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: sin registro | enero2026: sin registro | febrero2026: cuotas=0, monto=0, obs=MARZO | marzo2026: cuotas=1, monto=76000, obs=1ra cuota</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="9" t="inlineStr">
+      <c r="A62" s="8" t="inlineStr">
         <is>
           <t>ROJO</t>
         </is>
@@ -8087,7 +7605,7 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="D62" s="13" t="n">
+      <c r="D62" s="12" t="n">
         <v>46073</v>
       </c>
       <c r="E62" s="4" t="inlineStr">
@@ -8131,14 +7649,14 @@
           <t>ABRIL</t>
         </is>
       </c>
-      <c r="P62" s="14" t="inlineStr">
+      <c r="P62" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: sin registro | enero2026: sin registro | febrero2026: cuotas=0, monto=0, obs=MARZO | marzo2026: cuotas=0, monto=0, obs=ABRIL</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="7" t="inlineStr">
+      <c r="A63" s="5" t="inlineStr">
         <is>
           <t>VERDE</t>
         </is>
@@ -8153,7 +7671,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="D63" s="13" t="n">
+      <c r="D63" s="12" t="n">
         <v>46073</v>
       </c>
       <c r="E63" s="4" t="inlineStr">
@@ -8197,14 +7715,14 @@
           <t>5ta cuota</t>
         </is>
       </c>
-      <c r="P63" s="14" t="inlineStr">
+      <c r="P63" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: cuotas=1, monto=76000, obs=1ra cuota | enero2026: cuotas=1, monto=76000, obs=2da cuota | febrero2026: cuotas=2, monto=152000, obs=3ra y 4ta cuota | marzo2026: cuotas=1, monto=76000, obs=5ta cuota</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="9" t="inlineStr">
+      <c r="A64" s="8" t="inlineStr">
         <is>
           <t>ROJO</t>
         </is>
@@ -8219,7 +7737,7 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="D64" s="13" t="n">
+      <c r="D64" s="12" t="n">
         <v>46073</v>
       </c>
       <c r="E64" s="4" t="inlineStr">
@@ -8263,14 +7781,14 @@
           <t>ABRIL</t>
         </is>
       </c>
-      <c r="P64" s="14" t="inlineStr">
+      <c r="P64" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: sin registro | enero2026: sin registro | febrero2026: cuotas=0, monto=0, obs=MARZO | marzo2026: cuotas=0, monto=0, obs=ABRIL</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="7" t="inlineStr">
+      <c r="A65" s="5" t="inlineStr">
         <is>
           <t>VERDE</t>
         </is>
@@ -8285,7 +7803,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="D65" s="13" t="n">
+      <c r="D65" s="12" t="n">
         <v>46073</v>
       </c>
       <c r="E65" s="4" t="inlineStr">
@@ -8329,14 +7847,14 @@
           <t>8va cuota</t>
         </is>
       </c>
-      <c r="P65" s="14" t="inlineStr">
+      <c r="P65" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: cuotas=1, monto=190000, obs=5ta cuota | enero2026: cuotas=1, monto=190000, obs=6ta cuota | febrero2026: cuotas=1, monto=190000, obs=7ma cuota | marzo2026: cuotas=1, monto=190000, obs=8va cuota</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="7" t="inlineStr">
+      <c r="A66" s="5" t="inlineStr">
         <is>
           <t>VERDE</t>
         </is>
@@ -8351,7 +7869,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="D66" s="13" t="n">
+      <c r="D66" s="12" t="n">
         <v>46076</v>
       </c>
       <c r="E66" s="4" t="inlineStr">
@@ -8395,14 +7913,14 @@
           <t>2da cuota</t>
         </is>
       </c>
-      <c r="P66" s="14" t="inlineStr">
+      <c r="P66" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: cuotas=0, monto=0, obs=0 cuotas/ descuento febrero | enero2026: cuotas=0, monto=0, obs=0 cuotas fondos insuficientes | febrero2026: cuotas=1, monto=38000, obs=1ra cuota | marzo2026: cuotas=1, monto=38000, obs=2da cuota</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="7" t="inlineStr">
+      <c r="A67" s="5" t="inlineStr">
         <is>
           <t>VERDE</t>
         </is>
@@ -8417,7 +7935,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="D67" s="13" t="n">
+      <c r="D67" s="12" t="n">
         <v>46076</v>
       </c>
       <c r="E67" s="4" t="inlineStr">
@@ -8461,14 +7979,14 @@
           <t>4ta cuota</t>
         </is>
       </c>
-      <c r="P67" s="14" t="inlineStr">
+      <c r="P67" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: cuotas=1, monto=76000, obs=1ra cuota | enero2026: cuotas=0, monto=0, obs=va 2 cuotas fondos insuficientes | febrero2026: cuotas=1, monto=76000, obs=3ra cuota | marzo2026: cuotas=1, monto=76000, obs=4ta cuota</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="9" t="inlineStr">
+      <c r="A68" s="8" t="inlineStr">
         <is>
           <t>ROJO</t>
         </is>
@@ -8483,7 +8001,7 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="D68" s="13" t="n">
+      <c r="D68" s="12" t="n">
         <v>46077</v>
       </c>
       <c r="E68" s="4" t="inlineStr">
@@ -8527,14 +8045,14 @@
           <t>ABRIL</t>
         </is>
       </c>
-      <c r="P68" s="14" t="inlineStr">
+      <c r="P68" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: sin registro | enero2026: sin registro | febrero2026: cuotas=0, monto=0, obs=MARZO | marzo2026: cuotas=0, monto=0, obs=ABRIL</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="9" t="inlineStr">
+      <c r="A69" s="8" t="inlineStr">
         <is>
           <t>ROJO</t>
         </is>
@@ -8549,7 +8067,7 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="D69" s="13" t="n">
+      <c r="D69" s="12" t="n">
         <v>46078</v>
       </c>
       <c r="E69" s="4" t="inlineStr">
@@ -8593,14 +8111,14 @@
           <t>ABRIL</t>
         </is>
       </c>
-      <c r="P69" s="14" t="inlineStr">
+      <c r="P69" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: sin registro | enero2026: sin registro | febrero2026: cuotas=0, monto=0, obs=MARZO | marzo2026: cuotas=0, monto=0, obs=ABRIL</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="9" t="inlineStr">
+      <c r="A70" s="8" t="inlineStr">
         <is>
           <t>ROJO</t>
         </is>
@@ -8615,7 +8133,7 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="D70" s="13" t="n">
+      <c r="D70" s="12" t="n">
         <v>46079</v>
       </c>
       <c r="E70" s="4" t="inlineStr">
@@ -8659,14 +8177,14 @@
           <t>ABRIL</t>
         </is>
       </c>
-      <c r="P70" s="14" t="inlineStr">
+      <c r="P70" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: sin registro | enero2026: sin registro | febrero2026: cuotas=0, monto=0, obs=MARZO | marzo2026: cuotas=0, monto=0, obs=ABRIL</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="7" t="inlineStr">
+      <c r="A71" s="5" t="inlineStr">
         <is>
           <t>VERDE</t>
         </is>
@@ -8681,7 +8199,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="D71" s="13" t="n">
+      <c r="D71" s="12" t="n">
         <v>46080</v>
       </c>
       <c r="E71" s="4" t="inlineStr">
@@ -8725,14 +8243,14 @@
           <t>cancelado</t>
         </is>
       </c>
-      <c r="P71" s="14" t="inlineStr">
+      <c r="P71" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: cuotas=1, monto=45000, obs=9na cuota | enero2026: cuotas=1, monto=45000, obs=10ma cuota | febrero2026: cuotas=2, monto=90000, obs=cancelado | marzo2026: cuotas=0, monto=0, obs=cancelado</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="9" t="inlineStr">
+      <c r="A72" s="8" t="inlineStr">
         <is>
           <t>ROJO</t>
         </is>
@@ -8747,7 +8265,7 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="D72" s="13" t="n">
+      <c r="D72" s="12" t="n">
         <v>46083</v>
       </c>
       <c r="E72" s="4" t="inlineStr">
@@ -8791,14 +8309,14 @@
           <t>ABRIL</t>
         </is>
       </c>
-      <c r="P72" s="14" t="inlineStr">
+      <c r="P72" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: cuotas=1, monto=76000, obs=4ta cuota | enero2026: cuotas=0, monto=0, obs=va 4 cuotas fondos insuficientes | febrero2026: cuotas=2, monto=152000, obs=5ta y 6ta cuota | marzo2026: cuotas=0, monto=0, obs=ABRIL</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="9" t="inlineStr">
+      <c r="A73" s="8" t="inlineStr">
         <is>
           <t>ROJO</t>
         </is>
@@ -8813,7 +8331,7 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="D73" s="13" t="n">
+      <c r="D73" s="12" t="n">
         <v>46084</v>
       </c>
       <c r="E73" s="4" t="inlineStr">
@@ -8857,14 +8375,14 @@
           <t>ABRIL</t>
         </is>
       </c>
-      <c r="P73" s="14" t="inlineStr">
+      <c r="P73" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: sin registro | enero2026: sin registro | febrero2026: sin registro | marzo2026: cuotas=0, monto=0, obs=ABRIL</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="9" t="inlineStr">
+      <c r="A74" s="8" t="inlineStr">
         <is>
           <t>ROJO</t>
         </is>
@@ -8879,7 +8397,7 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="D74" s="13" t="n">
+      <c r="D74" s="12" t="n">
         <v>46084</v>
       </c>
       <c r="E74" s="4" t="inlineStr">
@@ -8923,14 +8441,14 @@
           <t>va 7 cuotas fondos insuficientes</t>
         </is>
       </c>
-      <c r="P74" s="14" t="inlineStr">
+      <c r="P74" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: cuotas=1, monto=190000, obs=5ta cuota | enero2026: cuotas=1, monto=190000, obs=6ta cuota | febrero2026: cuotas=1, monto=190000, obs=7ma cuota | marzo2026: cuotas=0, monto=0, obs=va 7 cuotas fondos insuficientes</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="9" t="inlineStr">
+      <c r="A75" s="8" t="inlineStr">
         <is>
           <t>ROJO</t>
         </is>
@@ -8945,7 +8463,7 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="D75" s="13" t="n">
+      <c r="D75" s="12" t="n">
         <v>46084</v>
       </c>
       <c r="E75" s="4" t="inlineStr">
@@ -8989,14 +8507,14 @@
           <t>ABRIL</t>
         </is>
       </c>
-      <c r="P75" s="14" t="inlineStr">
+      <c r="P75" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: sin registro | enero2026: sin registro | febrero2026: sin registro | marzo2026: cuotas=0, monto=0, obs=ABRIL</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="9" t="inlineStr">
+      <c r="A76" s="8" t="inlineStr">
         <is>
           <t>ROJO</t>
         </is>
@@ -9011,7 +8529,7 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="D76" s="13" t="n">
+      <c r="D76" s="12" t="n">
         <v>46084</v>
       </c>
       <c r="E76" s="4" t="inlineStr">
@@ -9055,14 +8573,14 @@
           <t>ABRIL</t>
         </is>
       </c>
-      <c r="P76" s="14" t="inlineStr">
+      <c r="P76" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: sin registro | enero2026: sin registro | febrero2026: sin registro | marzo2026: cuotas=0, monto=0, obs=ABRIL</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="9" t="inlineStr">
+      <c r="A77" s="8" t="inlineStr">
         <is>
           <t>ROJO</t>
         </is>
@@ -9077,7 +8595,7 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="D77" s="13" t="n">
+      <c r="D77" s="12" t="n">
         <v>46084</v>
       </c>
       <c r="E77" s="4" t="inlineStr">
@@ -9121,14 +8639,14 @@
           <t>ABRIL</t>
         </is>
       </c>
-      <c r="P77" s="14" t="inlineStr">
+      <c r="P77" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: sin registro | enero2026: sin registro | febrero2026: sin registro | marzo2026: cuotas=0, monto=0, obs=ABRIL</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="9" t="inlineStr">
+      <c r="A78" s="8" t="inlineStr">
         <is>
           <t>ROJO</t>
         </is>
@@ -9143,7 +8661,7 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="D78" s="13" t="n">
+      <c r="D78" s="12" t="n">
         <v>46084</v>
       </c>
       <c r="E78" s="4" t="inlineStr">
@@ -9187,14 +8705,14 @@
           <t>ABRIL</t>
         </is>
       </c>
-      <c r="P78" s="14" t="inlineStr">
+      <c r="P78" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: sin registro | enero2026: sin registro | febrero2026: sin registro | marzo2026: cuotas=0, monto=0, obs=ABRIL</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="9" t="inlineStr">
+      <c r="A79" s="8" t="inlineStr">
         <is>
           <t>ROJO</t>
         </is>
@@ -9209,7 +8727,7 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="D79" s="13" t="n">
+      <c r="D79" s="12" t="n">
         <v>46084</v>
       </c>
       <c r="E79" s="4" t="inlineStr">
@@ -9253,14 +8771,14 @@
           <t>ABRIL</t>
         </is>
       </c>
-      <c r="P79" s="14" t="inlineStr">
+      <c r="P79" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: sin registro | enero2026: sin registro | febrero2026: sin registro | marzo2026: cuotas=0, monto=0, obs=ABRIL</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="7" t="inlineStr">
+      <c r="A80" s="5" t="inlineStr">
         <is>
           <t>VERDE</t>
         </is>
@@ -9275,7 +8793,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="D80" s="13" t="n">
+      <c r="D80" s="12" t="n">
         <v>46085</v>
       </c>
       <c r="E80" s="4" t="inlineStr">
@@ -9319,14 +8837,14 @@
           <t>cancelado</t>
         </is>
       </c>
-      <c r="P80" s="14" t="inlineStr">
+      <c r="P80" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: cuotas=1, monto=76000, obs=9na cuota | enero2026: cuotas=1, monto=76000, obs=10ma cuota | febrero2026: cuotas=1, monto=76000, obs=11va cuota | marzo2026: cuotas=1, monto=76000, obs=cancelado</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="9" t="inlineStr">
+      <c r="A81" s="8" t="inlineStr">
         <is>
           <t>ROJO</t>
         </is>
@@ -9341,7 +8859,7 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="D81" s="13" t="n">
+      <c r="D81" s="12" t="n">
         <v>46085</v>
       </c>
       <c r="E81" s="4" t="inlineStr">
@@ -9385,14 +8903,14 @@
           <t>ABRIL</t>
         </is>
       </c>
-      <c r="P81" s="14" t="inlineStr">
+      <c r="P81" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: sin registro | enero2026: sin registro | febrero2026: sin registro | marzo2026: cuotas=0, monto=0, obs=ABRIL</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="9" t="inlineStr">
+      <c r="A82" s="8" t="inlineStr">
         <is>
           <t>ROJO</t>
         </is>
@@ -9407,7 +8925,7 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="D82" s="13" t="n">
+      <c r="D82" s="12" t="n">
         <v>46085</v>
       </c>
       <c r="E82" s="4" t="inlineStr">
@@ -9451,14 +8969,14 @@
           <t>ABRIL</t>
         </is>
       </c>
-      <c r="P82" s="14" t="inlineStr">
+      <c r="P82" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: sin registro | enero2026: sin registro | febrero2026: sin registro | marzo2026: cuotas=0, monto=0, obs=ABRIL</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="9" t="inlineStr">
+      <c r="A83" s="8" t="inlineStr">
         <is>
           <t>ROJO</t>
         </is>
@@ -9473,7 +8991,7 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="D83" s="13" t="n">
+      <c r="D83" s="12" t="n">
         <v>46086</v>
       </c>
       <c r="E83" s="4" t="inlineStr">
@@ -9517,14 +9035,14 @@
           <t>ABRIL</t>
         </is>
       </c>
-      <c r="P83" s="14" t="inlineStr">
+      <c r="P83" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: sin registro | enero2026: sin registro | febrero2026: sin registro | marzo2026: cuotas=0, monto=0, obs=ABRIL</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="7" t="inlineStr">
+      <c r="A84" s="5" t="inlineStr">
         <is>
           <t>VERDE</t>
         </is>
@@ -9539,7 +9057,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="D84" s="13" t="n">
+      <c r="D84" s="12" t="n">
         <v>46086</v>
       </c>
       <c r="E84" s="4" t="inlineStr">
@@ -9583,14 +9101,14 @@
           <t>cancelado renovacion</t>
         </is>
       </c>
-      <c r="P84" s="14" t="inlineStr">
+      <c r="P84" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: cuotas=0, monto=0, obs=va 5 cuotas fondos insuficientes | enero2026: cuotas=1, monto=38000, obs=6ta cuota | febrero2026: cuotas=2, monto=76000, obs=7ma y 8va cuota | marzo2026: cuotas=0, monto=0, obs=cancelado renovacion</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="7" t="inlineStr">
+      <c r="A85" s="5" t="inlineStr">
         <is>
           <t>VERDE</t>
         </is>
@@ -9605,7 +9123,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="D85" s="13" t="n">
+      <c r="D85" s="12" t="n">
         <v>46087</v>
       </c>
       <c r="E85" s="4" t="inlineStr">
@@ -9649,14 +9167,14 @@
           <t>cancelado renovacion</t>
         </is>
       </c>
-      <c r="P85" s="14" t="inlineStr">
+      <c r="P85" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: cuotas=1, monto=38000, obs=8va cuota | enero2026: cuotas=1, monto=38000, obs=9na cuota | febrero2026: cuotas=1, monto=38000, obs=10ma cuota | marzo2026: cuotas=0, monto=0, obs=cancelado renovacion</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="7" t="inlineStr">
+      <c r="A86" s="5" t="inlineStr">
         <is>
           <t>VERDE</t>
         </is>
@@ -9671,7 +9189,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="D86" s="13" t="n">
+      <c r="D86" s="12" t="n">
         <v>46087</v>
       </c>
       <c r="E86" s="4" t="inlineStr">
@@ -9715,14 +9233,14 @@
           <t>4ta cuota</t>
         </is>
       </c>
-      <c r="P86" s="14" t="inlineStr">
+      <c r="P86" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: cuotas=1, monto=76000, obs=1ra cuota | enero2026: cuotas=0, monto=0, obs=va 1 cuota fondos insuficientes | febrero2026: cuotas=2, monto=152000, obs=2da y 3ra cuota | marzo2026: cuotas=1, monto=76000, obs=4ta cuota</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="9" t="inlineStr">
+      <c r="A87" s="8" t="inlineStr">
         <is>
           <t>ROJO</t>
         </is>
@@ -9737,7 +9255,7 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="D87" s="13" t="n">
+      <c r="D87" s="12" t="n">
         <v>46087</v>
       </c>
       <c r="E87" s="4" t="inlineStr">
@@ -9781,14 +9299,14 @@
           <t>ABRIL</t>
         </is>
       </c>
-      <c r="P87" s="14" t="inlineStr">
+      <c r="P87" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: sin registro | enero2026: sin registro | febrero2026: sin registro | marzo2026: cuotas=0, monto=0, obs=ABRIL</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="9" t="inlineStr">
+      <c r="A88" s="8" t="inlineStr">
         <is>
           <t>ROJO</t>
         </is>
@@ -9803,7 +9321,7 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="D88" s="13" t="n">
+      <c r="D88" s="12" t="n">
         <v>46087</v>
       </c>
       <c r="E88" s="4" t="inlineStr">
@@ -9847,14 +9365,14 @@
           <t>ABRIL</t>
         </is>
       </c>
-      <c r="P88" s="14" t="inlineStr">
+      <c r="P88" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: sin registro | enero2026: sin registro | febrero2026: sin registro | marzo2026: cuotas=0, monto=0, obs=ABRIL</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="9" t="inlineStr">
+      <c r="A89" s="8" t="inlineStr">
         <is>
           <t>ROJO</t>
         </is>
@@ -9869,7 +9387,7 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="D89" s="13" t="n">
+      <c r="D89" s="12" t="n">
         <v>46087</v>
       </c>
       <c r="E89" s="4" t="inlineStr">
@@ -9913,14 +9431,14 @@
           <t>ABRIL</t>
         </is>
       </c>
-      <c r="P89" s="14" t="inlineStr">
+      <c r="P89" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: sin registro | enero2026: sin registro | febrero2026: sin registro | marzo2026: cuotas=0, monto=0, obs=ABRIL</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="7" t="inlineStr">
+      <c r="A90" s="5" t="inlineStr">
         <is>
           <t>VERDE</t>
         </is>
@@ -9935,7 +9453,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="D90" s="13" t="n">
+      <c r="D90" s="12" t="n">
         <v>46090</v>
       </c>
       <c r="E90" s="4" t="inlineStr">
@@ -9979,14 +9497,14 @@
           <t>cancelado renovacion</t>
         </is>
       </c>
-      <c r="P90" s="14" t="inlineStr">
+      <c r="P90" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: cuotas=3, monto=342000, obs=5ta.6ta y 7ma cuota | enero2026: cuotas=1, monto=114000, obs=8va cuota | febrero2026: cuotas=1, monto=114000, obs=9na cuota | marzo2026: cuotas=0, monto=0, obs=cancelado renovacion</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="9" t="inlineStr">
+      <c r="A91" s="8" t="inlineStr">
         <is>
           <t>ROJO</t>
         </is>
@@ -10001,7 +9519,7 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="D91" s="13" t="n">
+      <c r="D91" s="12" t="n">
         <v>46090</v>
       </c>
       <c r="E91" s="4" t="inlineStr">
@@ -10045,14 +9563,14 @@
           <t>ABRIL</t>
         </is>
       </c>
-      <c r="P91" s="14" t="inlineStr">
+      <c r="P91" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: sin registro | enero2026: sin registro | febrero2026: sin registro | marzo2026: cuotas=0, monto=0, obs=ABRIL</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="9" t="inlineStr">
+      <c r="A92" s="8" t="inlineStr">
         <is>
           <t>ROJO</t>
         </is>
@@ -10067,7 +9585,7 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="D92" s="13" t="n">
+      <c r="D92" s="12" t="n">
         <v>46090</v>
       </c>
       <c r="E92" s="4" t="inlineStr">
@@ -10111,14 +9629,14 @@
           <t>ABRIL</t>
         </is>
       </c>
-      <c r="P92" s="14" t="inlineStr">
+      <c r="P92" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: sin registro | enero2026: sin registro | febrero2026: sin registro | marzo2026: cuotas=0, monto=0, obs=ABRIL</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="9" t="inlineStr">
+      <c r="A93" s="8" t="inlineStr">
         <is>
           <t>ROJO</t>
         </is>
@@ -10133,7 +9651,7 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="D93" s="13" t="n">
+      <c r="D93" s="12" t="n">
         <v>46090</v>
       </c>
       <c r="E93" s="4" t="inlineStr">
@@ -10177,14 +9695,14 @@
           <t>ABRIL</t>
         </is>
       </c>
-      <c r="P93" s="14" t="inlineStr">
+      <c r="P93" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: sin registro | enero2026: sin registro | febrero2026: sin registro | marzo2026: cuotas=0, monto=0, obs=ABRIL</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="9" t="inlineStr">
+      <c r="A94" s="8" t="inlineStr">
         <is>
           <t>ROJO</t>
         </is>
@@ -10199,7 +9717,7 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="D94" s="13" t="n">
+      <c r="D94" s="12" t="n">
         <v>46091</v>
       </c>
       <c r="E94" s="4" t="inlineStr">
@@ -10243,14 +9761,14 @@
           <t>ABRIL</t>
         </is>
       </c>
-      <c r="P94" s="14" t="inlineStr">
+      <c r="P94" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: sin registro | enero2026: sin registro | febrero2026: sin registro | marzo2026: cuotas=0, monto=0, obs=ABRIL</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="7" t="inlineStr">
+      <c r="A95" s="5" t="inlineStr">
         <is>
           <t>VERDE</t>
         </is>
@@ -10265,7 +9783,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="D95" s="13" t="n">
+      <c r="D95" s="12" t="n">
         <v>46091</v>
       </c>
       <c r="E95" s="4" t="inlineStr">
@@ -10309,14 +9827,14 @@
           <t>cancelado renovacion</t>
         </is>
       </c>
-      <c r="P95" s="14" t="inlineStr">
+      <c r="P95" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: cuotas=1, monto=114000, obs=8va cuota | enero2026: cuotas=1, monto=114000, obs=9na cuota | febrero2026: cuotas=1, monto=114000, obs=10ma cuota | marzo2026: cuotas=0, monto=0, obs=cancelado renovacion</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="7" t="inlineStr">
+      <c r="A96" s="5" t="inlineStr">
         <is>
           <t>VERDE</t>
         </is>
@@ -10331,7 +9849,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="D96" s="13" t="n">
+      <c r="D96" s="12" t="n">
         <v>46091</v>
       </c>
       <c r="E96" s="4" t="inlineStr">
@@ -10375,14 +9893,14 @@
           <t>cancelado</t>
         </is>
       </c>
-      <c r="P96" s="14" t="inlineStr">
+      <c r="P96" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: cuotas=1, monto=135000, obs=11va cuota | enero2026: cuotas=1, monto=135000, obs=12va cuota finalizado | febrero2026: cuotas=0, monto=0, obs=cancelado | marzo2026: cuotas=0, monto=0, obs=cancelado</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="7" t="inlineStr">
+      <c r="A97" s="5" t="inlineStr">
         <is>
           <t>VERDE</t>
         </is>
@@ -10397,7 +9915,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="D97" s="13" t="n">
+      <c r="D97" s="12" t="n">
         <v>46091</v>
       </c>
       <c r="E97" s="4" t="inlineStr">
@@ -10441,14 +9959,14 @@
           <t>cancelado renovacion</t>
         </is>
       </c>
-      <c r="P97" s="14" t="inlineStr">
+      <c r="P97" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: cuotas=1, monto=76000, obs=8va cuota | enero2026: cuotas=1, monto=76000, obs=9na cuota | febrero2026: cuotas=1, monto=76000, obs=10ma cuota | marzo2026: cuotas=0, monto=0, obs=cancelado renovacion</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="9" t="inlineStr">
+      <c r="A98" s="8" t="inlineStr">
         <is>
           <t>ROJO</t>
         </is>
@@ -10463,7 +9981,7 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="D98" s="13" t="n">
+      <c r="D98" s="12" t="n">
         <v>46092</v>
       </c>
       <c r="E98" s="4" t="inlineStr">
@@ -10507,14 +10025,14 @@
           <t>ABRIL</t>
         </is>
       </c>
-      <c r="P98" s="14" t="inlineStr">
+      <c r="P98" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: sin registro | enero2026: sin registro | febrero2026: sin registro | marzo2026: cuotas=0, monto=0, obs=ABRIL</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="9" t="inlineStr">
+      <c r="A99" s="8" t="inlineStr">
         <is>
           <t>ROJO</t>
         </is>
@@ -10529,7 +10047,7 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="D99" s="13" t="n">
+      <c r="D99" s="12" t="n">
         <v>46092</v>
       </c>
       <c r="E99" s="4" t="inlineStr">
@@ -10573,14 +10091,14 @@
           <t>ABRIL</t>
         </is>
       </c>
-      <c r="P99" s="14" t="inlineStr">
+      <c r="P99" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: sin registro | enero2026: sin registro | febrero2026: sin registro | marzo2026: cuotas=0, monto=0, obs=ABRIL</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="9" t="inlineStr">
+      <c r="A100" s="8" t="inlineStr">
         <is>
           <t>ROJO</t>
         </is>
@@ -10595,7 +10113,7 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="D100" s="13" t="n">
+      <c r="D100" s="12" t="n">
         <v>46092</v>
       </c>
       <c r="E100" s="4" t="inlineStr">
@@ -10639,14 +10157,14 @@
           <t>ABRIL</t>
         </is>
       </c>
-      <c r="P100" s="14" t="inlineStr">
+      <c r="P100" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: sin registro | enero2026: sin registro | febrero2026: sin registro | marzo2026: cuotas=0, monto=0, obs=ABRIL</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="9" t="inlineStr">
+      <c r="A101" s="8" t="inlineStr">
         <is>
           <t>ROJO</t>
         </is>
@@ -10661,7 +10179,7 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="D101" s="13" t="n">
+      <c r="D101" s="12" t="n">
         <v>46092</v>
       </c>
       <c r="E101" s="4" t="inlineStr">
@@ -10705,14 +10223,14 @@
           <t>ABRIL</t>
         </is>
       </c>
-      <c r="P101" s="14" t="inlineStr">
+      <c r="P101" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: sin registro | enero2026: sin registro | febrero2026: sin registro | marzo2026: cuotas=0, monto=0, obs=ABRIL</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="9" t="inlineStr">
+      <c r="A102" s="8" t="inlineStr">
         <is>
           <t>ROJO</t>
         </is>
@@ -10727,7 +10245,7 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="D102" s="13" t="n">
+      <c r="D102" s="12" t="n">
         <v>46092</v>
       </c>
       <c r="E102" s="4" t="inlineStr">
@@ -10771,14 +10289,14 @@
           <t>ABRIL</t>
         </is>
       </c>
-      <c r="P102" s="14" t="inlineStr">
+      <c r="P102" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: sin registro | enero2026: sin registro | febrero2026: sin registro | marzo2026: cuotas=0, monto=0, obs=ABRIL</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="9" t="inlineStr">
+      <c r="A103" s="8" t="inlineStr">
         <is>
           <t>ROJO</t>
         </is>
@@ -10793,7 +10311,7 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="D103" s="13" t="n">
+      <c r="D103" s="12" t="n">
         <v>46092</v>
       </c>
       <c r="E103" s="4" t="inlineStr">
@@ -10837,14 +10355,14 @@
           <t>ABRIL</t>
         </is>
       </c>
-      <c r="P103" s="14" t="inlineStr">
+      <c r="P103" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: sin registro | enero2026: sin registro | febrero2026: sin registro | marzo2026: cuotas=0, monto=0, obs=ABRIL</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="7" t="inlineStr">
+      <c r="A104" s="5" t="inlineStr">
         <is>
           <t>VERDE</t>
         </is>
@@ -10859,7 +10377,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="D104" s="13" t="n">
+      <c r="D104" s="12" t="n">
         <v>46093</v>
       </c>
       <c r="E104" s="4" t="inlineStr">
@@ -10903,14 +10421,14 @@
           <t>cancelado renovacion</t>
         </is>
       </c>
-      <c r="P104" s="14" t="inlineStr">
+      <c r="P104" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: cuotas=1, monto=38000, obs=7ma cuota | enero2026: cuotas=1, monto=38000, obs=8va cuota | febrero2026: cuotas=1, monto=38000, obs=9na cuota | marzo2026: cuotas=0, monto=0, obs=cancelado renovacion</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="9" t="inlineStr">
+      <c r="A105" s="8" t="inlineStr">
         <is>
           <t>ROJO</t>
         </is>
@@ -10925,7 +10443,7 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="D105" s="13" t="n">
+      <c r="D105" s="12" t="n">
         <v>46094</v>
       </c>
       <c r="E105" s="4" t="inlineStr">
@@ -10969,14 +10487,14 @@
           <t>ABRIL</t>
         </is>
       </c>
-      <c r="P105" s="14" t="inlineStr">
+      <c r="P105" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: sin registro | enero2026: sin registro | febrero2026: sin registro | marzo2026: cuotas=0, monto=0, obs=ABRIL</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="9" t="inlineStr">
+      <c r="A106" s="8" t="inlineStr">
         <is>
           <t>ROJO</t>
         </is>
@@ -10991,7 +10509,7 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="D106" s="13" t="n">
+      <c r="D106" s="12" t="n">
         <v>46094</v>
       </c>
       <c r="E106" s="4" t="inlineStr">
@@ -11035,14 +10553,14 @@
           <t>ABRIL</t>
         </is>
       </c>
-      <c r="P106" s="14" t="inlineStr">
+      <c r="P106" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: sin registro | enero2026: sin registro | febrero2026: sin registro | marzo2026: cuotas=0, monto=0, obs=ABRIL</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="9" t="inlineStr">
+      <c r="A107" s="8" t="inlineStr">
         <is>
           <t>ROJO</t>
         </is>
@@ -11057,7 +10575,7 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="D107" s="13" t="n">
+      <c r="D107" s="12" t="n">
         <v>46094</v>
       </c>
       <c r="E107" s="4" t="inlineStr">
@@ -11101,14 +10619,14 @@
           <t>ABRIL</t>
         </is>
       </c>
-      <c r="P107" s="14" t="inlineStr">
+      <c r="P107" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: sin registro | enero2026: sin registro | febrero2026: sin registro | marzo2026: cuotas=0, monto=0, obs=ABRIL</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="9" t="inlineStr">
+      <c r="A108" s="8" t="inlineStr">
         <is>
           <t>ROJO</t>
         </is>
@@ -11123,7 +10641,7 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="D108" s="13" t="n">
+      <c r="D108" s="12" t="n">
         <v>46094</v>
       </c>
       <c r="E108" s="4" t="inlineStr">
@@ -11167,14 +10685,14 @@
           <t>ABRIL</t>
         </is>
       </c>
-      <c r="P108" s="14" t="inlineStr">
+      <c r="P108" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: sin registro | enero2026: sin registro | febrero2026: sin registro | marzo2026: cuotas=0, monto=0, obs=ABRIL</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="7" t="inlineStr">
+      <c r="A109" s="5" t="inlineStr">
         <is>
           <t>VERDE</t>
         </is>
@@ -11189,7 +10707,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="D109" s="13" t="n">
+      <c r="D109" s="12" t="n">
         <v>46098</v>
       </c>
       <c r="E109" s="4" t="inlineStr">
@@ -11233,14 +10751,14 @@
           <t>cancelado renovacion</t>
         </is>
       </c>
-      <c r="P109" s="14" t="inlineStr">
+      <c r="P109" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: cuotas=1, monto=342000, obs=5ta, 6ta y 7ma cuota | enero2026: cuotas=1, monto=114000, obs=8va cuota | febrero2026: cuotas=2, monto=228000, obs=9na y 10ma cuota | marzo2026: cuotas=0, monto=0, obs=cancelado renovacion</t>
         </is>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="9" t="inlineStr">
+      <c r="A110" s="8" t="inlineStr">
         <is>
           <t>ROJO</t>
         </is>
@@ -11255,7 +10773,7 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="D110" s="13" t="n">
+      <c r="D110" s="12" t="n">
         <v>46100</v>
       </c>
       <c r="E110" s="4" t="inlineStr">
@@ -11299,14 +10817,14 @@
           <t>ABRIL</t>
         </is>
       </c>
-      <c r="P110" s="14" t="inlineStr">
+      <c r="P110" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: sin registro | enero2026: sin registro | febrero2026: sin registro | marzo2026: cuotas=0, monto=0, obs=ABRIL</t>
         </is>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="9" t="inlineStr">
+      <c r="A111" s="8" t="inlineStr">
         <is>
           <t>ROJO</t>
         </is>
@@ -11321,7 +10839,7 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="D111" s="13" t="n">
+      <c r="D111" s="12" t="n">
         <v>46100</v>
       </c>
       <c r="E111" s="4" t="inlineStr">
@@ -11365,14 +10883,14 @@
           <t>ABRIL</t>
         </is>
       </c>
-      <c r="P111" s="14" t="inlineStr">
+      <c r="P111" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: sin registro | enero2026: sin registro | febrero2026: sin registro | marzo2026: cuotas=0, monto=0, obs=ABRIL</t>
         </is>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="7" t="inlineStr">
+      <c r="A112" s="5" t="inlineStr">
         <is>
           <t>VERDE</t>
         </is>
@@ -11387,7 +10905,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="D112" s="13" t="n">
+      <c r="D112" s="12" t="n">
         <v>46100</v>
       </c>
       <c r="E112" s="4" t="inlineStr">
@@ -11431,14 +10949,14 @@
           <t>7ma cuota</t>
         </is>
       </c>
-      <c r="P112" s="14" t="inlineStr">
+      <c r="P112" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: cuotas=1, monto=380000, obs=4ta cuota | enero2026: cuotas=1, monto=380000, obs=5ta cuota | febrero2026: cuotas=1, monto=380000, obs=6ta cuota | marzo2026: cuotas=1, monto=380000, obs=7ma cuota</t>
         </is>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="9" t="inlineStr">
+      <c r="A113" s="8" t="inlineStr">
         <is>
           <t>ROJO</t>
         </is>
@@ -11453,7 +10971,7 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="D113" s="13" t="n">
+      <c r="D113" s="12" t="n">
         <v>46101</v>
       </c>
       <c r="E113" s="4" t="inlineStr">
@@ -11497,14 +11015,14 @@
           <t>MAYO</t>
         </is>
       </c>
-      <c r="P113" s="14" t="inlineStr">
+      <c r="P113" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: sin registro | enero2026: sin registro | febrero2026: sin registro | marzo2026: cuotas=0, monto=0, obs=MAYO</t>
         </is>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="9" t="inlineStr">
+      <c r="A114" s="8" t="inlineStr">
         <is>
           <t>ROJO</t>
         </is>
@@ -11519,7 +11037,7 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="D114" s="13" t="n">
+      <c r="D114" s="12" t="n">
         <v>46101</v>
       </c>
       <c r="E114" s="4" t="inlineStr">
@@ -11563,14 +11081,14 @@
           <t>MAYO</t>
         </is>
       </c>
-      <c r="P114" s="14" t="inlineStr">
+      <c r="P114" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: sin registro | enero2026: sin registro | febrero2026: sin registro | marzo2026: cuotas=0, monto=0, obs=MAYO</t>
         </is>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="7" t="inlineStr">
+      <c r="A115" s="5" t="inlineStr">
         <is>
           <t>VERDE</t>
         </is>
@@ -11585,7 +11103,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="D115" s="13" t="n">
+      <c r="D115" s="12" t="n">
         <v>46101</v>
       </c>
       <c r="E115" s="4" t="inlineStr">
@@ -11629,14 +11147,14 @@
           <t>cancelado</t>
         </is>
       </c>
-      <c r="P115" s="14" t="inlineStr">
+      <c r="P115" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: cuotas=1, monto=225000, obs=10ma cuota y renovacion, se cancelo 450000, se deposito el resto | enero2026: cuotas=1, monto=225000, obs=10ma cuota y renovacion, se cancelo 450000, se deposito el resto | febrero2026: cuotas=0, monto=0, obs=cancelado | marzo2026: cuotas=0, monto=0, obs=cancelado</t>
         </is>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="9" t="inlineStr">
+      <c r="A116" s="8" t="inlineStr">
         <is>
           <t>ROJO</t>
         </is>
@@ -11651,7 +11169,7 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="D116" s="13" t="n">
+      <c r="D116" s="12" t="n">
         <v>46101</v>
       </c>
       <c r="E116" s="4" t="inlineStr">
@@ -11695,14 +11213,14 @@
           <t>MAYO</t>
         </is>
       </c>
-      <c r="P116" s="14" t="inlineStr">
+      <c r="P116" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: sin registro | enero2026: sin registro | febrero2026: sin registro | marzo2026: cuotas=0, monto=0, obs=MAYO</t>
         </is>
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="9" t="inlineStr">
+      <c r="A117" s="8" t="inlineStr">
         <is>
           <t>ROJO</t>
         </is>
@@ -11717,7 +11235,7 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="D117" s="13" t="n">
+      <c r="D117" s="12" t="n">
         <v>46106</v>
       </c>
       <c r="E117" s="4" t="inlineStr">
@@ -11761,14 +11279,14 @@
           <t>MAYO</t>
         </is>
       </c>
-      <c r="P117" s="14" t="inlineStr">
+      <c r="P117" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: sin registro | enero2026: sin registro | febrero2026: sin registro | marzo2026: cuotas=0, monto=0, obs=MAYO</t>
         </is>
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="9" t="inlineStr">
+      <c r="A118" s="8" t="inlineStr">
         <is>
           <t>ROJO</t>
         </is>
@@ -11783,7 +11301,7 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="D118" s="13" t="n">
+      <c r="D118" s="12" t="n">
         <v>46106</v>
       </c>
       <c r="E118" s="4" t="inlineStr">
@@ -11827,14 +11345,14 @@
           <t>MAYO</t>
         </is>
       </c>
-      <c r="P118" s="14" t="inlineStr">
+      <c r="P118" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: sin registro | enero2026: sin registro | febrero2026: sin registro | marzo2026: cuotas=0, monto=0, obs=MAYO</t>
         </is>
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="9" t="inlineStr">
+      <c r="A119" s="8" t="inlineStr">
         <is>
           <t>ROJO</t>
         </is>
@@ -11849,7 +11367,7 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="D119" s="13" t="n">
+      <c r="D119" s="12" t="n">
         <v>46106</v>
       </c>
       <c r="E119" s="4" t="inlineStr">
@@ -11893,14 +11411,14 @@
           <t>MAYO</t>
         </is>
       </c>
-      <c r="P119" s="14" t="inlineStr">
+      <c r="P119" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: sin registro | enero2026: sin registro | febrero2026: sin registro | marzo2026: cuotas=0, monto=0, obs=MAYO</t>
         </is>
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="7" t="inlineStr">
+      <c r="A120" s="5" t="inlineStr">
         <is>
           <t>VERDE</t>
         </is>
@@ -11915,7 +11433,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="D120" s="13" t="n">
+      <c r="D120" s="12" t="n">
         <v>46106</v>
       </c>
       <c r="E120" s="4" t="inlineStr">
@@ -11959,14 +11477,14 @@
           <t>cancelado</t>
         </is>
       </c>
-      <c r="P120" s="14" t="inlineStr">
+      <c r="P120" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: cuotas=0, monto=0, obs=12va cuota finalizado | enero2026: cuotas=0, monto=0, obs=12va cuota finalizado | febrero2026: cuotas=0, monto=0, obs=cancelado | marzo2026: cuotas=0, monto=0, obs=cancelado</t>
         </is>
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="7" t="inlineStr">
+      <c r="A121" s="5" t="inlineStr">
         <is>
           <t>VERDE</t>
         </is>
@@ -11981,7 +11499,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="D121" s="13" t="n">
+      <c r="D121" s="12" t="n">
         <v>46106</v>
       </c>
       <c r="E121" s="4" t="inlineStr">
@@ -12025,14 +11543,14 @@
           <t>5ta cuota</t>
         </is>
       </c>
-      <c r="P121" s="14" t="inlineStr">
+      <c r="P121" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: cuotas=1, monto=38000, obs=1ra cuota | enero2026: cuotas=1, monto=38000, obs=3ra cuota | febrero2026: cuotas=1, monto=38000, obs=4ta cuota | marzo2026: cuotas=1, monto=38000, obs=5ta cuota</t>
         </is>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="9" t="inlineStr">
+      <c r="A122" s="8" t="inlineStr">
         <is>
           <t>ROJO</t>
         </is>
@@ -12047,7 +11565,7 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="D122" s="13" t="n">
+      <c r="D122" s="12" t="n">
         <v>46108</v>
       </c>
       <c r="E122" s="4" t="inlineStr">
@@ -12091,14 +11609,14 @@
           <t>MAYO</t>
         </is>
       </c>
-      <c r="P122" s="14" t="inlineStr">
+      <c r="P122" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: sin registro | enero2026: sin registro | febrero2026: sin registro | marzo2026: cuotas=0, monto=0, obs=MAYO</t>
         </is>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="9" t="inlineStr">
+      <c r="A123" s="8" t="inlineStr">
         <is>
           <t>ROJO</t>
         </is>
@@ -12113,7 +11631,7 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="D123" s="13" t="n">
+      <c r="D123" s="12" t="n">
         <v>46108</v>
       </c>
       <c r="E123" s="4" t="inlineStr">
@@ -12157,14 +11675,14 @@
           <t>MAYO</t>
         </is>
       </c>
-      <c r="P123" s="14" t="inlineStr">
+      <c r="P123" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: sin registro | enero2026: sin registro | febrero2026: sin registro | marzo2026: cuotas=0, monto=0, obs=MAYO</t>
         </is>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="9" t="inlineStr">
+      <c r="A124" s="8" t="inlineStr">
         <is>
           <t>ROJO</t>
         </is>
@@ -12179,7 +11697,7 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="D124" s="13" t="n">
+      <c r="D124" s="12" t="n">
         <v>46112</v>
       </c>
       <c r="E124" s="4" t="inlineStr">
@@ -12223,14 +11741,14 @@
           <t>MAYO</t>
         </is>
       </c>
-      <c r="P124" s="14" t="inlineStr">
+      <c r="P124" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: sin registro | enero2026: sin registro | febrero2026: sin registro | marzo2026: cuotas=0, monto=0, obs=MAYO</t>
         </is>
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="9" t="inlineStr">
+      <c r="A125" s="8" t="inlineStr">
         <is>
           <t>ROJO</t>
         </is>
@@ -12245,7 +11763,7 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="D125" s="13" t="n">
+      <c r="D125" s="12" t="n">
         <v>46112</v>
       </c>
       <c r="E125" s="4" t="inlineStr">
@@ -12289,14 +11807,14 @@
           <t>MAYO</t>
         </is>
       </c>
-      <c r="P125" s="14" t="inlineStr">
+      <c r="P125" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: sin registro | enero2026: sin registro | febrero2026: sin registro | marzo2026: cuotas=0, monto=0, obs=MAYO</t>
         </is>
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="8" t="inlineStr">
+      <c r="A126" s="7" t="inlineStr">
         <is>
           <t>AMARILLO</t>
         </is>
@@ -12311,7 +11829,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="D126" s="13" t="n">
+      <c r="D126" s="12" t="n">
         <v>46113</v>
       </c>
       <c r="E126" s="4" t="inlineStr">
@@ -12351,14 +11869,14 @@
         <v>0</v>
       </c>
       <c r="O126" s="4" t="inlineStr"/>
-      <c r="P126" s="14" t="inlineStr">
+      <c r="P126" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: sin registro | enero2026: sin registro | febrero2026: sin registro | marzo2026: sin registro</t>
         </is>
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="8" t="inlineStr">
+      <c r="A127" s="7" t="inlineStr">
         <is>
           <t>AMARILLO</t>
         </is>
@@ -12373,7 +11891,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="D127" s="13" t="n">
+      <c r="D127" s="12" t="n">
         <v>46113</v>
       </c>
       <c r="E127" s="4" t="inlineStr">
@@ -12413,14 +11931,14 @@
         <v>0</v>
       </c>
       <c r="O127" s="4" t="inlineStr"/>
-      <c r="P127" s="14" t="inlineStr">
+      <c r="P127" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: sin registro | enero2026: sin registro | febrero2026: sin registro | marzo2026: sin registro</t>
         </is>
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="8" t="inlineStr">
+      <c r="A128" s="7" t="inlineStr">
         <is>
           <t>AMARILLO</t>
         </is>
@@ -12435,7 +11953,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="D128" s="13" t="n">
+      <c r="D128" s="12" t="n">
         <v>46113</v>
       </c>
       <c r="E128" s="4" t="inlineStr">
@@ -12475,14 +11993,14 @@
         <v>0</v>
       </c>
       <c r="O128" s="4" t="inlineStr"/>
-      <c r="P128" s="14" t="inlineStr">
+      <c r="P128" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: sin registro | enero2026: sin registro | febrero2026: sin registro | marzo2026: sin registro</t>
         </is>
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="7" t="inlineStr">
+      <c r="A129" s="5" t="inlineStr">
         <is>
           <t>VERDE</t>
         </is>
@@ -12497,7 +12015,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="D129" s="13" t="n">
+      <c r="D129" s="12" t="n">
         <v>46118</v>
       </c>
       <c r="E129" s="4" t="inlineStr">
@@ -12541,14 +12059,14 @@
           <t>cancelado</t>
         </is>
       </c>
-      <c r="P129" s="14" t="inlineStr">
+      <c r="P129" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: cuotas=1, monto=90000, obs=11va cuota | enero2026: cuotas=1, monto=90000, obs=12va cuota finalizado | febrero2026: cuotas=0, monto=0, obs=cancelado | marzo2026: cuotas=0, monto=0, obs=cancelado</t>
         </is>
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="8" t="inlineStr">
+      <c r="A130" s="7" t="inlineStr">
         <is>
           <t>AMARILLO</t>
         </is>
@@ -12563,7 +12081,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="D130" s="13" t="n">
+      <c r="D130" s="12" t="n">
         <v>46119</v>
       </c>
       <c r="E130" s="4" t="inlineStr">
@@ -12603,14 +12121,14 @@
         <v>0</v>
       </c>
       <c r="O130" s="4" t="inlineStr"/>
-      <c r="P130" s="14" t="inlineStr">
+      <c r="P130" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: sin registro | enero2026: sin registro | febrero2026: sin registro | marzo2026: sin registro</t>
         </is>
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="8" t="inlineStr">
+      <c r="A131" s="7" t="inlineStr">
         <is>
           <t>AMARILLO</t>
         </is>
@@ -12625,7 +12143,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="D131" s="13" t="n">
+      <c r="D131" s="12" t="n">
         <v>46119</v>
       </c>
       <c r="E131" s="4" t="inlineStr">
@@ -12665,14 +12183,14 @@
         <v>0</v>
       </c>
       <c r="O131" s="4" t="inlineStr"/>
-      <c r="P131" s="14" t="inlineStr">
+      <c r="P131" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: sin registro | enero2026: sin registro | febrero2026: sin registro | marzo2026: sin registro</t>
         </is>
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="8" t="inlineStr">
+      <c r="A132" s="7" t="inlineStr">
         <is>
           <t>AMARILLO</t>
         </is>
@@ -12687,7 +12205,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="D132" s="13" t="n">
+      <c r="D132" s="12" t="n">
         <v>46120</v>
       </c>
       <c r="E132" s="4" t="inlineStr">
@@ -12727,14 +12245,14 @@
         <v>0</v>
       </c>
       <c r="O132" s="4" t="inlineStr"/>
-      <c r="P132" s="14" t="inlineStr">
+      <c r="P132" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: sin registro | enero2026: sin registro | febrero2026: sin registro | marzo2026: sin registro</t>
         </is>
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="7" t="inlineStr">
+      <c r="A133" s="5" t="inlineStr">
         <is>
           <t>VERDE</t>
         </is>
@@ -12749,7 +12267,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="D133" s="13" t="n">
+      <c r="D133" s="12" t="n">
         <v>46121</v>
       </c>
       <c r="E133" s="4" t="inlineStr">
@@ -12793,14 +12311,14 @@
           <t>10ma cuota</t>
         </is>
       </c>
-      <c r="P133" s="14" t="inlineStr">
+      <c r="P133" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: cuotas=1, monto=76000, obs=7ma cuota | enero2026: cuotas=1, monto=76000, obs=8va cuota | febrero2026: cuotas=1, monto=76000, obs=9na cuota | marzo2026: cuotas=1, monto=76000, obs=10ma cuota</t>
         </is>
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="8" t="inlineStr">
+      <c r="A134" s="7" t="inlineStr">
         <is>
           <t>AMARILLO</t>
         </is>
@@ -12815,7 +12333,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="D134" s="13" t="n">
+      <c r="D134" s="12" t="n">
         <v>46121</v>
       </c>
       <c r="E134" s="4" t="inlineStr">
@@ -12855,14 +12373,14 @@
         <v>0</v>
       </c>
       <c r="O134" s="4" t="inlineStr"/>
-      <c r="P134" s="14" t="inlineStr">
+      <c r="P134" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: sin registro | enero2026: sin registro | febrero2026: sin registro | marzo2026: sin registro</t>
         </is>
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="8" t="inlineStr">
+      <c r="A135" s="7" t="inlineStr">
         <is>
           <t>AMARILLO</t>
         </is>
@@ -12877,7 +12395,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="D135" s="13" t="n">
+      <c r="D135" s="12" t="n">
         <v>46121</v>
       </c>
       <c r="E135" s="4" t="inlineStr">
@@ -12917,14 +12435,14 @@
         <v>0</v>
       </c>
       <c r="O135" s="4" t="inlineStr"/>
-      <c r="P135" s="14" t="inlineStr">
+      <c r="P135" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: sin registro | enero2026: sin registro | febrero2026: sin registro | marzo2026: sin registro</t>
         </is>
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="8" t="inlineStr">
+      <c r="A136" s="7" t="inlineStr">
         <is>
           <t>AMARILLO</t>
         </is>
@@ -12939,7 +12457,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="D136" s="13" t="n">
+      <c r="D136" s="12" t="n">
         <v>46121</v>
       </c>
       <c r="E136" s="4" t="inlineStr">
@@ -12979,14 +12497,14 @@
         <v>0</v>
       </c>
       <c r="O136" s="4" t="inlineStr"/>
-      <c r="P136" s="14" t="inlineStr">
+      <c r="P136" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: sin registro | enero2026: sin registro | febrero2026: sin registro | marzo2026: sin registro</t>
         </is>
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="8" t="inlineStr">
+      <c r="A137" s="7" t="inlineStr">
         <is>
           <t>AMARILLO</t>
         </is>
@@ -13001,7 +12519,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="D137" s="13" t="n">
+      <c r="D137" s="12" t="n">
         <v>46121</v>
       </c>
       <c r="E137" s="4" t="inlineStr">
@@ -13041,14 +12559,14 @@
         <v>0</v>
       </c>
       <c r="O137" s="4" t="inlineStr"/>
-      <c r="P137" s="14" t="inlineStr">
+      <c r="P137" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: sin registro | enero2026: sin registro | febrero2026: sin registro | marzo2026: sin registro</t>
         </is>
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="7" t="inlineStr">
+      <c r="A138" s="5" t="inlineStr">
         <is>
           <t>VERDE</t>
         </is>
@@ -13063,7 +12581,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="D138" s="13" t="n">
+      <c r="D138" s="12" t="n">
         <v>46121</v>
       </c>
       <c r="E138" s="4" t="inlineStr">
@@ -13107,14 +12625,14 @@
           <t>10ma cuota</t>
         </is>
       </c>
-      <c r="P138" s="14" t="inlineStr">
+      <c r="P138" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: cuotas=1, monto=190000, obs=7ma cuota | enero2026: cuotas=1, monto=190000, obs=8va cuota | febrero2026: cuotas=1, monto=190000, obs=9na cuota | marzo2026: cuotas=1, monto=190000, obs=10ma cuota</t>
         </is>
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="8" t="inlineStr">
+      <c r="A139" s="7" t="inlineStr">
         <is>
           <t>AMARILLO</t>
         </is>
@@ -13129,7 +12647,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="D139" s="13" t="n">
+      <c r="D139" s="12" t="n">
         <v>46122</v>
       </c>
       <c r="E139" s="4" t="inlineStr">
@@ -13169,14 +12687,14 @@
         <v>0</v>
       </c>
       <c r="O139" s="4" t="inlineStr"/>
-      <c r="P139" s="14" t="inlineStr">
+      <c r="P139" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: sin registro | enero2026: sin registro | febrero2026: sin registro | marzo2026: sin registro</t>
         </is>
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="7" t="inlineStr">
+      <c r="A140" s="5" t="inlineStr">
         <is>
           <t>VERDE</t>
         </is>
@@ -13191,7 +12709,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="D140" s="13" t="n">
+      <c r="D140" s="12" t="n">
         <v>46122</v>
       </c>
       <c r="E140" s="4" t="inlineStr">
@@ -13235,14 +12753,14 @@
           <t>6ta cuota</t>
         </is>
       </c>
-      <c r="P140" s="14" t="inlineStr">
+      <c r="P140" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: cuotas=1, monto=76000, obs=2da cuota | enero2026: cuotas=1, monto=76000, obs=3ra cuota | febrero2026: cuotas=2, monto=152000, obs=4ta y 5ta cuota | marzo2026: cuotas=1, monto=76000, obs=6ta cuota</t>
         </is>
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="7" t="inlineStr">
+      <c r="A141" s="5" t="inlineStr">
         <is>
           <t>VERDE</t>
         </is>
@@ -13257,7 +12775,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="D141" s="13" t="n">
+      <c r="D141" s="12" t="n">
         <v>46122</v>
       </c>
       <c r="E141" s="4" t="inlineStr">
@@ -13301,14 +12819,14 @@
           <t>4ta cuota</t>
         </is>
       </c>
-      <c r="P141" s="14" t="inlineStr">
+      <c r="P141" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: cuotas=1, monto=190000, obs=1ra cuota | enero2026: cuotas=1, monto=190000, obs=2da cuota | febrero2026: cuotas=1, monto=190000, obs=3ra cuota | marzo2026: cuotas=1, monto=190000, obs=4ta cuota</t>
         </is>
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="8" t="inlineStr">
+      <c r="A142" s="7" t="inlineStr">
         <is>
           <t>AMARILLO</t>
         </is>
@@ -13323,7 +12841,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="D142" s="13" t="n">
+      <c r="D142" s="12" t="n">
         <v>46122</v>
       </c>
       <c r="E142" s="4" t="inlineStr">
@@ -13363,14 +12881,14 @@
         <v>0</v>
       </c>
       <c r="O142" s="4" t="inlineStr"/>
-      <c r="P142" s="14" t="inlineStr">
+      <c r="P142" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: sin registro | enero2026: sin registro | febrero2026: sin registro | marzo2026: sin registro</t>
         </is>
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="8" t="inlineStr">
+      <c r="A143" s="7" t="inlineStr">
         <is>
           <t>AMARILLO</t>
         </is>
@@ -13385,7 +12903,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="D143" s="13" t="n">
+      <c r="D143" s="12" t="n">
         <v>46125</v>
       </c>
       <c r="E143" s="4" t="inlineStr">
@@ -13425,14 +12943,14 @@
         <v>0</v>
       </c>
       <c r="O143" s="4" t="inlineStr"/>
-      <c r="P143" s="14" t="inlineStr">
+      <c r="P143" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: sin registro | enero2026: sin registro | febrero2026: sin registro | marzo2026: sin registro</t>
         </is>
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="8" t="inlineStr">
+      <c r="A144" s="7" t="inlineStr">
         <is>
           <t>AMARILLO</t>
         </is>
@@ -13447,7 +12965,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="D144" s="13" t="n">
+      <c r="D144" s="12" t="n">
         <v>46125</v>
       </c>
       <c r="E144" s="4" t="inlineStr">
@@ -13487,14 +13005,14 @@
         <v>0</v>
       </c>
       <c r="O144" s="4" t="inlineStr"/>
-      <c r="P144" s="14" t="inlineStr">
+      <c r="P144" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: sin registro | enero2026: sin registro | febrero2026: sin registro | marzo2026: sin registro</t>
         </is>
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="8" t="inlineStr">
+      <c r="A145" s="7" t="inlineStr">
         <is>
           <t>AMARILLO</t>
         </is>
@@ -13509,7 +13027,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="D145" s="13" t="n">
+      <c r="D145" s="12" t="n">
         <v>46125</v>
       </c>
       <c r="E145" s="4" t="inlineStr">
@@ -13549,14 +13067,14 @@
         <v>0</v>
       </c>
       <c r="O145" s="4" t="inlineStr"/>
-      <c r="P145" s="14" t="inlineStr">
+      <c r="P145" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: sin registro | enero2026: sin registro | febrero2026: sin registro | marzo2026: sin registro</t>
         </is>
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="8" t="inlineStr">
+      <c r="A146" s="7" t="inlineStr">
         <is>
           <t>AMARILLO</t>
         </is>
@@ -13571,7 +13089,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="D146" s="13" t="n">
+      <c r="D146" s="12" t="n">
         <v>46126</v>
       </c>
       <c r="E146" s="4" t="inlineStr">
@@ -13611,14 +13129,14 @@
         <v>0</v>
       </c>
       <c r="O146" s="4" t="inlineStr"/>
-      <c r="P146" s="14" t="inlineStr">
+      <c r="P146" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: sin registro | enero2026: sin registro | febrero2026: sin registro | marzo2026: sin registro</t>
         </is>
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="7" t="inlineStr">
+      <c r="A147" s="5" t="inlineStr">
         <is>
           <t>VERDE</t>
         </is>
@@ -13633,7 +13151,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="D147" s="13" t="n">
+      <c r="D147" s="12" t="n">
         <v>46127</v>
       </c>
       <c r="E147" s="4" t="inlineStr">
@@ -13677,14 +13195,14 @@
           <t>2da cuota</t>
         </is>
       </c>
-      <c r="P147" s="14" t="inlineStr">
+      <c r="P147" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: sin registro | enero2026: cuotas=0, monto=0, obs= | febrero2026: cuotas=1, monto=266000, obs=1ra cuota | marzo2026: cuotas=1, monto=266000, obs=2da cuota</t>
         </is>
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="8" t="inlineStr">
+      <c r="A148" s="7" t="inlineStr">
         <is>
           <t>AMARILLO</t>
         </is>
@@ -13699,7 +13217,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="D148" s="13" t="n">
+      <c r="D148" s="12" t="n">
         <v>46127</v>
       </c>
       <c r="E148" s="4" t="inlineStr">
@@ -13739,14 +13257,14 @@
         <v>0</v>
       </c>
       <c r="O148" s="4" t="inlineStr"/>
-      <c r="P148" s="14" t="inlineStr">
+      <c r="P148" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: sin registro | enero2026: sin registro | febrero2026: sin registro | marzo2026: sin registro</t>
         </is>
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="7" t="inlineStr">
+      <c r="A149" s="5" t="inlineStr">
         <is>
           <t>VERDE</t>
         </is>
@@ -13761,7 +13279,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="D149" s="13" t="n">
+      <c r="D149" s="12" t="n">
         <v>46127</v>
       </c>
       <c r="E149" s="4" t="inlineStr">
@@ -13805,14 +13323,14 @@
           <t>7ma cuota</t>
         </is>
       </c>
-      <c r="P149" s="14" t="inlineStr">
+      <c r="P149" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: cuotas=1, monto=38000, obs=4ta cuota | enero2026: cuotas=1, monto=38000, obs=5ta cuota | febrero2026: cuotas=1, monto=38000, obs=6ta cuota | marzo2026: cuotas=1, monto=38000, obs=7ma cuota</t>
         </is>
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="7" t="inlineStr">
+      <c r="A150" s="5" t="inlineStr">
         <is>
           <t>VERDE</t>
         </is>
@@ -13827,7 +13345,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="D150" s="13" t="n">
+      <c r="D150" s="12" t="n">
         <v>46128</v>
       </c>
       <c r="E150" s="4" t="inlineStr">
@@ -13871,14 +13389,14 @@
           <t>11va cuota</t>
         </is>
       </c>
-      <c r="P150" s="14" t="inlineStr">
+      <c r="P150" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: cuotas=1, monto=38000, obs=8va cuota | enero2026: cuotas=1, monto=38000, obs=9na cuota | febrero2026: cuotas=1, monto=38000, obs=10ma cuota | marzo2026: cuotas=1, monto=38000, obs=11va cuota</t>
         </is>
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="7" t="inlineStr">
+      <c r="A151" s="5" t="inlineStr">
         <is>
           <t>VERDE</t>
         </is>
@@ -13893,7 +13411,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="D151" s="13" t="n">
+      <c r="D151" s="12" t="n">
         <v>46129</v>
       </c>
       <c r="E151" s="4" t="inlineStr">
@@ -13937,14 +13455,14 @@
           <t>cancelado</t>
         </is>
       </c>
-      <c r="P151" s="14" t="inlineStr">
+      <c r="P151" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: cuotas=0, monto=0, obs=va 9 cuotas fondos insuficientes | enero2026: cuotas=1, monto=114000, obs=10ma cuota | febrero2026: cuotas=1, monto=114000, obs=11va cuota | marzo2026: cuotas=1, monto=114000, obs=cancelado</t>
         </is>
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="8" t="inlineStr">
+      <c r="A152" s="7" t="inlineStr">
         <is>
           <t>AMARILLO</t>
         </is>
@@ -13959,7 +13477,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="D152" s="13" t="n">
+      <c r="D152" s="12" t="n">
         <v>46129</v>
       </c>
       <c r="E152" s="4" t="inlineStr">
@@ -13999,14 +13517,14 @@
         <v>0</v>
       </c>
       <c r="O152" s="4" t="inlineStr"/>
-      <c r="P152" s="14" t="inlineStr">
+      <c r="P152" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: sin registro | enero2026: sin registro | febrero2026: sin registro | marzo2026: sin registro</t>
         </is>
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="8" t="inlineStr">
+      <c r="A153" s="7" t="inlineStr">
         <is>
           <t>AMARILLO</t>
         </is>
@@ -14021,7 +13539,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="D153" s="13" t="n">
+      <c r="D153" s="12" t="n">
         <v>46129</v>
       </c>
       <c r="E153" s="4" t="inlineStr">
@@ -14061,14 +13579,14 @@
         <v>0</v>
       </c>
       <c r="O153" s="4" t="inlineStr"/>
-      <c r="P153" s="14" t="inlineStr">
+      <c r="P153" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: sin registro | enero2026: sin registro | febrero2026: sin registro | marzo2026: sin registro</t>
         </is>
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="7" t="inlineStr">
+      <c r="A154" s="5" t="inlineStr">
         <is>
           <t>VERDE</t>
         </is>
@@ -14083,7 +13601,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="D154" s="13" t="n">
+      <c r="D154" s="12" t="n">
         <v>46129</v>
       </c>
       <c r="E154" s="4" t="inlineStr">
@@ -14127,14 +13645,14 @@
           <t>2da cuota</t>
         </is>
       </c>
-      <c r="P154" s="14" t="inlineStr">
+      <c r="P154" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: sin registro | enero2026: cuotas=0, monto=0, obs= | febrero2026: cuotas=1, monto=76000, obs=1ra cuota | marzo2026: cuotas=1, monto=76000, obs=2da cuota</t>
         </is>
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="8" t="inlineStr">
+      <c r="A155" s="7" t="inlineStr">
         <is>
           <t>AMARILLO</t>
         </is>
@@ -14149,7 +13667,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="D155" s="13" t="n">
+      <c r="D155" s="12" t="n">
         <v>46129</v>
       </c>
       <c r="E155" s="4" t="inlineStr">
@@ -14189,14 +13707,14 @@
         <v>0</v>
       </c>
       <c r="O155" s="4" t="inlineStr"/>
-      <c r="P155" s="14" t="inlineStr">
+      <c r="P155" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: sin registro | enero2026: sin registro | febrero2026: sin registro | marzo2026: sin registro</t>
         </is>
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="8" t="inlineStr">
+      <c r="A156" s="7" t="inlineStr">
         <is>
           <t>AMARILLO</t>
         </is>
@@ -14211,7 +13729,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="D156" s="13" t="n">
+      <c r="D156" s="12" t="n">
         <v>46129</v>
       </c>
       <c r="E156" s="4" t="inlineStr">
@@ -14251,14 +13769,14 @@
         <v>0</v>
       </c>
       <c r="O156" s="4" t="inlineStr"/>
-      <c r="P156" s="14" t="inlineStr">
+      <c r="P156" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: sin registro | enero2026: sin registro | febrero2026: sin registro | marzo2026: sin registro</t>
         </is>
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="8" t="inlineStr">
+      <c r="A157" s="7" t="inlineStr">
         <is>
           <t>AMARILLO</t>
         </is>
@@ -14273,7 +13791,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="D157" s="13" t="n">
+      <c r="D157" s="12" t="n">
         <v>46129</v>
       </c>
       <c r="E157" s="4" t="inlineStr">
@@ -14313,14 +13831,14 @@
         <v>0</v>
       </c>
       <c r="O157" s="4" t="inlineStr"/>
-      <c r="P157" s="14" t="inlineStr">
+      <c r="P157" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: sin registro | enero2026: sin registro | febrero2026: sin registro | marzo2026: sin registro</t>
         </is>
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="8" t="inlineStr">
+      <c r="A158" s="7" t="inlineStr">
         <is>
           <t>AMARILLO</t>
         </is>
@@ -14335,7 +13853,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="D158" s="13" t="n">
+      <c r="D158" s="12" t="n">
         <v>46129</v>
       </c>
       <c r="E158" s="4" t="inlineStr">
@@ -14375,14 +13893,14 @@
         <v>0</v>
       </c>
       <c r="O158" s="4" t="inlineStr"/>
-      <c r="P158" s="14" t="inlineStr">
+      <c r="P158" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: sin registro | enero2026: sin registro | febrero2026: sin registro | marzo2026: sin registro</t>
         </is>
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="7" t="inlineStr">
+      <c r="A159" s="5" t="inlineStr">
         <is>
           <t>VERDE</t>
         </is>
@@ -14397,7 +13915,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="D159" s="13" t="n">
+      <c r="D159" s="12" t="n">
         <v>46129</v>
       </c>
       <c r="E159" s="4" t="inlineStr">
@@ -14441,14 +13959,14 @@
           <t>7ma cuota</t>
         </is>
       </c>
-      <c r="P159" s="14" t="inlineStr">
+      <c r="P159" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: cuotas=1, monto=76000, obs=4ta cuota | enero2026: cuotas=1, monto=76000, obs=5ta cuota | febrero2026: cuotas=1, monto=76000, obs=6ta cuota | marzo2026: cuotas=1, monto=76000, obs=7ma cuota</t>
         </is>
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="7" t="inlineStr">
+      <c r="A160" s="5" t="inlineStr">
         <is>
           <t>VERDE</t>
         </is>
@@ -14463,7 +13981,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="D160" s="13" t="n">
+      <c r="D160" s="12" t="n">
         <v>46132</v>
       </c>
       <c r="E160" s="4" t="inlineStr">
@@ -14507,14 +14025,14 @@
           <t>6ta y 7ma cuota</t>
         </is>
       </c>
-      <c r="P160" s="14" t="inlineStr">
+      <c r="P160" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: cuotas=1, monto=38000, obs=3ra cuota | enero2026: cuotas=1, monto=38000, obs=4ta cuota | febrero2026: cuotas=1, monto=38000, obs=5ta cuota | marzo2026: cuotas=2, monto=76000, obs=6ta y 7ma cuota</t>
         </is>
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="8" t="inlineStr">
+      <c r="A161" s="7" t="inlineStr">
         <is>
           <t>AMARILLO</t>
         </is>
@@ -14529,7 +14047,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="D161" s="13" t="n">
+      <c r="D161" s="12" t="n">
         <v>46132</v>
       </c>
       <c r="E161" s="4" t="inlineStr">
@@ -14569,14 +14087,14 @@
         <v>0</v>
       </c>
       <c r="O161" s="4" t="inlineStr"/>
-      <c r="P161" s="14" t="inlineStr">
+      <c r="P161" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: sin registro | enero2026: sin registro | febrero2026: sin registro | marzo2026: sin registro</t>
         </is>
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="7" t="inlineStr">
+      <c r="A162" s="5" t="inlineStr">
         <is>
           <t>VERDE</t>
         </is>
@@ -14591,7 +14109,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="D162" s="13" t="n">
+      <c r="D162" s="12" t="n">
         <v>46133</v>
       </c>
       <c r="E162" s="4" t="inlineStr">
@@ -14635,14 +14153,14 @@
           <t>4ta cuota</t>
         </is>
       </c>
-      <c r="P162" s="14" t="inlineStr">
+      <c r="P162" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: cuotas=1, monto=190000, obs=1ra cuota | enero2026: cuotas=1, monto=190000, obs=2da cuota | febrero2026: cuotas=1, monto=228000, obs=3ra cuota | marzo2026: cuotas=1, monto=228000, obs=4ta cuota</t>
         </is>
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="8" t="inlineStr">
+      <c r="A163" s="7" t="inlineStr">
         <is>
           <t>AMARILLO</t>
         </is>
@@ -14657,7 +14175,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="D163" s="13" t="n">
+      <c r="D163" s="12" t="n">
         <v>46133</v>
       </c>
       <c r="E163" s="4" t="inlineStr">
@@ -14697,7 +14215,7 @@
         <v>0</v>
       </c>
       <c r="O163" s="4" t="inlineStr"/>
-      <c r="P163" s="14" t="inlineStr">
+      <c r="P163" s="13" t="inlineStr">
         <is>
           <t>diciembre2025: sin registro | enero2026: sin registro | febrero2026: sin registro | marzo2026: sin registro</t>
         </is>

--- a/catamarca_creditos/analisis_cartera_catamarca.xlsx
+++ b/catamarca_creditos/analisis_cartera_catamarca.xlsx
@@ -23,7 +23,7 @@
     <numFmt numFmtId="164" formatCode="$ #,##0.00"/>
     <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -43,8 +43,49 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001F1F1F"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001F1F1F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="001F1F1F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001F1F1F"/>
+      <sz val="15"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001F1F1F"/>
+      <sz val="12"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="14">
     <fill>
       <patternFill/>
     </fill>
@@ -76,6 +117,41 @@
         <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F3B5C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DCEAF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EDF4FB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9EAD3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4CCCC"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -103,7 +179,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -121,6 +197,49 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="9" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="9" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -552,247 +671,355 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="4" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="3" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="3" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="21" customHeight="1">
+      <c r="A1" s="14" t="inlineStr">
         <is>
           <t>ANÁLISIS DE CARTERA CATAMARCA</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="2" ht="21" customHeight="1">
+      <c r="A2" s="15" t="inlineStr">
+        <is>
+          <t>Dashboard ejecutivo | créditos desde 2025-12-01 y cobranza hasta marzo 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="21" customHeight="1"/>
+    <row r="4" ht="21" customHeight="1">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>Fuente</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t>Cruce entre Excel de depósitos y Excel de cobranzas Cecilia</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Corte</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Créditos desde 2025-12-01 y lectura de cobranza hasta marzo 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="n"/>
+      <c r="F4" s="4" t="n"/>
+      <c r="G4" s="4" t="n"/>
+      <c r="H4" s="4" t="n"/>
+    </row>
+    <row r="5" ht="21" customHeight="1">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>Criterio de mora</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="inlineStr">
+        <is>
+          <t>Mora operativa = crédito exigible a marzo sin cobro en marzo o sin registro en marzo, salvo cancelado/finalizado</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="n"/>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="4" t="n"/>
+      <c r="F5" s="4" t="n"/>
+      <c r="G5" s="4" t="n"/>
+      <c r="H5" s="4" t="n"/>
+    </row>
+    <row r="6" ht="21" customHeight="1">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>Semáforo</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B6" s="17" t="inlineStr">
         <is>
           <t>VERDE = al día / con cobro o finalizado | AMARILLO = sin exigibilidad clara | ROJO = mora operativa</t>
         </is>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>KPIs principales</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Valor</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>Resumen de estado</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="C6" s="4" t="n"/>
+      <c r="D6" s="4" t="n"/>
+      <c r="E6" s="4" t="n"/>
+      <c r="F6" s="4" t="n"/>
+      <c r="G6" s="4" t="n"/>
+      <c r="H6" s="4" t="n"/>
+    </row>
+    <row r="7" ht="21" customHeight="1"/>
+    <row r="8" ht="21" customHeight="1">
+      <c r="A8" s="18" t="inlineStr">
+        <is>
+          <t>Créditos analizados</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="n"/>
+      <c r="D8" s="18" t="inlineStr">
+        <is>
+          <t>Monto depositado total</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="n"/>
+      <c r="G8" s="18" t="inlineStr">
+        <is>
+          <t>Monto total a cobrar</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="n"/>
+    </row>
+    <row r="9" ht="21" customHeight="1">
+      <c r="A9" s="19" t="n">
+        <v>162</v>
+      </c>
+      <c r="B9" s="20" t="n"/>
+      <c r="D9" s="21" t="n">
+        <v>70588070</v>
+      </c>
+      <c r="E9" s="20" t="n"/>
+      <c r="G9" s="21" t="n">
+        <v>293652000</v>
+      </c>
+      <c r="H9" s="20" t="n"/>
+    </row>
+    <row r="10" ht="21" customHeight="1">
+      <c r="A10" s="20" t="n"/>
+      <c r="B10" s="20" t="n"/>
+      <c r="D10" s="20" t="n"/>
+      <c r="E10" s="20" t="n"/>
+      <c r="G10" s="20" t="n"/>
+      <c r="H10" s="20" t="n"/>
+    </row>
+    <row r="11" ht="21" customHeight="1"/>
+    <row r="12" ht="21" customHeight="1">
+      <c r="A12" s="18" t="inlineStr">
+        <is>
+          <t>Monto cobrado en marzo</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="n"/>
+      <c r="D12" s="18" t="inlineStr">
+        <is>
+          <t>Mora operativa</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="n"/>
+      <c r="G12" s="18" t="inlineStr">
+        <is>
+          <t>Monto cartera en mora</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="n"/>
+    </row>
+    <row r="13" ht="21" customHeight="1">
+      <c r="A13" s="21" t="n">
+        <v>8740000</v>
+      </c>
+      <c r="B13" s="20" t="n"/>
+      <c r="D13" s="19" t="n">
+        <v>59</v>
+      </c>
+      <c r="E13" s="20" t="n"/>
+      <c r="G13" s="21" t="n">
+        <v>106806000</v>
+      </c>
+      <c r="H13" s="20" t="n"/>
+    </row>
+    <row r="14" ht="21" customHeight="1">
+      <c r="A14" s="20" t="n"/>
+      <c r="B14" s="20" t="n"/>
+      <c r="D14" s="20" t="n"/>
+      <c r="E14" s="20" t="n"/>
+      <c r="G14" s="20" t="n"/>
+      <c r="H14" s="20" t="n"/>
+    </row>
+    <row r="15" ht="21" customHeight="1"/>
+    <row r="16" ht="21" customHeight="1">
+      <c r="A16" s="18" t="inlineStr">
+        <is>
+          <t>% con cobro en marzo</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="n"/>
+      <c r="D16" s="18" t="inlineStr">
+        <is>
+          <t>% mora operativa</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="n"/>
+      <c r="G16" s="22" t="inlineStr">
+        <is>
+          <t>Semaforización</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="21" customHeight="1">
+      <c r="A17" s="23" t="n">
+        <v>0.3641975308641975</v>
+      </c>
+      <c r="B17" s="20" t="n"/>
+      <c r="D17" s="23" t="n">
+        <v>0.3641975308641975</v>
+      </c>
+      <c r="E17" s="20" t="n"/>
+      <c r="G17" s="24" t="inlineStr">
+        <is>
+          <t>VERDE</t>
+        </is>
+      </c>
+      <c r="H17" s="25" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="18" ht="21" customHeight="1">
+      <c r="A18" s="20" t="n"/>
+      <c r="B18" s="20" t="n"/>
+      <c r="D18" s="20" t="n"/>
+      <c r="E18" s="20" t="n"/>
+      <c r="G18" s="26" t="inlineStr">
+        <is>
+          <t>AMARILLO</t>
+        </is>
+      </c>
+      <c r="H18" s="25" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="19" ht="21" customHeight="1">
+      <c r="G19" s="27" t="inlineStr">
+        <is>
+          <t>ROJO</t>
+        </is>
+      </c>
+      <c r="H19" s="25" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="20" ht="21" customHeight="1"/>
+    <row r="21" ht="21" customHeight="1"/>
+    <row r="22" ht="21" customHeight="1">
+      <c r="A22" s="22" t="inlineStr">
+        <is>
+          <t>Resumen de estado de cartera</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="21" customHeight="1">
+      <c r="A23" s="17" t="inlineStr">
+        <is>
+          <t>Cobro en marzo</t>
+        </is>
+      </c>
+      <c r="B23" s="13" t="n"/>
+      <c r="C23" s="13" t="n"/>
+      <c r="D23" s="13" t="n"/>
+      <c r="E23" s="13" t="n"/>
+      <c r="F23" s="13" t="n"/>
+      <c r="G23" s="28" t="inlineStr">
         <is>
           <t>Cantidad</t>
         </is>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>Créditos analizados</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="n">
-        <v>162</v>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>VERDE</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="n">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>Monto depositado total</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="n">
-        <v>70588070</v>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>AMARILLO</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="n">
+      <c r="H23" s="25" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="24" ht="21" customHeight="1">
+      <c r="A24" s="17" t="inlineStr">
+        <is>
+          <t>Cancelados / finalizados</t>
+        </is>
+      </c>
+      <c r="B24" s="13" t="n"/>
+      <c r="C24" s="13" t="n"/>
+      <c r="D24" s="13" t="n"/>
+      <c r="E24" s="13" t="n"/>
+      <c r="F24" s="13" t="n"/>
+      <c r="G24" s="28" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+      <c r="H24" s="25" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" ht="21" customHeight="1">
+      <c r="A25" s="17" t="inlineStr">
+        <is>
+          <t>Sin cobro en marzo</t>
+        </is>
+      </c>
+      <c r="B25" s="13" t="n"/>
+      <c r="C25" s="13" t="n"/>
+      <c r="D25" s="13" t="n"/>
+      <c r="E25" s="13" t="n"/>
+      <c r="F25" s="13" t="n"/>
+      <c r="G25" s="28" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+      <c r="H25" s="25" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="26" ht="21" customHeight="1">
+      <c r="A26" s="17" t="inlineStr">
+        <is>
+          <t>Sin registro en marzo</t>
+        </is>
+      </c>
+      <c r="B26" s="13" t="n"/>
+      <c r="C26" s="13" t="n"/>
+      <c r="D26" s="13" t="n"/>
+      <c r="E26" s="13" t="n"/>
+      <c r="F26" s="13" t="n"/>
+      <c r="G26" s="28" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+      <c r="H26" s="25" t="n">
         <v>25</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>Monto total a cobrar</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="n">
-        <v>293652000</v>
-      </c>
-      <c r="D9" s="8" t="inlineStr">
-        <is>
-          <t>ROJO</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="n">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>Monto cobrado en marzo</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="n">
-        <v>8740000</v>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>Cancelados / finalizados</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>Clientes con cobro en marzo</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="n">
-        <v>59</v>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>Sin cobro en marzo</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="n">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>Mora operativa</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="n">
-        <v>59</v>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>Sin registro en marzo</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>Monto cartera en mora</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="n">
-        <v>106806000</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>% mora operativa</t>
-        </is>
-      </c>
-      <c r="B14" s="9" t="n">
-        <v>0.3641975308641975</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>Resumen ejecutivo</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Créditos analizados: 162</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Clientes con cobro en marzo: 59</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Mora operativa: 59</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Cancelados / finalizados: 23</t>
-        </is>
-      </c>
-    </row>
+    <row r="27" ht="21" customHeight="1"/>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
+  <mergeCells count="27">
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="B6:H6"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="A26:F26"/>
+    <mergeCell ref="A17:B18"/>
+    <mergeCell ref="B5:H5"/>
+    <mergeCell ref="D9:E10"/>
+    <mergeCell ref="A13:B14"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="B4:H4"/>
+    <mergeCell ref="A23:F23"/>
+    <mergeCell ref="A9:B10"/>
+    <mergeCell ref="G9:H10"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="A22:H22"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="G13:H14"/>
+    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="D17:E18"/>
+    <mergeCell ref="A25:F25"/>
+    <mergeCell ref="D13:E14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/catamarca_creditos/analisis_cartera_catamarca.xlsx
+++ b/catamarca_creditos/analisis_cartera_catamarca.xlsx
@@ -8,9 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KPIs" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mora" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Consolidado" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mora" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Consolidado" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -153,7 +152,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -175,11 +174,95 @@
         <color rgb="00D9D9D9"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D9D9D9"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D9D9D9"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -241,6 +324,11 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -328,18 +416,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T_KPIs" displayName="T_KPIs" ref="A1:B14" headerRowCount="1">
-  <autoFilter ref="A1:B14"/>
-  <tableColumns count="2">
-    <tableColumn id="1" name="KPI"/>
-    <tableColumn id="2" name="Valor"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="T_Mora" displayName="T_Mora" ref="A1:J60" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T_Mora" displayName="T_Mora" ref="A1:J60" headerRowCount="1">
   <autoFilter ref="A1:J60"/>
   <tableColumns count="10">
     <tableColumn id="1" name="Semáforo"/>
@@ -357,8 +434,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="T_Consolidado" displayName="T_Consolidado" ref="A1:P163" headerRowCount="1">
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="T_Consolidado" displayName="T_Consolidado" ref="A1:P163" headerRowCount="1">
   <autoFilter ref="A1:P163"/>
   <tableColumns count="16">
     <tableColumn id="1" name="Semáforo"/>
@@ -710,12 +787,12 @@
           <t>Cruce entre Excel de depósitos y Excel de cobranzas Cecilia</t>
         </is>
       </c>
-      <c r="C4" s="4" t="n"/>
-      <c r="D4" s="4" t="n"/>
-      <c r="E4" s="4" t="n"/>
-      <c r="F4" s="4" t="n"/>
-      <c r="G4" s="4" t="n"/>
-      <c r="H4" s="4" t="n"/>
+      <c r="C4" s="29" t="n"/>
+      <c r="D4" s="29" t="n"/>
+      <c r="E4" s="29" t="n"/>
+      <c r="F4" s="29" t="n"/>
+      <c r="G4" s="29" t="n"/>
+      <c r="H4" s="30" t="n"/>
     </row>
     <row r="5" ht="21" customHeight="1">
       <c r="A5" s="16" t="inlineStr">
@@ -728,12 +805,12 @@
           <t>Mora operativa = crédito exigible a marzo sin cobro en marzo o sin registro en marzo, salvo cancelado/finalizado</t>
         </is>
       </c>
-      <c r="C5" s="4" t="n"/>
-      <c r="D5" s="4" t="n"/>
-      <c r="E5" s="4" t="n"/>
-      <c r="F5" s="4" t="n"/>
-      <c r="G5" s="4" t="n"/>
-      <c r="H5" s="4" t="n"/>
+      <c r="C5" s="29" t="n"/>
+      <c r="D5" s="29" t="n"/>
+      <c r="E5" s="29" t="n"/>
+      <c r="F5" s="29" t="n"/>
+      <c r="G5" s="29" t="n"/>
+      <c r="H5" s="30" t="n"/>
     </row>
     <row r="6" ht="21" customHeight="1">
       <c r="A6" s="16" t="inlineStr">
@@ -746,12 +823,12 @@
           <t>VERDE = al día / con cobro o finalizado | AMARILLO = sin exigibilidad clara | ROJO = mora operativa</t>
         </is>
       </c>
-      <c r="C6" s="4" t="n"/>
-      <c r="D6" s="4" t="n"/>
-      <c r="E6" s="4" t="n"/>
-      <c r="F6" s="4" t="n"/>
-      <c r="G6" s="4" t="n"/>
-      <c r="H6" s="4" t="n"/>
+      <c r="C6" s="29" t="n"/>
+      <c r="D6" s="29" t="n"/>
+      <c r="E6" s="29" t="n"/>
+      <c r="F6" s="29" t="n"/>
+      <c r="G6" s="29" t="n"/>
+      <c r="H6" s="30" t="n"/>
     </row>
     <row r="7" ht="21" customHeight="1"/>
     <row r="8" ht="21" customHeight="1">
@@ -760,41 +837,41 @@
           <t>Créditos analizados</t>
         </is>
       </c>
-      <c r="B8" s="4" t="n"/>
+      <c r="B8" s="30" t="n"/>
       <c r="D8" s="18" t="inlineStr">
         <is>
           <t>Monto depositado total</t>
         </is>
       </c>
-      <c r="E8" s="4" t="n"/>
+      <c r="E8" s="30" t="n"/>
       <c r="G8" s="18" t="inlineStr">
         <is>
           <t>Monto total a cobrar</t>
         </is>
       </c>
-      <c r="H8" s="4" t="n"/>
+      <c r="H8" s="30" t="n"/>
     </row>
     <row r="9" ht="21" customHeight="1">
       <c r="A9" s="19" t="n">
         <v>162</v>
       </c>
-      <c r="B9" s="20" t="n"/>
+      <c r="B9" s="31" t="n"/>
       <c r="D9" s="21" t="n">
         <v>70588070</v>
       </c>
-      <c r="E9" s="20" t="n"/>
+      <c r="E9" s="31" t="n"/>
       <c r="G9" s="21" t="n">
         <v>293652000</v>
       </c>
-      <c r="H9" s="20" t="n"/>
+      <c r="H9" s="31" t="n"/>
     </row>
     <row r="10" ht="21" customHeight="1">
-      <c r="A10" s="20" t="n"/>
-      <c r="B10" s="20" t="n"/>
-      <c r="D10" s="20" t="n"/>
-      <c r="E10" s="20" t="n"/>
-      <c r="G10" s="20" t="n"/>
-      <c r="H10" s="20" t="n"/>
+      <c r="A10" s="32" t="n"/>
+      <c r="B10" s="33" t="n"/>
+      <c r="D10" s="32" t="n"/>
+      <c r="E10" s="33" t="n"/>
+      <c r="G10" s="32" t="n"/>
+      <c r="H10" s="33" t="n"/>
     </row>
     <row r="11" ht="21" customHeight="1"/>
     <row r="12" ht="21" customHeight="1">
@@ -803,41 +880,41 @@
           <t>Monto cobrado en marzo</t>
         </is>
       </c>
-      <c r="B12" s="4" t="n"/>
+      <c r="B12" s="30" t="n"/>
       <c r="D12" s="18" t="inlineStr">
         <is>
           <t>Mora operativa</t>
         </is>
       </c>
-      <c r="E12" s="4" t="n"/>
+      <c r="E12" s="30" t="n"/>
       <c r="G12" s="18" t="inlineStr">
         <is>
           <t>Monto cartera en mora</t>
         </is>
       </c>
-      <c r="H12" s="4" t="n"/>
+      <c r="H12" s="30" t="n"/>
     </row>
     <row r="13" ht="21" customHeight="1">
       <c r="A13" s="21" t="n">
         <v>8740000</v>
       </c>
-      <c r="B13" s="20" t="n"/>
+      <c r="B13" s="31" t="n"/>
       <c r="D13" s="19" t="n">
         <v>59</v>
       </c>
-      <c r="E13" s="20" t="n"/>
+      <c r="E13" s="31" t="n"/>
       <c r="G13" s="21" t="n">
         <v>106806000</v>
       </c>
-      <c r="H13" s="20" t="n"/>
+      <c r="H13" s="31" t="n"/>
     </row>
     <row r="14" ht="21" customHeight="1">
-      <c r="A14" s="20" t="n"/>
-      <c r="B14" s="20" t="n"/>
-      <c r="D14" s="20" t="n"/>
-      <c r="E14" s="20" t="n"/>
-      <c r="G14" s="20" t="n"/>
-      <c r="H14" s="20" t="n"/>
+      <c r="A14" s="32" t="n"/>
+      <c r="B14" s="33" t="n"/>
+      <c r="D14" s="32" t="n"/>
+      <c r="E14" s="33" t="n"/>
+      <c r="G14" s="32" t="n"/>
+      <c r="H14" s="33" t="n"/>
     </row>
     <row r="15" ht="21" customHeight="1"/>
     <row r="16" ht="21" customHeight="1">
@@ -846,13 +923,13 @@
           <t>% con cobro en marzo</t>
         </is>
       </c>
-      <c r="B16" s="4" t="n"/>
+      <c r="B16" s="30" t="n"/>
       <c r="D16" s="18" t="inlineStr">
         <is>
           <t>% mora operativa</t>
         </is>
       </c>
-      <c r="E16" s="4" t="n"/>
+      <c r="E16" s="30" t="n"/>
       <c r="G16" s="22" t="inlineStr">
         <is>
           <t>Semaforización</t>
@@ -863,11 +940,11 @@
       <c r="A17" s="23" t="n">
         <v>0.3641975308641975</v>
       </c>
-      <c r="B17" s="20" t="n"/>
+      <c r="B17" s="31" t="n"/>
       <c r="D17" s="23" t="n">
         <v>0.3641975308641975</v>
       </c>
-      <c r="E17" s="20" t="n"/>
+      <c r="E17" s="31" t="n"/>
       <c r="G17" s="24" t="inlineStr">
         <is>
           <t>VERDE</t>
@@ -878,10 +955,10 @@
       </c>
     </row>
     <row r="18" ht="21" customHeight="1">
-      <c r="A18" s="20" t="n"/>
-      <c r="B18" s="20" t="n"/>
-      <c r="D18" s="20" t="n"/>
-      <c r="E18" s="20" t="n"/>
+      <c r="A18" s="32" t="n"/>
+      <c r="B18" s="33" t="n"/>
+      <c r="D18" s="32" t="n"/>
+      <c r="E18" s="33" t="n"/>
       <c r="G18" s="26" t="inlineStr">
         <is>
           <t>AMARILLO</t>
@@ -916,11 +993,11 @@
           <t>Cobro en marzo</t>
         </is>
       </c>
-      <c r="B23" s="13" t="n"/>
-      <c r="C23" s="13" t="n"/>
-      <c r="D23" s="13" t="n"/>
-      <c r="E23" s="13" t="n"/>
-      <c r="F23" s="13" t="n"/>
+      <c r="B23" s="29" t="n"/>
+      <c r="C23" s="29" t="n"/>
+      <c r="D23" s="29" t="n"/>
+      <c r="E23" s="29" t="n"/>
+      <c r="F23" s="30" t="n"/>
       <c r="G23" s="28" t="inlineStr">
         <is>
           <t>Cantidad</t>
@@ -936,11 +1013,11 @@
           <t>Cancelados / finalizados</t>
         </is>
       </c>
-      <c r="B24" s="13" t="n"/>
-      <c r="C24" s="13" t="n"/>
-      <c r="D24" s="13" t="n"/>
-      <c r="E24" s="13" t="n"/>
-      <c r="F24" s="13" t="n"/>
+      <c r="B24" s="29" t="n"/>
+      <c r="C24" s="29" t="n"/>
+      <c r="D24" s="29" t="n"/>
+      <c r="E24" s="29" t="n"/>
+      <c r="F24" s="30" t="n"/>
       <c r="G24" s="28" t="inlineStr">
         <is>
           <t>Cantidad</t>
@@ -956,11 +1033,11 @@
           <t>Sin cobro en marzo</t>
         </is>
       </c>
-      <c r="B25" s="13" t="n"/>
-      <c r="C25" s="13" t="n"/>
-      <c r="D25" s="13" t="n"/>
-      <c r="E25" s="13" t="n"/>
-      <c r="F25" s="13" t="n"/>
+      <c r="B25" s="29" t="n"/>
+      <c r="C25" s="29" t="n"/>
+      <c r="D25" s="29" t="n"/>
+      <c r="E25" s="29" t="n"/>
+      <c r="F25" s="30" t="n"/>
       <c r="G25" s="28" t="inlineStr">
         <is>
           <t>Cantidad</t>
@@ -976,11 +1053,11 @@
           <t>Sin registro en marzo</t>
         </is>
       </c>
-      <c r="B26" s="13" t="n"/>
-      <c r="C26" s="13" t="n"/>
-      <c r="D26" s="13" t="n"/>
-      <c r="E26" s="13" t="n"/>
-      <c r="F26" s="13" t="n"/>
+      <c r="B26" s="29" t="n"/>
+      <c r="C26" s="29" t="n"/>
+      <c r="D26" s="29" t="n"/>
+      <c r="E26" s="29" t="n"/>
+      <c r="F26" s="30" t="n"/>
       <c r="G26" s="28" t="inlineStr">
         <is>
           <t>Cantidad</t>
@@ -998,8 +1075,8 @@
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="G8:H8"/>
     <mergeCell ref="A26:F26"/>
+    <mergeCell ref="B5:H5"/>
     <mergeCell ref="A17:B18"/>
-    <mergeCell ref="B5:H5"/>
     <mergeCell ref="D9:E10"/>
     <mergeCell ref="A13:B14"/>
     <mergeCell ref="A16:B16"/>
@@ -1031,169 +1108,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="45" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="10" t="inlineStr">
-        <is>
-          <t>KPI</t>
-        </is>
-      </c>
-      <c r="B1" s="10" t="inlineStr">
-        <is>
-          <t>Valor</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>Créditos analizados (desde 2025-12-01)</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="n">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Monto depositado total</t>
-        </is>
-      </c>
-      <c r="B3" s="6" t="n">
-        <v>70588070</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>Monto total a cobrar</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>293652000</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>Monto cobrado en marzo 2026</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="n">
-        <v>8740000</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>Clientes con cobro en marzo</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="n">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>Cancelados / finalizados</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>Sin cobro en marzo</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="n">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>Sin registro en marzo</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>Mora operativa</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="n">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>Monto total de cartera en mora operativa</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="n">
-        <v>106806000</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>Ticket promedio depositado</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="n">
-        <v>435728.8271604938</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>% con cobro en marzo</t>
-        </is>
-      </c>
-      <c r="B13" s="9" t="n">
-        <v>0.3641975308641975</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>% mora operativa</t>
-        </is>
-      </c>
-      <c r="B14" s="9" t="n">
-        <v>0.3641975308641975</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:J60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -3747,7 +3661,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
